--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="77">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -218,12 +218,42 @@
   </si>
   <si>
     <t>Nº</t>
+  </si>
+  <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
+    <t>2025</t>
+  </si>
+  <si>
+    <t>Djurgården</t>
+  </si>
+  <si>
+    <t>Häcken</t>
+  </si>
+  <si>
+    <t>Malmö FF</t>
+  </si>
+  <si>
+    <t>Brommapojkarna</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>['73', '90+4']</t>
+  </si>
+  <si>
+    <t>['45+8']</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -276,11 +306,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -575,7 +606,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP1"/>
+  <dimension ref="A1:BP3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -784,6 +815,418 @@
         <v>66</v>
       </c>
     </row>
+    <row r="2" spans="1:68">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>7778952</v>
+      </c>
+      <c r="C2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="2">
+        <v>45745.45833333334</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2" t="s">
+        <v>74</v>
+      </c>
+      <c r="P2" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q2">
+        <v>3.5</v>
+      </c>
+      <c r="R2">
+        <v>2.1</v>
+      </c>
+      <c r="S2">
+        <v>3.1</v>
+      </c>
+      <c r="T2">
+        <v>1.4</v>
+      </c>
+      <c r="U2">
+        <v>2.75</v>
+      </c>
+      <c r="V2">
+        <v>3</v>
+      </c>
+      <c r="W2">
+        <v>1.36</v>
+      </c>
+      <c r="X2">
+        <v>8</v>
+      </c>
+      <c r="Y2">
+        <v>1.08</v>
+      </c>
+      <c r="Z2">
+        <v>3.06</v>
+      </c>
+      <c r="AA2">
+        <v>3.32</v>
+      </c>
+      <c r="AB2">
+        <v>2.26</v>
+      </c>
+      <c r="AC2">
+        <v>1.06</v>
+      </c>
+      <c r="AD2">
+        <v>9.5</v>
+      </c>
+      <c r="AE2">
+        <v>1.3</v>
+      </c>
+      <c r="AF2">
+        <v>3.55</v>
+      </c>
+      <c r="AG2">
+        <v>1.91</v>
+      </c>
+      <c r="AH2">
+        <v>1.83</v>
+      </c>
+      <c r="AI2">
+        <v>1.75</v>
+      </c>
+      <c r="AJ2">
+        <v>2</v>
+      </c>
+      <c r="AK2">
+        <v>1.58</v>
+      </c>
+      <c r="AL2">
+        <v>1.3</v>
+      </c>
+      <c r="AM2">
+        <v>1.39</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <v>3</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>2</v>
+      </c>
+      <c r="AV2">
+        <v>3</v>
+      </c>
+      <c r="AW2">
+        <v>14</v>
+      </c>
+      <c r="AX2">
+        <v>7</v>
+      </c>
+      <c r="AY2">
+        <v>22</v>
+      </c>
+      <c r="AZ2">
+        <v>12</v>
+      </c>
+      <c r="BA2">
+        <v>7</v>
+      </c>
+      <c r="BB2">
+        <v>3</v>
+      </c>
+      <c r="BC2">
+        <v>10</v>
+      </c>
+      <c r="BD2">
+        <v>1.98</v>
+      </c>
+      <c r="BE2">
+        <v>6.75</v>
+      </c>
+      <c r="BF2">
+        <v>1.98</v>
+      </c>
+      <c r="BG2">
+        <v>1.23</v>
+      </c>
+      <c r="BH2">
+        <v>3.7</v>
+      </c>
+      <c r="BI2">
+        <v>1.4</v>
+      </c>
+      <c r="BJ2">
+        <v>2.7</v>
+      </c>
+      <c r="BK2">
+        <v>1.64</v>
+      </c>
+      <c r="BL2">
+        <v>2.1</v>
+      </c>
+      <c r="BM2">
+        <v>2</v>
+      </c>
+      <c r="BN2">
+        <v>1.71</v>
+      </c>
+      <c r="BO2">
+        <v>2.55</v>
+      </c>
+      <c r="BP2">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:68">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>7778956</v>
+      </c>
+      <c r="C3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="2">
+        <v>45745.5625</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" t="s">
+        <v>73</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>2</v>
+      </c>
+      <c r="O3" t="s">
+        <v>75</v>
+      </c>
+      <c r="P3" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q3">
+        <v>2.05</v>
+      </c>
+      <c r="R3">
+        <v>2.6</v>
+      </c>
+      <c r="S3">
+        <v>5</v>
+      </c>
+      <c r="T3">
+        <v>1.25</v>
+      </c>
+      <c r="U3">
+        <v>3.75</v>
+      </c>
+      <c r="V3">
+        <v>2.2</v>
+      </c>
+      <c r="W3">
+        <v>1.62</v>
+      </c>
+      <c r="X3">
+        <v>5</v>
+      </c>
+      <c r="Y3">
+        <v>1.17</v>
+      </c>
+      <c r="Z3">
+        <v>1.62</v>
+      </c>
+      <c r="AA3">
+        <v>4.4</v>
+      </c>
+      <c r="AB3">
+        <v>4.4</v>
+      </c>
+      <c r="AC3">
+        <v>1.01</v>
+      </c>
+      <c r="AD3">
+        <v>16.5</v>
+      </c>
+      <c r="AE3">
+        <v>1.14</v>
+      </c>
+      <c r="AF3">
+        <v>5.55</v>
+      </c>
+      <c r="AG3">
+        <v>1.42</v>
+      </c>
+      <c r="AH3">
+        <v>2.74</v>
+      </c>
+      <c r="AI3">
+        <v>1.57</v>
+      </c>
+      <c r="AJ3">
+        <v>2.25</v>
+      </c>
+      <c r="AK3">
+        <v>1.18</v>
+      </c>
+      <c r="AL3">
+        <v>1.21</v>
+      </c>
+      <c r="AM3">
+        <v>2.2</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>3</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>7</v>
+      </c>
+      <c r="AV3">
+        <v>3</v>
+      </c>
+      <c r="AW3">
+        <v>8</v>
+      </c>
+      <c r="AX3">
+        <v>9</v>
+      </c>
+      <c r="AY3">
+        <v>19</v>
+      </c>
+      <c r="AZ3">
+        <v>14</v>
+      </c>
+      <c r="BA3">
+        <v>7</v>
+      </c>
+      <c r="BB3">
+        <v>5</v>
+      </c>
+      <c r="BC3">
+        <v>12</v>
+      </c>
+      <c r="BD3">
+        <v>1.47</v>
+      </c>
+      <c r="BE3">
+        <v>7.5</v>
+      </c>
+      <c r="BF3">
+        <v>2.9</v>
+      </c>
+      <c r="BG3">
+        <v>1.11</v>
+      </c>
+      <c r="BH3">
+        <v>5.3</v>
+      </c>
+      <c r="BI3">
+        <v>1.22</v>
+      </c>
+      <c r="BJ3">
+        <v>3.8</v>
+      </c>
+      <c r="BK3">
+        <v>1.36</v>
+      </c>
+      <c r="BL3">
+        <v>2.85</v>
+      </c>
+      <c r="BM3">
+        <v>1.57</v>
+      </c>
+      <c r="BN3">
+        <v>2.23</v>
+      </c>
+      <c r="BO3">
+        <v>1.89</v>
+      </c>
+      <c r="BP3">
+        <v>1.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="91">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -232,19 +232,61 @@
     <t>Häcken</t>
   </si>
   <si>
+    <t>Hammarby</t>
+  </si>
+  <si>
+    <t>Elfsborg</t>
+  </si>
+  <si>
+    <t>Norrköping</t>
+  </si>
+  <si>
+    <t>Halmstad</t>
+  </si>
+  <si>
     <t>Malmö FF</t>
   </si>
   <si>
     <t>Brommapojkarna</t>
   </si>
   <si>
+    <t>IFK Göteborg</t>
+  </si>
+  <si>
+    <t>Mjällby</t>
+  </si>
+  <si>
+    <t>Öster</t>
+  </si>
+  <si>
+    <t>Degerfors</t>
+  </si>
+  <si>
     <t>[]</t>
   </si>
   <si>
     <t>['73', '90+4']</t>
   </si>
   <si>
+    <t>['21', '42', '73', '85']</t>
+  </si>
+  <si>
+    <t>['60', '78']</t>
+  </si>
+  <si>
+    <t>['17', '19', '50', '65']</t>
+  </si>
+  <si>
     <t>['45+8']</t>
+  </si>
+  <si>
+    <t>['20', '29']</t>
+  </si>
+  <si>
+    <t>['31', '78', '90']</t>
+  </si>
+  <si>
+    <t>['45+1', '55', '74', '83', '90+3']</t>
   </si>
 </sst>
 </file>
@@ -606,7 +648,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP3"/>
+  <dimension ref="A1:BP7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -838,7 +880,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -859,10 +901,10 @@
         <v>1</v>
       </c>
       <c r="O2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="Q2">
         <v>3.5</v>
@@ -1044,7 +1086,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1065,10 +1107,10 @@
         <v>2</v>
       </c>
       <c r="O3" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="Q3">
         <v>2.05</v>
@@ -1225,6 +1267,830 @@
       </c>
       <c r="BP3">
         <v>1.8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:68">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>7778953</v>
+      </c>
+      <c r="C4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="2">
+        <v>45746.375</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H4" t="s">
+        <v>78</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>4</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>4</v>
+      </c>
+      <c r="O4" t="s">
+        <v>84</v>
+      </c>
+      <c r="P4" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q4">
+        <v>2.4</v>
+      </c>
+      <c r="R4">
+        <v>2.25</v>
+      </c>
+      <c r="S4">
+        <v>4.5</v>
+      </c>
+      <c r="T4">
+        <v>1.36</v>
+      </c>
+      <c r="U4">
+        <v>3</v>
+      </c>
+      <c r="V4">
+        <v>2.63</v>
+      </c>
+      <c r="W4">
+        <v>1.44</v>
+      </c>
+      <c r="X4">
+        <v>7</v>
+      </c>
+      <c r="Y4">
+        <v>1.1</v>
+      </c>
+      <c r="Z4">
+        <v>1.83</v>
+      </c>
+      <c r="AA4">
+        <v>3.74</v>
+      </c>
+      <c r="AB4">
+        <v>3.89</v>
+      </c>
+      <c r="AC4">
+        <v>1.05</v>
+      </c>
+      <c r="AD4">
+        <v>10</v>
+      </c>
+      <c r="AE4">
+        <v>1.28</v>
+      </c>
+      <c r="AF4">
+        <v>3.75</v>
+      </c>
+      <c r="AG4">
+        <v>1.8</v>
+      </c>
+      <c r="AH4">
+        <v>1.94</v>
+      </c>
+      <c r="AI4">
+        <v>1.75</v>
+      </c>
+      <c r="AJ4">
+        <v>2</v>
+      </c>
+      <c r="AK4">
+        <v>1.23</v>
+      </c>
+      <c r="AL4">
+        <v>1.26</v>
+      </c>
+      <c r="AM4">
+        <v>1.93</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>3</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>9</v>
+      </c>
+      <c r="AV4">
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <v>10</v>
+      </c>
+      <c r="AX4">
+        <v>5</v>
+      </c>
+      <c r="AY4">
+        <v>19</v>
+      </c>
+      <c r="AZ4">
+        <v>6</v>
+      </c>
+      <c r="BA4">
+        <v>8</v>
+      </c>
+      <c r="BB4">
+        <v>3</v>
+      </c>
+      <c r="BC4">
+        <v>11</v>
+      </c>
+      <c r="BD4">
+        <v>1.66</v>
+      </c>
+      <c r="BE4">
+        <v>7</v>
+      </c>
+      <c r="BF4">
+        <v>2.43</v>
+      </c>
+      <c r="BG4">
+        <v>1.16</v>
+      </c>
+      <c r="BH4">
+        <v>4.4</v>
+      </c>
+      <c r="BI4">
+        <v>1.29</v>
+      </c>
+      <c r="BJ4">
+        <v>3.2</v>
+      </c>
+      <c r="BK4">
+        <v>1.48</v>
+      </c>
+      <c r="BL4">
+        <v>2.43</v>
+      </c>
+      <c r="BM4">
+        <v>1.75</v>
+      </c>
+      <c r="BN4">
+        <v>1.95</v>
+      </c>
+      <c r="BO4">
+        <v>2.15</v>
+      </c>
+      <c r="BP4">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:68">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>7778954</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="2">
+        <v>45746.375</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>73</v>
+      </c>
+      <c r="H5" t="s">
+        <v>79</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+      <c r="N5">
+        <v>4</v>
+      </c>
+      <c r="O5" t="s">
+        <v>85</v>
+      </c>
+      <c r="P5" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q5">
+        <v>2.5</v>
+      </c>
+      <c r="R5">
+        <v>2.2</v>
+      </c>
+      <c r="S5">
+        <v>4.5</v>
+      </c>
+      <c r="T5">
+        <v>1.4</v>
+      </c>
+      <c r="U5">
+        <v>2.75</v>
+      </c>
+      <c r="V5">
+        <v>2.75</v>
+      </c>
+      <c r="W5">
+        <v>1.4</v>
+      </c>
+      <c r="X5">
+        <v>8</v>
+      </c>
+      <c r="Y5">
+        <v>1.08</v>
+      </c>
+      <c r="Z5">
+        <v>1.82</v>
+      </c>
+      <c r="AA5">
+        <v>3.74</v>
+      </c>
+      <c r="AB5">
+        <v>3.96</v>
+      </c>
+      <c r="AC5">
+        <v>1.05</v>
+      </c>
+      <c r="AD5">
+        <v>10</v>
+      </c>
+      <c r="AE5">
+        <v>1.3</v>
+      </c>
+      <c r="AF5">
+        <v>3.55</v>
+      </c>
+      <c r="AG5">
+        <v>1.87</v>
+      </c>
+      <c r="AH5">
+        <v>1.87</v>
+      </c>
+      <c r="AI5">
+        <v>1.8</v>
+      </c>
+      <c r="AJ5">
+        <v>1.95</v>
+      </c>
+      <c r="AK5">
+        <v>1.25</v>
+      </c>
+      <c r="AL5">
+        <v>1.28</v>
+      </c>
+      <c r="AM5">
+        <v>1.83</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>1</v>
+      </c>
+      <c r="AQ5">
+        <v>1</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>6</v>
+      </c>
+      <c r="AV5">
+        <v>6</v>
+      </c>
+      <c r="AW5">
+        <v>13</v>
+      </c>
+      <c r="AX5">
+        <v>5</v>
+      </c>
+      <c r="AY5">
+        <v>22</v>
+      </c>
+      <c r="AZ5">
+        <v>12</v>
+      </c>
+      <c r="BA5">
+        <v>7</v>
+      </c>
+      <c r="BB5">
+        <v>5</v>
+      </c>
+      <c r="BC5">
+        <v>12</v>
+      </c>
+      <c r="BD5">
+        <v>1.5</v>
+      </c>
+      <c r="BE5">
+        <v>7</v>
+      </c>
+      <c r="BF5">
+        <v>2.8</v>
+      </c>
+      <c r="BG5">
+        <v>1.17</v>
+      </c>
+      <c r="BH5">
+        <v>4.3</v>
+      </c>
+      <c r="BI5">
+        <v>1.3</v>
+      </c>
+      <c r="BJ5">
+        <v>3.15</v>
+      </c>
+      <c r="BK5">
+        <v>1.5</v>
+      </c>
+      <c r="BL5">
+        <v>2.35</v>
+      </c>
+      <c r="BM5">
+        <v>1.8</v>
+      </c>
+      <c r="BN5">
+        <v>1.89</v>
+      </c>
+      <c r="BO5">
+        <v>2.23</v>
+      </c>
+      <c r="BP5">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:68">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>7778957</v>
+      </c>
+      <c r="C6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="2">
+        <v>45746.47916666666</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H6" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+      <c r="N6">
+        <v>7</v>
+      </c>
+      <c r="O6" t="s">
+        <v>86</v>
+      </c>
+      <c r="P6" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q6">
+        <v>2.6</v>
+      </c>
+      <c r="R6">
+        <v>2.3</v>
+      </c>
+      <c r="S6">
+        <v>4</v>
+      </c>
+      <c r="T6">
+        <v>1.33</v>
+      </c>
+      <c r="U6">
+        <v>3.25</v>
+      </c>
+      <c r="V6">
+        <v>2.63</v>
+      </c>
+      <c r="W6">
+        <v>1.44</v>
+      </c>
+      <c r="X6">
+        <v>6.5</v>
+      </c>
+      <c r="Y6">
+        <v>1.11</v>
+      </c>
+      <c r="Z6">
+        <v>2.01</v>
+      </c>
+      <c r="AA6">
+        <v>3.73</v>
+      </c>
+      <c r="AB6">
+        <v>3.28</v>
+      </c>
+      <c r="AC6">
+        <v>1.05</v>
+      </c>
+      <c r="AD6">
+        <v>10</v>
+      </c>
+      <c r="AE6">
+        <v>1.25</v>
+      </c>
+      <c r="AF6">
+        <v>4</v>
+      </c>
+      <c r="AG6">
+        <v>1.65</v>
+      </c>
+      <c r="AH6">
+        <v>2.05</v>
+      </c>
+      <c r="AI6">
+        <v>1.62</v>
+      </c>
+      <c r="AJ6">
+        <v>2.2</v>
+      </c>
+      <c r="AK6">
+        <v>1.29</v>
+      </c>
+      <c r="AL6">
+        <v>1.27</v>
+      </c>
+      <c r="AM6">
+        <v>1.78</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>3</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>8</v>
+      </c>
+      <c r="AV6">
+        <v>5</v>
+      </c>
+      <c r="AW6">
+        <v>4</v>
+      </c>
+      <c r="AX6">
+        <v>3</v>
+      </c>
+      <c r="AY6">
+        <v>14</v>
+      </c>
+      <c r="AZ6">
+        <v>8</v>
+      </c>
+      <c r="BA6">
+        <v>8</v>
+      </c>
+      <c r="BB6">
+        <v>10</v>
+      </c>
+      <c r="BC6">
+        <v>18</v>
+      </c>
+      <c r="BD6">
+        <v>1.65</v>
+      </c>
+      <c r="BE6">
+        <v>7</v>
+      </c>
+      <c r="BF6">
+        <v>2.48</v>
+      </c>
+      <c r="BG6">
+        <v>1.14</v>
+      </c>
+      <c r="BH6">
+        <v>4.8</v>
+      </c>
+      <c r="BI6">
+        <v>1.25</v>
+      </c>
+      <c r="BJ6">
+        <v>3.45</v>
+      </c>
+      <c r="BK6">
+        <v>1.43</v>
+      </c>
+      <c r="BL6">
+        <v>2.6</v>
+      </c>
+      <c r="BM6">
+        <v>1.68</v>
+      </c>
+      <c r="BN6">
+        <v>2.05</v>
+      </c>
+      <c r="BO6">
+        <v>2.02</v>
+      </c>
+      <c r="BP6">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:68">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>7778958</v>
+      </c>
+      <c r="C7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45746.47916666666</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>5</v>
+      </c>
+      <c r="N7">
+        <v>5</v>
+      </c>
+      <c r="O7" t="s">
+        <v>82</v>
+      </c>
+      <c r="P7" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q7">
+        <v>3</v>
+      </c>
+      <c r="R7">
+        <v>2.1</v>
+      </c>
+      <c r="S7">
+        <v>3.6</v>
+      </c>
+      <c r="T7">
+        <v>1.44</v>
+      </c>
+      <c r="U7">
+        <v>2.63</v>
+      </c>
+      <c r="V7">
+        <v>3</v>
+      </c>
+      <c r="W7">
+        <v>1.36</v>
+      </c>
+      <c r="X7">
+        <v>9</v>
+      </c>
+      <c r="Y7">
+        <v>1.07</v>
+      </c>
+      <c r="Z7">
+        <v>2.18</v>
+      </c>
+      <c r="AA7">
+        <v>3.21</v>
+      </c>
+      <c r="AB7">
+        <v>3.34</v>
+      </c>
+      <c r="AC7">
+        <v>1.06</v>
+      </c>
+      <c r="AD7">
+        <v>9</v>
+      </c>
+      <c r="AE7">
+        <v>1.33</v>
+      </c>
+      <c r="AF7">
+        <v>3.35</v>
+      </c>
+      <c r="AG7">
+        <v>2</v>
+      </c>
+      <c r="AH7">
+        <v>1.75</v>
+      </c>
+      <c r="AI7">
+        <v>1.8</v>
+      </c>
+      <c r="AJ7">
+        <v>1.95</v>
+      </c>
+      <c r="AK7">
+        <v>1.37</v>
+      </c>
+      <c r="AL7">
+        <v>1.31</v>
+      </c>
+      <c r="AM7">
+        <v>1.58</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>3</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>4</v>
+      </c>
+      <c r="AV7">
+        <v>11</v>
+      </c>
+      <c r="AW7">
+        <v>2</v>
+      </c>
+      <c r="AX7">
+        <v>7</v>
+      </c>
+      <c r="AY7">
+        <v>7</v>
+      </c>
+      <c r="AZ7">
+        <v>18</v>
+      </c>
+      <c r="BA7">
+        <v>5</v>
+      </c>
+      <c r="BB7">
+        <v>5</v>
+      </c>
+      <c r="BC7">
+        <v>10</v>
+      </c>
+      <c r="BD7">
+        <v>1.78</v>
+      </c>
+      <c r="BE7">
+        <v>6.75</v>
+      </c>
+      <c r="BF7">
+        <v>2.2</v>
+      </c>
+      <c r="BG7">
+        <v>1.24</v>
+      </c>
+      <c r="BH7">
+        <v>3.65</v>
+      </c>
+      <c r="BI7">
+        <v>1.41</v>
+      </c>
+      <c r="BJ7">
+        <v>2.65</v>
+      </c>
+      <c r="BK7">
+        <v>1.68</v>
+      </c>
+      <c r="BL7">
+        <v>2.05</v>
+      </c>
+      <c r="BM7">
+        <v>2.05</v>
+      </c>
+      <c r="BN7">
+        <v>1.68</v>
+      </c>
+      <c r="BO7">
+        <v>2.55</v>
+      </c>
+      <c r="BP7">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="98">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -244,6 +244,12 @@
     <t>Halmstad</t>
   </si>
   <si>
+    <t>Värnamo</t>
+  </si>
+  <si>
+    <t>GAIS</t>
+  </si>
+  <si>
     <t>Malmö FF</t>
   </si>
   <si>
@@ -262,6 +268,12 @@
     <t>Degerfors</t>
   </si>
   <si>
+    <t>Sirius</t>
+  </si>
+  <si>
+    <t>AIK</t>
+  </si>
+  <si>
     <t>[]</t>
   </si>
   <si>
@@ -277,6 +289,9 @@
     <t>['17', '19', '50', '65']</t>
   </si>
   <si>
+    <t>['50']</t>
+  </si>
+  <si>
     <t>['45+8']</t>
   </si>
   <si>
@@ -287,6 +302,12 @@
   </si>
   <si>
     <t>['45+1', '55', '74', '83', '90+3']</t>
+  </si>
+  <si>
+    <t>['61', '85']</t>
+  </si>
+  <si>
+    <t>['90+2']</t>
   </si>
 </sst>
 </file>
@@ -648,7 +669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP7"/>
+  <dimension ref="A1:BP9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -880,7 +901,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -901,10 +922,10 @@
         <v>1</v>
       </c>
       <c r="O2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="Q2">
         <v>3.5</v>
@@ -1086,7 +1107,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1107,10 +1128,10 @@
         <v>2</v>
       </c>
       <c r="O3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="P3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="Q3">
         <v>2.05</v>
@@ -1292,7 +1313,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I4">
         <v>2</v>
@@ -1313,10 +1334,10 @@
         <v>4</v>
       </c>
       <c r="O4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="Q4">
         <v>2.4</v>
@@ -1498,7 +1519,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1519,10 +1540,10 @@
         <v>4</v>
       </c>
       <c r="O5" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="Q5">
         <v>2.5</v>
@@ -1704,7 +1725,7 @@
         <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I6">
         <v>2</v>
@@ -1725,10 +1746,10 @@
         <v>7</v>
       </c>
       <c r="O6" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="Q6">
         <v>2.6</v>
@@ -1910,7 +1931,7 @@
         <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1931,10 +1952,10 @@
         <v>5</v>
       </c>
       <c r="O7" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -2091,6 +2112,418 @@
       </c>
       <c r="BP7">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:68">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>7778959</v>
+      </c>
+      <c r="C8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="2">
+        <v>45747.58333333334</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H8" t="s">
+        <v>84</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>2</v>
+      </c>
+      <c r="N8">
+        <v>3</v>
+      </c>
+      <c r="O8" t="s">
+        <v>91</v>
+      </c>
+      <c r="P8" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q8">
+        <v>3.2</v>
+      </c>
+      <c r="R8">
+        <v>2.1</v>
+      </c>
+      <c r="S8">
+        <v>3.4</v>
+      </c>
+      <c r="T8">
+        <v>1.4</v>
+      </c>
+      <c r="U8">
+        <v>2.75</v>
+      </c>
+      <c r="V8">
+        <v>3</v>
+      </c>
+      <c r="W8">
+        <v>1.36</v>
+      </c>
+      <c r="X8">
+        <v>8</v>
+      </c>
+      <c r="Y8">
+        <v>1.08</v>
+      </c>
+      <c r="Z8">
+        <v>2.55</v>
+      </c>
+      <c r="AA8">
+        <v>3.28</v>
+      </c>
+      <c r="AB8">
+        <v>2.68</v>
+      </c>
+      <c r="AC8">
+        <v>1.06</v>
+      </c>
+      <c r="AD8">
+        <v>9</v>
+      </c>
+      <c r="AE8">
+        <v>1.3</v>
+      </c>
+      <c r="AF8">
+        <v>3.45</v>
+      </c>
+      <c r="AG8">
+        <v>1.92</v>
+      </c>
+      <c r="AH8">
+        <v>1.82</v>
+      </c>
+      <c r="AI8">
+        <v>1.75</v>
+      </c>
+      <c r="AJ8">
+        <v>2</v>
+      </c>
+      <c r="AK8">
+        <v>1.42</v>
+      </c>
+      <c r="AL8">
+        <v>1.31</v>
+      </c>
+      <c r="AM8">
+        <v>1.52</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <v>3</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>6</v>
+      </c>
+      <c r="AV8">
+        <v>4</v>
+      </c>
+      <c r="AW8">
+        <v>8</v>
+      </c>
+      <c r="AX8">
+        <v>3</v>
+      </c>
+      <c r="AY8">
+        <v>15</v>
+      </c>
+      <c r="AZ8">
+        <v>7</v>
+      </c>
+      <c r="BA8">
+        <v>4</v>
+      </c>
+      <c r="BB8">
+        <v>3</v>
+      </c>
+      <c r="BC8">
+        <v>7</v>
+      </c>
+      <c r="BD8">
+        <v>1.98</v>
+      </c>
+      <c r="BE8">
+        <v>6.75</v>
+      </c>
+      <c r="BF8">
+        <v>1.95</v>
+      </c>
+      <c r="BG8">
+        <v>1.14</v>
+      </c>
+      <c r="BH8">
+        <v>4.8</v>
+      </c>
+      <c r="BI8">
+        <v>1.25</v>
+      </c>
+      <c r="BJ8">
+        <v>3.45</v>
+      </c>
+      <c r="BK8">
+        <v>1.43</v>
+      </c>
+      <c r="BL8">
+        <v>2.55</v>
+      </c>
+      <c r="BM8">
+        <v>1.68</v>
+      </c>
+      <c r="BN8">
+        <v>2.05</v>
+      </c>
+      <c r="BO8">
+        <v>2.02</v>
+      </c>
+      <c r="BP8">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:68">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>7778955</v>
+      </c>
+      <c r="C9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="2">
+        <v>45747.59027777778</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>77</v>
+      </c>
+      <c r="H9" t="s">
+        <v>85</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9" t="s">
+        <v>86</v>
+      </c>
+      <c r="P9" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q9">
+        <v>3.4</v>
+      </c>
+      <c r="R9">
+        <v>2.05</v>
+      </c>
+      <c r="S9">
+        <v>3.4</v>
+      </c>
+      <c r="T9">
+        <v>1.44</v>
+      </c>
+      <c r="U9">
+        <v>2.63</v>
+      </c>
+      <c r="V9">
+        <v>3.4</v>
+      </c>
+      <c r="W9">
+        <v>1.3</v>
+      </c>
+      <c r="X9">
+        <v>10</v>
+      </c>
+      <c r="Y9">
+        <v>1.06</v>
+      </c>
+      <c r="Z9">
+        <v>2.62</v>
+      </c>
+      <c r="AA9">
+        <v>3.14</v>
+      </c>
+      <c r="AB9">
+        <v>2.71</v>
+      </c>
+      <c r="AC9">
+        <v>1.08</v>
+      </c>
+      <c r="AD9">
+        <v>8</v>
+      </c>
+      <c r="AE9">
+        <v>1.4</v>
+      </c>
+      <c r="AF9">
+        <v>3</v>
+      </c>
+      <c r="AG9">
+        <v>1.91</v>
+      </c>
+      <c r="AH9">
+        <v>1.75</v>
+      </c>
+      <c r="AI9">
+        <v>1.91</v>
+      </c>
+      <c r="AJ9">
+        <v>1.91</v>
+      </c>
+      <c r="AK9">
+        <v>1.44</v>
+      </c>
+      <c r="AL9">
+        <v>1.32</v>
+      </c>
+      <c r="AM9">
+        <v>1.49</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>0</v>
+      </c>
+      <c r="AQ9">
+        <v>3</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <v>3</v>
+      </c>
+      <c r="AV9">
+        <v>2</v>
+      </c>
+      <c r="AW9">
+        <v>10</v>
+      </c>
+      <c r="AX9">
+        <v>6</v>
+      </c>
+      <c r="AY9">
+        <v>14</v>
+      </c>
+      <c r="AZ9">
+        <v>10</v>
+      </c>
+      <c r="BA9">
+        <v>4</v>
+      </c>
+      <c r="BB9">
+        <v>3</v>
+      </c>
+      <c r="BC9">
+        <v>7</v>
+      </c>
+      <c r="BD9">
+        <v>1.76</v>
+      </c>
+      <c r="BE9">
+        <v>7</v>
+      </c>
+      <c r="BF9">
+        <v>2.23</v>
+      </c>
+      <c r="BG9">
+        <v>1.2</v>
+      </c>
+      <c r="BH9">
+        <v>4</v>
+      </c>
+      <c r="BI9">
+        <v>1.34</v>
+      </c>
+      <c r="BJ9">
+        <v>2.9</v>
+      </c>
+      <c r="BK9">
+        <v>1.56</v>
+      </c>
+      <c r="BL9">
+        <v>2.23</v>
+      </c>
+      <c r="BM9">
+        <v>1.88</v>
+      </c>
+      <c r="BN9">
+        <v>1.81</v>
+      </c>
+      <c r="BO9">
+        <v>2.32</v>
+      </c>
+      <c r="BP9">
+        <v>1.52</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
@@ -2481,10 +2481,10 @@
         <v>4</v>
       </c>
       <c r="BB9">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BC9">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="BD9">
         <v>1.76</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="101">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -250,27 +250,27 @@
     <t>GAIS</t>
   </si>
   <si>
+    <t>IFK Göteborg</t>
+  </si>
+  <si>
+    <t>Sirius</t>
+  </si>
+  <si>
+    <t>Öster</t>
+  </si>
+  <si>
     <t>Malmö FF</t>
   </si>
   <si>
     <t>Brommapojkarna</t>
   </si>
   <si>
-    <t>IFK Göteborg</t>
-  </si>
-  <si>
     <t>Mjällby</t>
   </si>
   <si>
-    <t>Öster</t>
-  </si>
-  <si>
     <t>Degerfors</t>
   </si>
   <si>
-    <t>Sirius</t>
-  </si>
-  <si>
     <t>AIK</t>
   </si>
   <si>
@@ -292,6 +292,12 @@
     <t>['50']</t>
   </si>
   <si>
+    <t>['54']</t>
+  </si>
+  <si>
+    <t>['35', '57']</t>
+  </si>
+  <si>
     <t>['45+8']</t>
   </si>
   <si>
@@ -308,6 +314,9 @@
   </si>
   <si>
     <t>['90+2']</t>
+  </si>
+  <si>
+    <t>['51']</t>
   </si>
 </sst>
 </file>
@@ -669,7 +678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP9"/>
+  <dimension ref="A1:BP12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -901,7 +910,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -925,7 +934,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="Q2">
         <v>3.5</v>
@@ -1107,7 +1116,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1313,7 +1322,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I4">
         <v>2</v>
@@ -1519,7 +1528,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1543,7 +1552,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="Q5">
         <v>2.5</v>
@@ -1725,7 +1734,7 @@
         <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I6">
         <v>2</v>
@@ -1749,7 +1758,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="Q6">
         <v>2.6</v>
@@ -1931,7 +1940,7 @@
         <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1955,7 +1964,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -2137,7 +2146,7 @@
         <v>76</v>
       </c>
       <c r="H8" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -2161,7 +2170,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -2367,7 +2376,7 @@
         <v>86</v>
       </c>
       <c r="P9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -2524,6 +2533,624 @@
       </c>
       <c r="BP9">
         <v>1.52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:68">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>7778962</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="2">
+        <v>45752.41666666666</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H10" t="s">
+        <v>75</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10" t="s">
+        <v>92</v>
+      </c>
+      <c r="P10" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q10">
+        <v>2</v>
+      </c>
+      <c r="R10">
+        <v>2.38</v>
+      </c>
+      <c r="S10">
+        <v>6</v>
+      </c>
+      <c r="T10">
+        <v>1.33</v>
+      </c>
+      <c r="U10">
+        <v>3.25</v>
+      </c>
+      <c r="V10">
+        <v>2.63</v>
+      </c>
+      <c r="W10">
+        <v>1.44</v>
+      </c>
+      <c r="X10">
+        <v>7</v>
+      </c>
+      <c r="Y10">
+        <v>1.1</v>
+      </c>
+      <c r="Z10">
+        <v>1.52</v>
+      </c>
+      <c r="AA10">
+        <v>4.2</v>
+      </c>
+      <c r="AB10">
+        <v>5.7</v>
+      </c>
+      <c r="AC10">
+        <v>1.05</v>
+      </c>
+      <c r="AD10">
+        <v>10</v>
+      </c>
+      <c r="AE10">
+        <v>1.3</v>
+      </c>
+      <c r="AF10">
+        <v>3.65</v>
+      </c>
+      <c r="AG10">
+        <v>1.73</v>
+      </c>
+      <c r="AH10">
+        <v>1.91</v>
+      </c>
+      <c r="AI10">
+        <v>1.95</v>
+      </c>
+      <c r="AJ10">
+        <v>1.8</v>
+      </c>
+      <c r="AK10">
+        <v>1.11</v>
+      </c>
+      <c r="AL10">
+        <v>1.18</v>
+      </c>
+      <c r="AM10">
+        <v>2.45</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>3</v>
+      </c>
+      <c r="AQ10">
+        <v>0</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <v>4</v>
+      </c>
+      <c r="AV10">
+        <v>2</v>
+      </c>
+      <c r="AW10">
+        <v>8</v>
+      </c>
+      <c r="AX10">
+        <v>1</v>
+      </c>
+      <c r="AY10">
+        <v>12</v>
+      </c>
+      <c r="AZ10">
+        <v>3</v>
+      </c>
+      <c r="BA10">
+        <v>2</v>
+      </c>
+      <c r="BB10">
+        <v>1</v>
+      </c>
+      <c r="BC10">
+        <v>3</v>
+      </c>
+      <c r="BD10">
+        <v>1.33</v>
+      </c>
+      <c r="BE10">
+        <v>10.25</v>
+      </c>
+      <c r="BF10">
+        <v>4.1</v>
+      </c>
+      <c r="BG10">
+        <v>1.12</v>
+      </c>
+      <c r="BH10">
+        <v>4.7</v>
+      </c>
+      <c r="BI10">
+        <v>1.27</v>
+      </c>
+      <c r="BJ10">
+        <v>3.14</v>
+      </c>
+      <c r="BK10">
+        <v>1.5</v>
+      </c>
+      <c r="BL10">
+        <v>2.35</v>
+      </c>
+      <c r="BM10">
+        <v>1.85</v>
+      </c>
+      <c r="BN10">
+        <v>1.85</v>
+      </c>
+      <c r="BO10">
+        <v>2.34</v>
+      </c>
+      <c r="BP10">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:68">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>7778966</v>
+      </c>
+      <c r="C11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="2">
+        <v>45752.41666666666</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H11" t="s">
+        <v>70</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11" t="s">
+        <v>86</v>
+      </c>
+      <c r="P11" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q11">
+        <v>4</v>
+      </c>
+      <c r="R11">
+        <v>2.2</v>
+      </c>
+      <c r="S11">
+        <v>2.6</v>
+      </c>
+      <c r="T11">
+        <v>1.36</v>
+      </c>
+      <c r="U11">
+        <v>3</v>
+      </c>
+      <c r="V11">
+        <v>2.75</v>
+      </c>
+      <c r="W11">
+        <v>1.4</v>
+      </c>
+      <c r="X11">
+        <v>7</v>
+      </c>
+      <c r="Y11">
+        <v>1.1</v>
+      </c>
+      <c r="Z11">
+        <v>3.04</v>
+      </c>
+      <c r="AA11">
+        <v>3.45</v>
+      </c>
+      <c r="AB11">
+        <v>2.22</v>
+      </c>
+      <c r="AC11">
+        <v>1.03</v>
+      </c>
+      <c r="AD11">
+        <v>13</v>
+      </c>
+      <c r="AE11">
+        <v>1.25</v>
+      </c>
+      <c r="AF11">
+        <v>3.9</v>
+      </c>
+      <c r="AG11">
+        <v>1.8</v>
+      </c>
+      <c r="AH11">
+        <v>1.94</v>
+      </c>
+      <c r="AI11">
+        <v>1.7</v>
+      </c>
+      <c r="AJ11">
+        <v>2.05</v>
+      </c>
+      <c r="AK11">
+        <v>1.77</v>
+      </c>
+      <c r="AL11">
+        <v>1.25</v>
+      </c>
+      <c r="AM11">
+        <v>1.28</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <v>0</v>
+      </c>
+      <c r="AQ11">
+        <v>3</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AU11">
+        <v>3</v>
+      </c>
+      <c r="AV11">
+        <v>8</v>
+      </c>
+      <c r="AW11">
+        <v>8</v>
+      </c>
+      <c r="AX11">
+        <v>10</v>
+      </c>
+      <c r="AY11">
+        <v>11</v>
+      </c>
+      <c r="AZ11">
+        <v>23</v>
+      </c>
+      <c r="BA11">
+        <v>1</v>
+      </c>
+      <c r="BB11">
+        <v>1</v>
+      </c>
+      <c r="BC11">
+        <v>2</v>
+      </c>
+      <c r="BD11">
+        <v>2.73</v>
+      </c>
+      <c r="BE11">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF11">
+        <v>1.63</v>
+      </c>
+      <c r="BG11">
+        <v>1.21</v>
+      </c>
+      <c r="BH11">
+        <v>3.58</v>
+      </c>
+      <c r="BI11">
+        <v>1.41</v>
+      </c>
+      <c r="BJ11">
+        <v>2.6</v>
+      </c>
+      <c r="BK11">
+        <v>1.77</v>
+      </c>
+      <c r="BL11">
+        <v>1.95</v>
+      </c>
+      <c r="BM11">
+        <v>2.19</v>
+      </c>
+      <c r="BN11">
+        <v>1.57</v>
+      </c>
+      <c r="BO11">
+        <v>2.88</v>
+      </c>
+      <c r="BP11">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:68">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>7778963</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="2">
+        <v>45752.52083333334</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12" t="s">
+        <v>80</v>
+      </c>
+      <c r="H12" t="s">
+        <v>71</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>2</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>2</v>
+      </c>
+      <c r="O12" t="s">
+        <v>93</v>
+      </c>
+      <c r="P12" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q12">
+        <v>4</v>
+      </c>
+      <c r="R12">
+        <v>2.38</v>
+      </c>
+      <c r="S12">
+        <v>2.5</v>
+      </c>
+      <c r="T12">
+        <v>1.3</v>
+      </c>
+      <c r="U12">
+        <v>3.4</v>
+      </c>
+      <c r="V12">
+        <v>2.5</v>
+      </c>
+      <c r="W12">
+        <v>1.5</v>
+      </c>
+      <c r="X12">
+        <v>6</v>
+      </c>
+      <c r="Y12">
+        <v>1.13</v>
+      </c>
+      <c r="Z12">
+        <v>3.2</v>
+      </c>
+      <c r="AA12">
+        <v>3.85</v>
+      </c>
+      <c r="AB12">
+        <v>2.01</v>
+      </c>
+      <c r="AC12">
+        <v>1.04</v>
+      </c>
+      <c r="AD12">
+        <v>11</v>
+      </c>
+      <c r="AE12">
+        <v>1.2</v>
+      </c>
+      <c r="AF12">
+        <v>4.83</v>
+      </c>
+      <c r="AG12">
+        <v>1.57</v>
+      </c>
+      <c r="AH12">
+        <v>2.15</v>
+      </c>
+      <c r="AI12">
+        <v>1.57</v>
+      </c>
+      <c r="AJ12">
+        <v>2.25</v>
+      </c>
+      <c r="AK12">
+        <v>1.85</v>
+      </c>
+      <c r="AL12">
+        <v>1.2</v>
+      </c>
+      <c r="AM12">
+        <v>1.25</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>3</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>-1</v>
+      </c>
+      <c r="AV12">
+        <v>-1</v>
+      </c>
+      <c r="AW12">
+        <v>-1</v>
+      </c>
+      <c r="AX12">
+        <v>-1</v>
+      </c>
+      <c r="AY12">
+        <v>-1</v>
+      </c>
+      <c r="AZ12">
+        <v>-1</v>
+      </c>
+      <c r="BA12">
+        <v>-1</v>
+      </c>
+      <c r="BB12">
+        <v>-1</v>
+      </c>
+      <c r="BC12">
+        <v>-1</v>
+      </c>
+      <c r="BD12">
+        <v>2.41</v>
+      </c>
+      <c r="BE12">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="BF12">
+        <v>1.75</v>
+      </c>
+      <c r="BG12">
+        <v>1.08</v>
+      </c>
+      <c r="BH12">
+        <v>5.45</v>
+      </c>
+      <c r="BI12">
+        <v>1.2</v>
+      </c>
+      <c r="BJ12">
+        <v>3.68</v>
+      </c>
+      <c r="BK12">
+        <v>1.4</v>
+      </c>
+      <c r="BL12">
+        <v>2.64</v>
+      </c>
+      <c r="BM12">
+        <v>1.7</v>
+      </c>
+      <c r="BN12">
+        <v>2.05</v>
+      </c>
+      <c r="BO12">
+        <v>2.1</v>
+      </c>
+      <c r="BP12">
+        <v>1.62</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="103">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -259,6 +259,9 @@
     <t>Öster</t>
   </si>
   <si>
+    <t>AIK</t>
+  </si>
+  <si>
     <t>Malmö FF</t>
   </si>
   <si>
@@ -271,9 +274,6 @@
     <t>Degerfors</t>
   </si>
   <si>
-    <t>AIK</t>
-  </si>
-  <si>
     <t>[]</t>
   </si>
   <si>
@@ -298,6 +298,9 @@
     <t>['35', '57']</t>
   </si>
   <si>
+    <t>['59', '74', '84', '90']</t>
+  </si>
+  <si>
     <t>['45+8']</t>
   </si>
   <si>
@@ -317,6 +320,9 @@
   </si>
   <si>
     <t>['51']</t>
+  </si>
+  <si>
+    <t>['25', '62', '71']</t>
   </si>
 </sst>
 </file>
@@ -678,7 +684,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP12"/>
+  <dimension ref="A1:BP13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -910,7 +916,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -934,7 +940,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q2">
         <v>3.5</v>
@@ -1116,7 +1122,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1528,7 +1534,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1552,7 +1558,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q5">
         <v>2.5</v>
@@ -1758,7 +1764,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q6">
         <v>2.6</v>
@@ -1940,7 +1946,7 @@
         <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1964,7 +1970,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -2170,7 +2176,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -2352,7 +2358,7 @@
         <v>77</v>
       </c>
       <c r="H9" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -2376,7 +2382,7 @@
         <v>86</v>
       </c>
       <c r="P9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -2693,13 +2699,13 @@
         <v>3</v>
       </c>
       <c r="BA10">
+        <v>4</v>
+      </c>
+      <c r="BB10">
         <v>2</v>
       </c>
-      <c r="BB10">
-        <v>1</v>
-      </c>
       <c r="BC10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BD10">
         <v>1.33</v>
@@ -2788,7 +2794,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q11">
         <v>4</v>
@@ -2899,13 +2905,13 @@
         <v>23</v>
       </c>
       <c r="BA11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BB11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BC11">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BD11">
         <v>2.73</v>
@@ -3087,31 +3093,31 @@
         <v>0</v>
       </c>
       <c r="AU12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AV12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AW12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AX12">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AY12">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AZ12">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="BA12">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BB12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="BC12">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="BD12">
         <v>2.41</v>
@@ -3151,6 +3157,212 @@
       </c>
       <c r="BP12">
         <v>1.62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:68">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>7778960</v>
+      </c>
+      <c r="C13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" s="2">
+        <v>45753.375</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H13" t="s">
+        <v>74</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>4</v>
+      </c>
+      <c r="M13">
+        <v>3</v>
+      </c>
+      <c r="N13">
+        <v>7</v>
+      </c>
+      <c r="O13" t="s">
+        <v>94</v>
+      </c>
+      <c r="P13" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q13">
+        <v>2.45</v>
+      </c>
+      <c r="R13">
+        <v>2.05</v>
+      </c>
+      <c r="S13">
+        <v>4.33</v>
+      </c>
+      <c r="T13">
+        <v>1.41</v>
+      </c>
+      <c r="U13">
+        <v>2.65</v>
+      </c>
+      <c r="V13">
+        <v>2.85</v>
+      </c>
+      <c r="W13">
+        <v>1.37</v>
+      </c>
+      <c r="X13">
+        <v>7.5</v>
+      </c>
+      <c r="Y13">
+        <v>1.08</v>
+      </c>
+      <c r="Z13">
+        <v>1.63</v>
+      </c>
+      <c r="AA13">
+        <v>3.97</v>
+      </c>
+      <c r="AB13">
+        <v>4.9</v>
+      </c>
+      <c r="AC13">
+        <v>1.07</v>
+      </c>
+      <c r="AD13">
+        <v>8.5</v>
+      </c>
+      <c r="AE13">
+        <v>1.36</v>
+      </c>
+      <c r="AF13">
+        <v>3.2</v>
+      </c>
+      <c r="AG13">
+        <v>1.89</v>
+      </c>
+      <c r="AH13">
+        <v>1.85</v>
+      </c>
+      <c r="AI13">
+        <v>1.85</v>
+      </c>
+      <c r="AJ13">
+        <v>1.82</v>
+      </c>
+      <c r="AK13">
+        <v>1.23</v>
+      </c>
+      <c r="AL13">
+        <v>1.29</v>
+      </c>
+      <c r="AM13">
+        <v>1.87</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>3</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <v>6</v>
+      </c>
+      <c r="AV13">
+        <v>6</v>
+      </c>
+      <c r="AW13">
+        <v>10</v>
+      </c>
+      <c r="AX13">
+        <v>7</v>
+      </c>
+      <c r="AY13">
+        <v>16</v>
+      </c>
+      <c r="AZ13">
+        <v>13</v>
+      </c>
+      <c r="BA13">
+        <v>4</v>
+      </c>
+      <c r="BB13">
+        <v>2</v>
+      </c>
+      <c r="BC13">
+        <v>6</v>
+      </c>
+      <c r="BD13">
+        <v>1.58</v>
+      </c>
+      <c r="BE13">
+        <v>6.5</v>
+      </c>
+      <c r="BF13">
+        <v>2.65</v>
+      </c>
+      <c r="BG13">
+        <v>1.3</v>
+      </c>
+      <c r="BH13">
+        <v>3.05</v>
+      </c>
+      <c r="BI13">
+        <v>1.53</v>
+      </c>
+      <c r="BJ13">
+        <v>2.32</v>
+      </c>
+      <c r="BK13">
+        <v>1.85</v>
+      </c>
+      <c r="BL13">
+        <v>1.83</v>
+      </c>
+      <c r="BM13">
+        <v>2.32</v>
+      </c>
+      <c r="BN13">
+        <v>1.53</v>
+      </c>
+      <c r="BO13">
+        <v>2.95</v>
+      </c>
+      <c r="BP13">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="109">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -262,18 +262,18 @@
     <t>AIK</t>
   </si>
   <si>
+    <t>Brommapojkarna</t>
+  </si>
+  <si>
+    <t>Degerfors</t>
+  </si>
+  <si>
+    <t>Mjällby</t>
+  </si>
+  <si>
     <t>Malmö FF</t>
   </si>
   <si>
-    <t>Brommapojkarna</t>
-  </si>
-  <si>
-    <t>Mjällby</t>
-  </si>
-  <si>
-    <t>Degerfors</t>
-  </si>
-  <si>
     <t>[]</t>
   </si>
   <si>
@@ -301,6 +301,15 @@
     <t>['59', '74', '84', '90']</t>
   </si>
   <si>
+    <t>['5']</t>
+  </si>
+  <si>
+    <t>['90+6']</t>
+  </si>
+  <si>
+    <t>['47', '78']</t>
+  </si>
+  <si>
     <t>['45+8']</t>
   </si>
   <si>
@@ -323,6 +332,15 @@
   </si>
   <si>
     <t>['25', '62', '71']</t>
+  </si>
+  <si>
+    <t>['55', '90+2']</t>
+  </si>
+  <si>
+    <t>['90']</t>
+  </si>
+  <si>
+    <t>['71']</t>
   </si>
 </sst>
 </file>
@@ -684,7 +702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP13"/>
+  <dimension ref="A1:BP17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -916,7 +934,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -940,7 +958,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Q2">
         <v>3.5</v>
@@ -1122,7 +1140,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1558,7 +1576,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="Q5">
         <v>2.5</v>
@@ -1764,7 +1782,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="Q6">
         <v>2.6</v>
@@ -1946,7 +1964,7 @@
         <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1970,7 +1988,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -2176,7 +2194,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -2382,7 +2400,7 @@
         <v>86</v>
       </c>
       <c r="P9" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -2794,7 +2812,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="Q11">
         <v>4</v>
@@ -3206,7 +3224,7 @@
         <v>94</v>
       </c>
       <c r="P13" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -3363,6 +3381,830 @@
       </c>
       <c r="BP13">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:68">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>7778961</v>
+      </c>
+      <c r="C14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="2">
+        <v>45753.375</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14" t="s">
+        <v>82</v>
+      </c>
+      <c r="H14" t="s">
+        <v>72</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>2</v>
+      </c>
+      <c r="N14">
+        <v>2</v>
+      </c>
+      <c r="O14" t="s">
+        <v>86</v>
+      </c>
+      <c r="P14" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q14">
+        <v>4</v>
+      </c>
+      <c r="R14">
+        <v>2.25</v>
+      </c>
+      <c r="S14">
+        <v>2.35</v>
+      </c>
+      <c r="T14">
+        <v>1.3</v>
+      </c>
+      <c r="U14">
+        <v>3.2</v>
+      </c>
+      <c r="V14">
+        <v>2.38</v>
+      </c>
+      <c r="W14">
+        <v>1.53</v>
+      </c>
+      <c r="X14">
+        <v>5.65</v>
+      </c>
+      <c r="Y14">
+        <v>1.08</v>
+      </c>
+      <c r="Z14">
+        <v>4.2</v>
+      </c>
+      <c r="AA14">
+        <v>3.71</v>
+      </c>
+      <c r="AB14">
+        <v>1.78</v>
+      </c>
+      <c r="AC14">
+        <v>1.04</v>
+      </c>
+      <c r="AD14">
+        <v>11</v>
+      </c>
+      <c r="AE14">
+        <v>1.22</v>
+      </c>
+      <c r="AF14">
+        <v>4.33</v>
+      </c>
+      <c r="AG14">
+        <v>1.61</v>
+      </c>
+      <c r="AH14">
+        <v>2.05</v>
+      </c>
+      <c r="AI14">
+        <v>1.55</v>
+      </c>
+      <c r="AJ14">
+        <v>2.25</v>
+      </c>
+      <c r="AK14">
+        <v>1.91</v>
+      </c>
+      <c r="AL14">
+        <v>1.22</v>
+      </c>
+      <c r="AM14">
+        <v>1.25</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>0</v>
+      </c>
+      <c r="AQ14">
+        <v>3</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>0</v>
+      </c>
+      <c r="AU14">
+        <v>6</v>
+      </c>
+      <c r="AV14">
+        <v>8</v>
+      </c>
+      <c r="AW14">
+        <v>6</v>
+      </c>
+      <c r="AX14">
+        <v>12</v>
+      </c>
+      <c r="AY14">
+        <v>16</v>
+      </c>
+      <c r="AZ14">
+        <v>26</v>
+      </c>
+      <c r="BA14">
+        <v>5</v>
+      </c>
+      <c r="BB14">
+        <v>6</v>
+      </c>
+      <c r="BC14">
+        <v>11</v>
+      </c>
+      <c r="BD14">
+        <v>2.8</v>
+      </c>
+      <c r="BE14">
+        <v>7.5</v>
+      </c>
+      <c r="BF14">
+        <v>1.49</v>
+      </c>
+      <c r="BG14">
+        <v>1.17</v>
+      </c>
+      <c r="BH14">
+        <v>4.35</v>
+      </c>
+      <c r="BI14">
+        <v>1.3</v>
+      </c>
+      <c r="BJ14">
+        <v>3.15</v>
+      </c>
+      <c r="BK14">
+        <v>1.5</v>
+      </c>
+      <c r="BL14">
+        <v>2.38</v>
+      </c>
+      <c r="BM14">
+        <v>1.79</v>
+      </c>
+      <c r="BN14">
+        <v>1.9</v>
+      </c>
+      <c r="BO14">
+        <v>2.23</v>
+      </c>
+      <c r="BP14">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="15" spans="1:68">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>7778967</v>
+      </c>
+      <c r="C15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="2">
+        <v>45753.47916666666</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15" t="s">
+        <v>83</v>
+      </c>
+      <c r="H15" t="s">
+        <v>76</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15" t="s">
+        <v>95</v>
+      </c>
+      <c r="P15" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q15">
+        <v>2.7</v>
+      </c>
+      <c r="R15">
+        <v>2.1</v>
+      </c>
+      <c r="S15">
+        <v>3.6</v>
+      </c>
+      <c r="T15">
+        <v>1.39</v>
+      </c>
+      <c r="U15">
+        <v>2.75</v>
+      </c>
+      <c r="V15">
+        <v>2.8</v>
+      </c>
+      <c r="W15">
+        <v>1.38</v>
+      </c>
+      <c r="X15">
+        <v>7.25</v>
+      </c>
+      <c r="Y15">
+        <v>1.08</v>
+      </c>
+      <c r="Z15">
+        <v>1.89</v>
+      </c>
+      <c r="AA15">
+        <v>3.55</v>
+      </c>
+      <c r="AB15">
+        <v>3.86</v>
+      </c>
+      <c r="AC15">
+        <v>1.06</v>
+      </c>
+      <c r="AD15">
+        <v>9</v>
+      </c>
+      <c r="AE15">
+        <v>1.33</v>
+      </c>
+      <c r="AF15">
+        <v>3.35</v>
+      </c>
+      <c r="AG15">
+        <v>1.77</v>
+      </c>
+      <c r="AH15">
+        <v>1.98</v>
+      </c>
+      <c r="AI15">
+        <v>1.77</v>
+      </c>
+      <c r="AJ15">
+        <v>1.93</v>
+      </c>
+      <c r="AK15">
+        <v>1.33</v>
+      </c>
+      <c r="AL15">
+        <v>1.29</v>
+      </c>
+      <c r="AM15">
+        <v>1.66</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <v>3</v>
+      </c>
+      <c r="AQ15">
+        <v>0</v>
+      </c>
+      <c r="AR15">
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <v>0</v>
+      </c>
+      <c r="AU15">
+        <v>5</v>
+      </c>
+      <c r="AV15">
+        <v>4</v>
+      </c>
+      <c r="AW15">
+        <v>3</v>
+      </c>
+      <c r="AX15">
+        <v>12</v>
+      </c>
+      <c r="AY15">
+        <v>8</v>
+      </c>
+      <c r="AZ15">
+        <v>17</v>
+      </c>
+      <c r="BA15">
+        <v>2</v>
+      </c>
+      <c r="BB15">
+        <v>7</v>
+      </c>
+      <c r="BC15">
+        <v>9</v>
+      </c>
+      <c r="BD15">
+        <v>1.7</v>
+      </c>
+      <c r="BE15">
+        <v>7</v>
+      </c>
+      <c r="BF15">
+        <v>2.35</v>
+      </c>
+      <c r="BG15">
+        <v>1.17</v>
+      </c>
+      <c r="BH15">
+        <v>4.3</v>
+      </c>
+      <c r="BI15">
+        <v>1.3</v>
+      </c>
+      <c r="BJ15">
+        <v>3.05</v>
+      </c>
+      <c r="BK15">
+        <v>1.5</v>
+      </c>
+      <c r="BL15">
+        <v>2.35</v>
+      </c>
+      <c r="BM15">
+        <v>1.81</v>
+      </c>
+      <c r="BN15">
+        <v>1.88</v>
+      </c>
+      <c r="BO15">
+        <v>2.2</v>
+      </c>
+      <c r="BP15">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:68">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>7778965</v>
+      </c>
+      <c r="C16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="2">
+        <v>45753.47916666666</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16" t="s">
+        <v>84</v>
+      </c>
+      <c r="H16" t="s">
+        <v>77</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>2</v>
+      </c>
+      <c r="O16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P16" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q16">
+        <v>2.55</v>
+      </c>
+      <c r="R16">
+        <v>2.05</v>
+      </c>
+      <c r="S16">
+        <v>4.1</v>
+      </c>
+      <c r="T16">
+        <v>1.43</v>
+      </c>
+      <c r="U16">
+        <v>2.6</v>
+      </c>
+      <c r="V16">
+        <v>2.95</v>
+      </c>
+      <c r="W16">
+        <v>1.35</v>
+      </c>
+      <c r="X16">
+        <v>7.75</v>
+      </c>
+      <c r="Y16">
+        <v>1.07</v>
+      </c>
+      <c r="Z16">
+        <v>2.22</v>
+      </c>
+      <c r="AA16">
+        <v>3.45</v>
+      </c>
+      <c r="AB16">
+        <v>3.04</v>
+      </c>
+      <c r="AC16">
+        <v>1.07</v>
+      </c>
+      <c r="AD16">
+        <v>8.5</v>
+      </c>
+      <c r="AE16">
+        <v>1.38</v>
+      </c>
+      <c r="AF16">
+        <v>3.1</v>
+      </c>
+      <c r="AG16">
+        <v>1.82</v>
+      </c>
+      <c r="AH16">
+        <v>1.92</v>
+      </c>
+      <c r="AI16">
+        <v>1.88</v>
+      </c>
+      <c r="AJ16">
+        <v>1.8</v>
+      </c>
+      <c r="AK16">
+        <v>1.25</v>
+      </c>
+      <c r="AL16">
+        <v>1.3</v>
+      </c>
+      <c r="AM16">
+        <v>1.8</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>1</v>
+      </c>
+      <c r="AQ16">
+        <v>1</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <v>3</v>
+      </c>
+      <c r="AV16">
+        <v>3</v>
+      </c>
+      <c r="AW16">
+        <v>11</v>
+      </c>
+      <c r="AX16">
+        <v>7</v>
+      </c>
+      <c r="AY16">
+        <v>14</v>
+      </c>
+      <c r="AZ16">
+        <v>11</v>
+      </c>
+      <c r="BA16">
+        <v>6</v>
+      </c>
+      <c r="BB16">
+        <v>5</v>
+      </c>
+      <c r="BC16">
+        <v>11</v>
+      </c>
+      <c r="BD16">
+        <v>1.73</v>
+      </c>
+      <c r="BE16">
+        <v>7</v>
+      </c>
+      <c r="BF16">
+        <v>2.3</v>
+      </c>
+      <c r="BG16">
+        <v>1.18</v>
+      </c>
+      <c r="BH16">
+        <v>4.1</v>
+      </c>
+      <c r="BI16">
+        <v>1.32</v>
+      </c>
+      <c r="BJ16">
+        <v>3</v>
+      </c>
+      <c r="BK16">
+        <v>1.54</v>
+      </c>
+      <c r="BL16">
+        <v>2.3</v>
+      </c>
+      <c r="BM16">
+        <v>1.86</v>
+      </c>
+      <c r="BN16">
+        <v>1.82</v>
+      </c>
+      <c r="BO16">
+        <v>2.3</v>
+      </c>
+      <c r="BP16">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:68">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>7778964</v>
+      </c>
+      <c r="C17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" s="2">
+        <v>45754.59027777778</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17" t="s">
+        <v>85</v>
+      </c>
+      <c r="H17" t="s">
+        <v>73</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>2</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>3</v>
+      </c>
+      <c r="O17" t="s">
+        <v>97</v>
+      </c>
+      <c r="P17" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q17">
+        <v>2.3</v>
+      </c>
+      <c r="R17">
+        <v>2.25</v>
+      </c>
+      <c r="S17">
+        <v>5</v>
+      </c>
+      <c r="T17">
+        <v>1.36</v>
+      </c>
+      <c r="U17">
+        <v>3</v>
+      </c>
+      <c r="V17">
+        <v>2.75</v>
+      </c>
+      <c r="W17">
+        <v>1.4</v>
+      </c>
+      <c r="X17">
+        <v>7</v>
+      </c>
+      <c r="Y17">
+        <v>1.1</v>
+      </c>
+      <c r="Z17">
+        <v>1.63</v>
+      </c>
+      <c r="AA17">
+        <v>3.99</v>
+      </c>
+      <c r="AB17">
+        <v>4.9</v>
+      </c>
+      <c r="AC17">
+        <v>1.05</v>
+      </c>
+      <c r="AD17">
+        <v>10</v>
+      </c>
+      <c r="AE17">
+        <v>1.28</v>
+      </c>
+      <c r="AF17">
+        <v>3.8</v>
+      </c>
+      <c r="AG17">
+        <v>1.79</v>
+      </c>
+      <c r="AH17">
+        <v>1.95</v>
+      </c>
+      <c r="AI17">
+        <v>1.8</v>
+      </c>
+      <c r="AJ17">
+        <v>1.95</v>
+      </c>
+      <c r="AK17">
+        <v>1.18</v>
+      </c>
+      <c r="AL17">
+        <v>1.22</v>
+      </c>
+      <c r="AM17">
+        <v>2.05</v>
+      </c>
+      <c r="AN17">
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <v>3</v>
+      </c>
+      <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17">
+        <v>9</v>
+      </c>
+      <c r="AV17">
+        <v>2</v>
+      </c>
+      <c r="AW17">
+        <v>17</v>
+      </c>
+      <c r="AX17">
+        <v>6</v>
+      </c>
+      <c r="AY17">
+        <v>32</v>
+      </c>
+      <c r="AZ17">
+        <v>8</v>
+      </c>
+      <c r="BA17">
+        <v>5</v>
+      </c>
+      <c r="BB17">
+        <v>3</v>
+      </c>
+      <c r="BC17">
+        <v>8</v>
+      </c>
+      <c r="BD17">
+        <v>1.45</v>
+      </c>
+      <c r="BE17">
+        <v>7</v>
+      </c>
+      <c r="BF17">
+        <v>3.05</v>
+      </c>
+      <c r="BG17">
+        <v>1.19</v>
+      </c>
+      <c r="BH17">
+        <v>4.1</v>
+      </c>
+      <c r="BI17">
+        <v>1.33</v>
+      </c>
+      <c r="BJ17">
+        <v>2.95</v>
+      </c>
+      <c r="BK17">
+        <v>1.54</v>
+      </c>
+      <c r="BL17">
+        <v>2.3</v>
+      </c>
+      <c r="BM17">
+        <v>1.85</v>
+      </c>
+      <c r="BN17">
+        <v>1.83</v>
+      </c>
+      <c r="BO17">
+        <v>2.3</v>
+      </c>
+      <c r="BP17">
+        <v>1.54</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
@@ -3750,10 +3750,10 @@
         <v>2</v>
       </c>
       <c r="BB15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BC15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BD15">
         <v>1.7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="209">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -481,6 +481,12 @@
     <t>['7', '34', '65']</t>
   </si>
   <si>
+    <t>['30', '59']</t>
+  </si>
+  <si>
+    <t>['70', '9005']</t>
+  </si>
+  <si>
     <t>['45+8']</t>
   </si>
   <si>
@@ -632,6 +638,9 @@
   </si>
   <si>
     <t>['57']</t>
+  </si>
+  <si>
+    <t>['46', '76']</t>
   </si>
 </sst>
 </file>
@@ -993,7 +1002,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP99"/>
+  <dimension ref="A1:BP101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1249,7 +1258,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q2">
         <v>3.5</v>
@@ -1739,7 +1748,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AQ4">
         <v>2</v>
@@ -1867,7 +1876,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q5">
         <v>2.5</v>
@@ -2073,7 +2082,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q6">
         <v>2.6</v>
@@ -2279,7 +2288,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -2485,7 +2494,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -2566,7 +2575,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ8">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2691,7 +2700,7 @@
         <v>86</v>
       </c>
       <c r="P9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -2978,7 +2987,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ10">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3103,7 +3112,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q11">
         <v>4</v>
@@ -3387,7 +3396,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AQ12">
         <v>1.17</v>
@@ -3515,7 +3524,7 @@
         <v>94</v>
       </c>
       <c r="P13" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -3721,7 +3730,7 @@
         <v>86</v>
       </c>
       <c r="P14" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4133,7 +4142,7 @@
         <v>96</v>
       </c>
       <c r="P16" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q16">
         <v>2.55</v>
@@ -4339,7 +4348,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -4545,7 +4554,7 @@
         <v>86</v>
       </c>
       <c r="P18" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q18">
         <v>2.62</v>
@@ -5035,7 +5044,7 @@
         <v>3</v>
       </c>
       <c r="AP20">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AQ20">
         <v>1.5</v>
@@ -5163,7 +5172,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5575,7 +5584,7 @@
         <v>86</v>
       </c>
       <c r="P23" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q23">
         <v>2.62</v>
@@ -6193,7 +6202,7 @@
         <v>102</v>
       </c>
       <c r="P26" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q26">
         <v>3.2</v>
@@ -6399,7 +6408,7 @@
         <v>103</v>
       </c>
       <c r="P27" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q27">
         <v>1.72</v>
@@ -6480,7 +6489,7 @@
         <v>2</v>
       </c>
       <c r="AQ27">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AR27">
         <v>2.77</v>
@@ -6892,7 +6901,7 @@
         <v>1</v>
       </c>
       <c r="AQ29">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR29">
         <v>1.64</v>
@@ -7095,7 +7104,7 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AQ30">
         <v>1.88</v>
@@ -7223,7 +7232,7 @@
         <v>105</v>
       </c>
       <c r="P31" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7429,7 +7438,7 @@
         <v>106</v>
       </c>
       <c r="P32" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q32">
         <v>2.88</v>
@@ -7919,7 +7928,7 @@
         <v>2</v>
       </c>
       <c r="AP34">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AQ34">
         <v>1.33</v>
@@ -8047,7 +8056,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8128,7 +8137,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ35">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AR35">
         <v>1.66</v>
@@ -8253,7 +8262,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q36">
         <v>4.75</v>
@@ -8459,7 +8468,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q37">
         <v>2</v>
@@ -8665,7 +8674,7 @@
         <v>111</v>
       </c>
       <c r="P38" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q38">
         <v>4</v>
@@ -8871,7 +8880,7 @@
         <v>112</v>
       </c>
       <c r="P39" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9489,7 +9498,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q42">
         <v>2.95</v>
@@ -9695,7 +9704,7 @@
         <v>115</v>
       </c>
       <c r="P43" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q43">
         <v>2</v>
@@ -10107,7 +10116,7 @@
         <v>117</v>
       </c>
       <c r="P45" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10394,7 +10403,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ46">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR46">
         <v>1.57</v>
@@ -10931,7 +10940,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q49">
         <v>3</v>
@@ -11012,7 +11021,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ49">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AR49">
         <v>1.44</v>
@@ -11137,7 +11146,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q50">
         <v>3.75</v>
@@ -11549,7 +11558,7 @@
         <v>86</v>
       </c>
       <c r="P52" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -11755,7 +11764,7 @@
         <v>86</v>
       </c>
       <c r="P53" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q53">
         <v>5.5</v>
@@ -11833,7 +11842,7 @@
         <v>1.33</v>
       </c>
       <c r="AP53">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AQ53">
         <v>1.83</v>
@@ -12167,7 +12176,7 @@
         <v>125</v>
       </c>
       <c r="P55" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q55">
         <v>1.83</v>
@@ -12660,7 +12669,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ57">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR57">
         <v>1.8</v>
@@ -12785,7 +12794,7 @@
         <v>127</v>
       </c>
       <c r="P58" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q58">
         <v>2.38</v>
@@ -13197,7 +13206,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q60">
         <v>3.1</v>
@@ -13481,7 +13490,7 @@
         <v>1</v>
       </c>
       <c r="AP61">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AQ61">
         <v>1.4</v>
@@ -13687,7 +13696,7 @@
         <v>1</v>
       </c>
       <c r="AP62">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AQ62">
         <v>1.8</v>
@@ -13815,7 +13824,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q63">
         <v>6</v>
@@ -14021,7 +14030,7 @@
         <v>132</v>
       </c>
       <c r="P64" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14227,7 +14236,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14433,7 +14442,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q66">
         <v>1.83</v>
@@ -14511,10 +14520,10 @@
         <v>1.25</v>
       </c>
       <c r="AP66">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AQ66">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AR66">
         <v>2.05</v>
@@ -14639,7 +14648,7 @@
         <v>135</v>
       </c>
       <c r="P67" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q67">
         <v>3.1</v>
@@ -14845,7 +14854,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q68">
         <v>5.25</v>
@@ -15051,7 +15060,7 @@
         <v>103</v>
       </c>
       <c r="P69" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q69">
         <v>2.38</v>
@@ -15257,7 +15266,7 @@
         <v>137</v>
       </c>
       <c r="P70" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q70">
         <v>2.2</v>
@@ -15463,7 +15472,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q71">
         <v>2.95</v>
@@ -16287,7 +16296,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q75">
         <v>3.95</v>
@@ -16365,7 +16374,7 @@
         <v>1.2</v>
       </c>
       <c r="AP75">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AQ75">
         <v>1.43</v>
@@ -16574,7 +16583,7 @@
         <v>2</v>
       </c>
       <c r="AQ76">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR76">
         <v>2.52</v>
@@ -16905,7 +16914,7 @@
         <v>143</v>
       </c>
       <c r="P78" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q78">
         <v>2.75</v>
@@ -17111,7 +17120,7 @@
         <v>144</v>
       </c>
       <c r="P79" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -17523,7 +17532,7 @@
         <v>146</v>
       </c>
       <c r="P81" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q81">
         <v>2.45</v>
@@ -17601,7 +17610,7 @@
         <v>2</v>
       </c>
       <c r="AP81">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AQ81">
         <v>2</v>
@@ -17935,7 +17944,7 @@
         <v>127</v>
       </c>
       <c r="P83" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q83">
         <v>2.45</v>
@@ -18141,7 +18150,7 @@
         <v>147</v>
       </c>
       <c r="P84" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q84">
         <v>2.5</v>
@@ -18222,7 +18231,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ84">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AR84">
         <v>2.01</v>
@@ -18553,7 +18562,7 @@
         <v>118</v>
       </c>
       <c r="P86" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q86">
         <v>4.75</v>
@@ -18759,7 +18768,7 @@
         <v>86</v>
       </c>
       <c r="P87" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q87">
         <v>3.5</v>
@@ -19455,7 +19464,7 @@
         <v>1.8</v>
       </c>
       <c r="AP90">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AQ90">
         <v>1.5</v>
@@ -19583,7 +19592,7 @@
         <v>86</v>
       </c>
       <c r="P91" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q91">
         <v>3.4</v>
@@ -19789,7 +19798,7 @@
         <v>86</v>
       </c>
       <c r="P92" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q92">
         <v>2.9</v>
@@ -20201,7 +20210,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -20819,7 +20828,7 @@
         <v>148</v>
       </c>
       <c r="P97" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21231,7 +21240,7 @@
         <v>154</v>
       </c>
       <c r="P99" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q99">
         <v>3.45</v>
@@ -21388,6 +21397,418 @@
       </c>
       <c r="BP99">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:68">
+      <c r="A100" s="1">
+        <v>99</v>
+      </c>
+      <c r="B100">
+        <v>7779050</v>
+      </c>
+      <c r="C100" t="s">
+        <v>68</v>
+      </c>
+      <c r="D100" t="s">
+        <v>69</v>
+      </c>
+      <c r="E100" s="2">
+        <v>45836.41666666666</v>
+      </c>
+      <c r="F100">
+        <v>13</v>
+      </c>
+      <c r="G100" t="s">
+        <v>72</v>
+      </c>
+      <c r="H100" t="s">
+        <v>75</v>
+      </c>
+      <c r="I100">
+        <v>1</v>
+      </c>
+      <c r="J100">
+        <v>0</v>
+      </c>
+      <c r="K100">
+        <v>1</v>
+      </c>
+      <c r="L100">
+        <v>2</v>
+      </c>
+      <c r="M100">
+        <v>0</v>
+      </c>
+      <c r="N100">
+        <v>2</v>
+      </c>
+      <c r="O100" t="s">
+        <v>155</v>
+      </c>
+      <c r="P100" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q100">
+        <v>1.73</v>
+      </c>
+      <c r="R100">
+        <v>2.63</v>
+      </c>
+      <c r="S100">
+        <v>8.5</v>
+      </c>
+      <c r="T100">
+        <v>1.29</v>
+      </c>
+      <c r="U100">
+        <v>3.5</v>
+      </c>
+      <c r="V100">
+        <v>2.25</v>
+      </c>
+      <c r="W100">
+        <v>1.57</v>
+      </c>
+      <c r="X100">
+        <v>5.5</v>
+      </c>
+      <c r="Y100">
+        <v>1.14</v>
+      </c>
+      <c r="Z100">
+        <v>1.24</v>
+      </c>
+      <c r="AA100">
+        <v>5.2</v>
+      </c>
+      <c r="AB100">
+        <v>8.6</v>
+      </c>
+      <c r="AC100">
+        <v>1.03</v>
+      </c>
+      <c r="AD100">
+        <v>13</v>
+      </c>
+      <c r="AE100">
+        <v>1.2</v>
+      </c>
+      <c r="AF100">
+        <v>4.75</v>
+      </c>
+      <c r="AG100">
+        <v>1.57</v>
+      </c>
+      <c r="AH100">
+        <v>2.15</v>
+      </c>
+      <c r="AI100">
+        <v>2</v>
+      </c>
+      <c r="AJ100">
+        <v>1.75</v>
+      </c>
+      <c r="AK100">
+        <v>1.05</v>
+      </c>
+      <c r="AL100">
+        <v>1.13</v>
+      </c>
+      <c r="AM100">
+        <v>3.5</v>
+      </c>
+      <c r="AN100">
+        <v>2.29</v>
+      </c>
+      <c r="AO100">
+        <v>0.8</v>
+      </c>
+      <c r="AP100">
+        <v>2.38</v>
+      </c>
+      <c r="AQ100">
+        <v>0.67</v>
+      </c>
+      <c r="AR100">
+        <v>2.06</v>
+      </c>
+      <c r="AS100">
+        <v>0.87</v>
+      </c>
+      <c r="AT100">
+        <v>2.93</v>
+      </c>
+      <c r="AU100">
+        <v>14</v>
+      </c>
+      <c r="AV100">
+        <v>0</v>
+      </c>
+      <c r="AW100">
+        <v>7</v>
+      </c>
+      <c r="AX100">
+        <v>5</v>
+      </c>
+      <c r="AY100">
+        <v>21</v>
+      </c>
+      <c r="AZ100">
+        <v>5</v>
+      </c>
+      <c r="BA100">
+        <v>7</v>
+      </c>
+      <c r="BB100">
+        <v>2</v>
+      </c>
+      <c r="BC100">
+        <v>9</v>
+      </c>
+      <c r="BD100">
+        <v>1.21</v>
+      </c>
+      <c r="BE100">
+        <v>8.5</v>
+      </c>
+      <c r="BF100">
+        <v>4.6</v>
+      </c>
+      <c r="BG100">
+        <v>1.19</v>
+      </c>
+      <c r="BH100">
+        <v>4.1</v>
+      </c>
+      <c r="BI100">
+        <v>1.33</v>
+      </c>
+      <c r="BJ100">
+        <v>2.95</v>
+      </c>
+      <c r="BK100">
+        <v>1.54</v>
+      </c>
+      <c r="BL100">
+        <v>2.3</v>
+      </c>
+      <c r="BM100">
+        <v>1.84</v>
+      </c>
+      <c r="BN100">
+        <v>1.84</v>
+      </c>
+      <c r="BO100">
+        <v>2.25</v>
+      </c>
+      <c r="BP100">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="101" spans="1:68">
+      <c r="A101" s="1">
+        <v>100</v>
+      </c>
+      <c r="B101">
+        <v>7779052</v>
+      </c>
+      <c r="C101" t="s">
+        <v>68</v>
+      </c>
+      <c r="D101" t="s">
+        <v>69</v>
+      </c>
+      <c r="E101" s="2">
+        <v>45836.52083333334</v>
+      </c>
+      <c r="F101">
+        <v>13</v>
+      </c>
+      <c r="G101" t="s">
+        <v>80</v>
+      </c>
+      <c r="H101" t="s">
+        <v>79</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
+      <c r="K101">
+        <v>0</v>
+      </c>
+      <c r="L101">
+        <v>2</v>
+      </c>
+      <c r="M101">
+        <v>2</v>
+      </c>
+      <c r="N101">
+        <v>4</v>
+      </c>
+      <c r="O101" t="s">
+        <v>156</v>
+      </c>
+      <c r="P101" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q101">
+        <v>3.4</v>
+      </c>
+      <c r="R101">
+        <v>2.2</v>
+      </c>
+      <c r="S101">
+        <v>3</v>
+      </c>
+      <c r="T101">
+        <v>1.36</v>
+      </c>
+      <c r="U101">
+        <v>3</v>
+      </c>
+      <c r="V101">
+        <v>2.75</v>
+      </c>
+      <c r="W101">
+        <v>1.4</v>
+      </c>
+      <c r="X101">
+        <v>7</v>
+      </c>
+      <c r="Y101">
+        <v>1.1</v>
+      </c>
+      <c r="Z101">
+        <v>2.72</v>
+      </c>
+      <c r="AA101">
+        <v>3.16</v>
+      </c>
+      <c r="AB101">
+        <v>2.3</v>
+      </c>
+      <c r="AC101">
+        <v>1</v>
+      </c>
+      <c r="AD101">
+        <v>9</v>
+      </c>
+      <c r="AE101">
+        <v>1.27</v>
+      </c>
+      <c r="AF101">
+        <v>3.64</v>
+      </c>
+      <c r="AG101">
+        <v>1.85</v>
+      </c>
+      <c r="AH101">
+        <v>1.85</v>
+      </c>
+      <c r="AI101">
+        <v>1.75</v>
+      </c>
+      <c r="AJ101">
+        <v>2</v>
+      </c>
+      <c r="AK101">
+        <v>1.55</v>
+      </c>
+      <c r="AL101">
+        <v>1.25</v>
+      </c>
+      <c r="AM101">
+        <v>1.4</v>
+      </c>
+      <c r="AN101">
+        <v>0.8</v>
+      </c>
+      <c r="AO101">
+        <v>0.83</v>
+      </c>
+      <c r="AP101">
+        <v>0.83</v>
+      </c>
+      <c r="AQ101">
+        <v>0.86</v>
+      </c>
+      <c r="AR101">
+        <v>1.03</v>
+      </c>
+      <c r="AS101">
+        <v>1.27</v>
+      </c>
+      <c r="AT101">
+        <v>2.3</v>
+      </c>
+      <c r="AU101">
+        <v>7</v>
+      </c>
+      <c r="AV101">
+        <v>7</v>
+      </c>
+      <c r="AW101">
+        <v>9</v>
+      </c>
+      <c r="AX101">
+        <v>13</v>
+      </c>
+      <c r="AY101">
+        <v>16</v>
+      </c>
+      <c r="AZ101">
+        <v>20</v>
+      </c>
+      <c r="BA101">
+        <v>6</v>
+      </c>
+      <c r="BB101">
+        <v>12</v>
+      </c>
+      <c r="BC101">
+        <v>18</v>
+      </c>
+      <c r="BD101">
+        <v>1.98</v>
+      </c>
+      <c r="BE101">
+        <v>7</v>
+      </c>
+      <c r="BF101">
+        <v>1.95</v>
+      </c>
+      <c r="BG101">
+        <v>1.15</v>
+      </c>
+      <c r="BH101">
+        <v>4.6</v>
+      </c>
+      <c r="BI101">
+        <v>1.27</v>
+      </c>
+      <c r="BJ101">
+        <v>3.3</v>
+      </c>
+      <c r="BK101">
+        <v>1.46</v>
+      </c>
+      <c r="BL101">
+        <v>2.48</v>
+      </c>
+      <c r="BM101">
+        <v>1.72</v>
+      </c>
+      <c r="BN101">
+        <v>1.98</v>
+      </c>
+      <c r="BO101">
+        <v>2.08</v>
+      </c>
+      <c r="BP101">
+        <v>1.66</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="210">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -642,6 +642,9 @@
   <si>
     <t>['46', '76']</t>
   </si>
+  <si>
+    <t>['20', '50', '53']</t>
+  </si>
 </sst>
 </file>
 
@@ -1002,7 +1005,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP101"/>
+  <dimension ref="A1:BP102"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1545,7 +1548,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ3">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -4014,7 +4017,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AQ15">
         <v>0.17</v>
@@ -5665,7 +5668,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ23">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR23">
         <v>1.22</v>
@@ -6692,7 +6695,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AQ28">
         <v>1.8</v>
@@ -9167,7 +9170,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ40">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR40">
         <v>1.88</v>
@@ -11018,7 +11021,7 @@
         <v>1.33</v>
       </c>
       <c r="AP49">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AQ49">
         <v>0.86</v>
@@ -12257,7 +12260,7 @@
         <v>2</v>
       </c>
       <c r="AQ55">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR55">
         <v>2.33</v>
@@ -13902,7 +13905,7 @@
         <v>1.33</v>
       </c>
       <c r="AP63">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AQ63">
         <v>1.33</v>
@@ -15347,7 +15350,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ70">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR70">
         <v>1.63</v>
@@ -16789,7 +16792,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ77">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR77">
         <v>1.37</v>
@@ -17198,7 +17201,7 @@
         <v>1.5</v>
       </c>
       <c r="AP79">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AQ79">
         <v>2</v>
@@ -20082,7 +20085,7 @@
         <v>0.67</v>
       </c>
       <c r="AP93">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AQ93">
         <v>0.71</v>
@@ -21809,6 +21812,212 @@
       </c>
       <c r="BP101">
         <v>1.66</v>
+      </c>
+    </row>
+    <row r="102" spans="1:68">
+      <c r="A102" s="1">
+        <v>101</v>
+      </c>
+      <c r="B102">
+        <v>7779054</v>
+      </c>
+      <c r="C102" t="s">
+        <v>68</v>
+      </c>
+      <c r="D102" t="s">
+        <v>69</v>
+      </c>
+      <c r="E102" s="2">
+        <v>45837.375</v>
+      </c>
+      <c r="F102">
+        <v>13</v>
+      </c>
+      <c r="G102" t="s">
+        <v>83</v>
+      </c>
+      <c r="H102" t="s">
+        <v>82</v>
+      </c>
+      <c r="I102">
+        <v>0</v>
+      </c>
+      <c r="J102">
+        <v>1</v>
+      </c>
+      <c r="K102">
+        <v>1</v>
+      </c>
+      <c r="L102">
+        <v>0</v>
+      </c>
+      <c r="M102">
+        <v>3</v>
+      </c>
+      <c r="N102">
+        <v>3</v>
+      </c>
+      <c r="O102" t="s">
+        <v>86</v>
+      </c>
+      <c r="P102" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q102">
+        <v>2.88</v>
+      </c>
+      <c r="R102">
+        <v>2.3</v>
+      </c>
+      <c r="S102">
+        <v>3.4</v>
+      </c>
+      <c r="T102">
+        <v>1.33</v>
+      </c>
+      <c r="U102">
+        <v>3.25</v>
+      </c>
+      <c r="V102">
+        <v>2.5</v>
+      </c>
+      <c r="W102">
+        <v>1.5</v>
+      </c>
+      <c r="X102">
+        <v>6.5</v>
+      </c>
+      <c r="Y102">
+        <v>1.11</v>
+      </c>
+      <c r="Z102">
+        <v>2.33</v>
+      </c>
+      <c r="AA102">
+        <v>3.29</v>
+      </c>
+      <c r="AB102">
+        <v>2.59</v>
+      </c>
+      <c r="AC102">
+        <v>1.05</v>
+      </c>
+      <c r="AD102">
+        <v>10</v>
+      </c>
+      <c r="AE102">
+        <v>1.25</v>
+      </c>
+      <c r="AF102">
+        <v>4</v>
+      </c>
+      <c r="AG102">
+        <v>1.7</v>
+      </c>
+      <c r="AH102">
+        <v>2.02</v>
+      </c>
+      <c r="AI102">
+        <v>1.62</v>
+      </c>
+      <c r="AJ102">
+        <v>2.2</v>
+      </c>
+      <c r="AK102">
+        <v>1.4</v>
+      </c>
+      <c r="AL102">
+        <v>1.25</v>
+      </c>
+      <c r="AM102">
+        <v>1.57</v>
+      </c>
+      <c r="AN102">
+        <v>0.83</v>
+      </c>
+      <c r="AO102">
+        <v>1.17</v>
+      </c>
+      <c r="AP102">
+        <v>0.71</v>
+      </c>
+      <c r="AQ102">
+        <v>1.43</v>
+      </c>
+      <c r="AR102">
+        <v>1.6</v>
+      </c>
+      <c r="AS102">
+        <v>1.69</v>
+      </c>
+      <c r="AT102">
+        <v>3.29</v>
+      </c>
+      <c r="AU102">
+        <v>2</v>
+      </c>
+      <c r="AV102">
+        <v>6</v>
+      </c>
+      <c r="AW102">
+        <v>14</v>
+      </c>
+      <c r="AX102">
+        <v>5</v>
+      </c>
+      <c r="AY102">
+        <v>16</v>
+      </c>
+      <c r="AZ102">
+        <v>11</v>
+      </c>
+      <c r="BA102">
+        <v>10</v>
+      </c>
+      <c r="BB102">
+        <v>4</v>
+      </c>
+      <c r="BC102">
+        <v>14</v>
+      </c>
+      <c r="BD102">
+        <v>1.81</v>
+      </c>
+      <c r="BE102">
+        <v>7</v>
+      </c>
+      <c r="BF102">
+        <v>2.15</v>
+      </c>
+      <c r="BG102">
+        <v>1.16</v>
+      </c>
+      <c r="BH102">
+        <v>4.6</v>
+      </c>
+      <c r="BI102">
+        <v>1.28</v>
+      </c>
+      <c r="BJ102">
+        <v>3.3</v>
+      </c>
+      <c r="BK102">
+        <v>1.48</v>
+      </c>
+      <c r="BL102">
+        <v>2.45</v>
+      </c>
+      <c r="BM102">
+        <v>1.74</v>
+      </c>
+      <c r="BN102">
+        <v>1.96</v>
+      </c>
+      <c r="BO102">
+        <v>2.12</v>
+      </c>
+      <c r="BP102">
+        <v>1.63</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="213">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -487,6 +487,12 @@
     <t>['70', '9005']</t>
   </si>
   <si>
+    <t>['30', '43', '61']</t>
+  </si>
+  <si>
+    <t>['81']</t>
+  </si>
+  <si>
     <t>['45+8']</t>
   </si>
   <si>
@@ -644,6 +650,9 @@
   </si>
   <si>
     <t>['20', '50', '53']</t>
+  </si>
+  <si>
+    <t>['7', '16', '68']</t>
   </si>
 </sst>
 </file>
@@ -1005,7 +1014,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP102"/>
+  <dimension ref="A1:BP105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1261,7 +1270,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q2">
         <v>3.5</v>
@@ -1545,7 +1554,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ3">
         <v>1.43</v>
@@ -1754,7 +1763,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ4">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1879,7 +1888,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q5">
         <v>2.5</v>
@@ -2085,7 +2094,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q6">
         <v>2.6</v>
@@ -2291,7 +2300,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -2497,7 +2506,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -2575,7 +2584,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AQ8">
         <v>0.86</v>
@@ -2703,7 +2712,7 @@
         <v>86</v>
       </c>
       <c r="P9" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3115,7 +3124,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q11">
         <v>4</v>
@@ -3527,7 +3536,7 @@
         <v>94</v>
       </c>
       <c r="P13" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -3605,7 +3614,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ13">
         <v>1.4</v>
@@ -3733,7 +3742,7 @@
         <v>86</v>
       </c>
       <c r="P14" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4145,7 +4154,7 @@
         <v>96</v>
       </c>
       <c r="P16" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q16">
         <v>2.55</v>
@@ -4226,7 +4235,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ16">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4351,7 +4360,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -4432,7 +4441,7 @@
         <v>2</v>
       </c>
       <c r="AQ17">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4557,7 +4566,7 @@
         <v>86</v>
       </c>
       <c r="P18" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q18">
         <v>2.62</v>
@@ -4635,7 +4644,7 @@
         <v>1</v>
       </c>
       <c r="AP18">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ18">
         <v>2</v>
@@ -5175,7 +5184,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5253,10 +5262,10 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AQ21">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AR21">
         <v>1.59</v>
@@ -5587,7 +5596,7 @@
         <v>86</v>
       </c>
       <c r="P23" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q23">
         <v>2.62</v>
@@ -6077,7 +6086,7 @@
         <v>3</v>
       </c>
       <c r="AP25">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ25">
         <v>1.33</v>
@@ -6205,7 +6214,7 @@
         <v>102</v>
       </c>
       <c r="P26" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q26">
         <v>3.2</v>
@@ -6411,7 +6420,7 @@
         <v>103</v>
       </c>
       <c r="P27" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q27">
         <v>1.72</v>
@@ -6698,7 +6707,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ28">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AR28">
         <v>1.15</v>
@@ -7235,7 +7244,7 @@
         <v>105</v>
       </c>
       <c r="P31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7441,7 +7450,7 @@
         <v>106</v>
       </c>
       <c r="P32" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q32">
         <v>2.88</v>
@@ -7728,7 +7737,7 @@
         <v>1</v>
       </c>
       <c r="AQ33">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR33">
         <v>1.7</v>
@@ -8059,7 +8068,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8265,7 +8274,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q36">
         <v>4.75</v>
@@ -8471,7 +8480,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q37">
         <v>2</v>
@@ -8549,7 +8558,7 @@
         <v>1.5</v>
       </c>
       <c r="AP37">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ37">
         <v>1.5</v>
@@ -8677,7 +8686,7 @@
         <v>111</v>
       </c>
       <c r="P38" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q38">
         <v>4</v>
@@ -8755,7 +8764,7 @@
         <v>3</v>
       </c>
       <c r="AP38">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AQ38">
         <v>1.88</v>
@@ -8883,7 +8892,7 @@
         <v>112</v>
       </c>
       <c r="P39" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -8964,7 +8973,7 @@
         <v>1</v>
       </c>
       <c r="AQ39">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AR39">
         <v>1.72</v>
@@ -9501,7 +9510,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q42">
         <v>2.95</v>
@@ -9579,7 +9588,7 @@
         <v>1.5</v>
       </c>
       <c r="AP42">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ42">
         <v>1.83</v>
@@ -9707,7 +9716,7 @@
         <v>115</v>
       </c>
       <c r="P43" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q43">
         <v>2</v>
@@ -9991,10 +10000,10 @@
         <v>1.5</v>
       </c>
       <c r="AP44">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ44">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AR44">
         <v>1.7</v>
@@ -10119,7 +10128,7 @@
         <v>117</v>
       </c>
       <c r="P45" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10197,7 +10206,7 @@
         <v>0</v>
       </c>
       <c r="AP45">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AQ45">
         <v>1.4</v>
@@ -10612,7 +10621,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ47">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR47">
         <v>1.75</v>
@@ -10943,7 +10952,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q49">
         <v>3</v>
@@ -11149,7 +11158,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q50">
         <v>3.75</v>
@@ -11561,7 +11570,7 @@
         <v>86</v>
       </c>
       <c r="P52" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -11767,7 +11776,7 @@
         <v>86</v>
       </c>
       <c r="P53" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q53">
         <v>5.5</v>
@@ -12054,7 +12063,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ54">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AR54">
         <v>1.34</v>
@@ -12179,7 +12188,7 @@
         <v>125</v>
       </c>
       <c r="P55" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q55">
         <v>1.83</v>
@@ -12466,7 +12475,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ56">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR56">
         <v>1.76</v>
@@ -12797,7 +12806,7 @@
         <v>127</v>
       </c>
       <c r="P58" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q58">
         <v>2.38</v>
@@ -13209,7 +13218,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q60">
         <v>3.1</v>
@@ -13287,7 +13296,7 @@
         <v>2.33</v>
       </c>
       <c r="AP60">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ60">
         <v>2</v>
@@ -13702,7 +13711,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ62">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AR62">
         <v>1.23</v>
@@ -13827,7 +13836,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q63">
         <v>6</v>
@@ -14033,7 +14042,7 @@
         <v>132</v>
       </c>
       <c r="P64" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14239,7 +14248,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14320,7 +14329,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ65">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR65">
         <v>1.28</v>
@@ -14445,7 +14454,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q66">
         <v>1.83</v>
@@ -14651,7 +14660,7 @@
         <v>135</v>
       </c>
       <c r="P67" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q67">
         <v>3.1</v>
@@ -14729,7 +14738,7 @@
         <v>2.5</v>
       </c>
       <c r="AP67">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ67">
         <v>1.88</v>
@@ -14857,7 +14866,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q68">
         <v>5.25</v>
@@ -14935,7 +14944,7 @@
         <v>1.75</v>
       </c>
       <c r="AP68">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AQ68">
         <v>1.33</v>
@@ -15063,7 +15072,7 @@
         <v>103</v>
       </c>
       <c r="P69" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q69">
         <v>2.38</v>
@@ -15269,7 +15278,7 @@
         <v>137</v>
       </c>
       <c r="P70" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q70">
         <v>2.2</v>
@@ -15475,7 +15484,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q71">
         <v>2.95</v>
@@ -15965,7 +15974,7 @@
         <v>1.75</v>
       </c>
       <c r="AP73">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ73">
         <v>1.83</v>
@@ -16171,7 +16180,7 @@
         <v>0.25</v>
       </c>
       <c r="AP74">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ74">
         <v>0.17</v>
@@ -16299,7 +16308,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q75">
         <v>3.95</v>
@@ -16380,7 +16389,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ75">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR75">
         <v>1.1</v>
@@ -16917,7 +16926,7 @@
         <v>143</v>
       </c>
       <c r="P78" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q78">
         <v>2.75</v>
@@ -17123,7 +17132,7 @@
         <v>144</v>
       </c>
       <c r="P79" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -17204,7 +17213,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ79">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AR79">
         <v>1.62</v>
@@ -17535,7 +17544,7 @@
         <v>146</v>
       </c>
       <c r="P81" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q81">
         <v>2.45</v>
@@ -17947,7 +17956,7 @@
         <v>127</v>
       </c>
       <c r="P83" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q83">
         <v>2.45</v>
@@ -18025,7 +18034,7 @@
         <v>0.6</v>
       </c>
       <c r="AP83">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AQ83">
         <v>0.71</v>
@@ -18153,7 +18162,7 @@
         <v>147</v>
       </c>
       <c r="P84" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q84">
         <v>2.5</v>
@@ -18565,7 +18574,7 @@
         <v>118</v>
       </c>
       <c r="P86" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q86">
         <v>4.75</v>
@@ -18646,7 +18655,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ86">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AR86">
         <v>1.3</v>
@@ -18771,7 +18780,7 @@
         <v>86</v>
       </c>
       <c r="P87" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q87">
         <v>3.5</v>
@@ -19595,7 +19604,7 @@
         <v>86</v>
       </c>
       <c r="P91" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q91">
         <v>3.4</v>
@@ -19801,7 +19810,7 @@
         <v>86</v>
       </c>
       <c r="P92" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q92">
         <v>2.9</v>
@@ -20213,7 +20222,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -20294,7 +20303,7 @@
         <v>1</v>
       </c>
       <c r="AQ94">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR94">
         <v>1.73</v>
@@ -20831,7 +20840,7 @@
         <v>148</v>
       </c>
       <c r="P97" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -20912,7 +20921,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ97">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AR97">
         <v>1.72</v>
@@ -21243,7 +21252,7 @@
         <v>154</v>
       </c>
       <c r="P99" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q99">
         <v>3.45</v>
@@ -21655,7 +21664,7 @@
         <v>156</v>
       </c>
       <c r="P101" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q101">
         <v>3.4</v>
@@ -21861,7 +21870,7 @@
         <v>86</v>
       </c>
       <c r="P102" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22018,6 +22027,624 @@
       </c>
       <c r="BP102">
         <v>1.63</v>
+      </c>
+    </row>
+    <row r="103" spans="1:68">
+      <c r="A103" s="1">
+        <v>102</v>
+      </c>
+      <c r="B103">
+        <v>7779048</v>
+      </c>
+      <c r="C103" t="s">
+        <v>68</v>
+      </c>
+      <c r="D103" t="s">
+        <v>69</v>
+      </c>
+      <c r="E103" s="2">
+        <v>45837.375</v>
+      </c>
+      <c r="F103">
+        <v>13</v>
+      </c>
+      <c r="G103" t="s">
+        <v>81</v>
+      </c>
+      <c r="H103" t="s">
+        <v>78</v>
+      </c>
+      <c r="I103">
+        <v>2</v>
+      </c>
+      <c r="J103">
+        <v>0</v>
+      </c>
+      <c r="K103">
+        <v>2</v>
+      </c>
+      <c r="L103">
+        <v>3</v>
+      </c>
+      <c r="M103">
+        <v>0</v>
+      </c>
+      <c r="N103">
+        <v>3</v>
+      </c>
+      <c r="O103" t="s">
+        <v>157</v>
+      </c>
+      <c r="P103" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q103">
+        <v>2.63</v>
+      </c>
+      <c r="R103">
+        <v>2.05</v>
+      </c>
+      <c r="S103">
+        <v>4.75</v>
+      </c>
+      <c r="T103">
+        <v>1.44</v>
+      </c>
+      <c r="U103">
+        <v>2.63</v>
+      </c>
+      <c r="V103">
+        <v>3.25</v>
+      </c>
+      <c r="W103">
+        <v>1.33</v>
+      </c>
+      <c r="X103">
+        <v>10</v>
+      </c>
+      <c r="Y103">
+        <v>1.06</v>
+      </c>
+      <c r="Z103">
+        <v>1.88</v>
+      </c>
+      <c r="AA103">
+        <v>3.14</v>
+      </c>
+      <c r="AB103">
+        <v>3.71</v>
+      </c>
+      <c r="AC103">
+        <v>1.08</v>
+      </c>
+      <c r="AD103">
+        <v>8</v>
+      </c>
+      <c r="AE103">
+        <v>1.42</v>
+      </c>
+      <c r="AF103">
+        <v>2.9</v>
+      </c>
+      <c r="AG103">
+        <v>1.98</v>
+      </c>
+      <c r="AH103">
+        <v>1.73</v>
+      </c>
+      <c r="AI103">
+        <v>2</v>
+      </c>
+      <c r="AJ103">
+        <v>1.75</v>
+      </c>
+      <c r="AK103">
+        <v>1.25</v>
+      </c>
+      <c r="AL103">
+        <v>1.28</v>
+      </c>
+      <c r="AM103">
+        <v>1.77</v>
+      </c>
+      <c r="AN103">
+        <v>2.2</v>
+      </c>
+      <c r="AO103">
+        <v>2</v>
+      </c>
+      <c r="AP103">
+        <v>2.33</v>
+      </c>
+      <c r="AQ103">
+        <v>1.71</v>
+      </c>
+      <c r="AR103">
+        <v>1.74</v>
+      </c>
+      <c r="AS103">
+        <v>1.24</v>
+      </c>
+      <c r="AT103">
+        <v>2.98</v>
+      </c>
+      <c r="AU103">
+        <v>5</v>
+      </c>
+      <c r="AV103">
+        <v>0</v>
+      </c>
+      <c r="AW103">
+        <v>10</v>
+      </c>
+      <c r="AX103">
+        <v>9</v>
+      </c>
+      <c r="AY103">
+        <v>15</v>
+      </c>
+      <c r="AZ103">
+        <v>9</v>
+      </c>
+      <c r="BA103">
+        <v>2</v>
+      </c>
+      <c r="BB103">
+        <v>5</v>
+      </c>
+      <c r="BC103">
+        <v>7</v>
+      </c>
+      <c r="BD103">
+        <v>1.68</v>
+      </c>
+      <c r="BE103">
+        <v>7</v>
+      </c>
+      <c r="BF103">
+        <v>2.4</v>
+      </c>
+      <c r="BG103">
+        <v>1.18</v>
+      </c>
+      <c r="BH103">
+        <v>4.1</v>
+      </c>
+      <c r="BI103">
+        <v>1.32</v>
+      </c>
+      <c r="BJ103">
+        <v>3.05</v>
+      </c>
+      <c r="BK103">
+        <v>1.52</v>
+      </c>
+      <c r="BL103">
+        <v>2.32</v>
+      </c>
+      <c r="BM103">
+        <v>1.82</v>
+      </c>
+      <c r="BN103">
+        <v>1.86</v>
+      </c>
+      <c r="BO103">
+        <v>2.23</v>
+      </c>
+      <c r="BP103">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="104" spans="1:68">
+      <c r="A104" s="1">
+        <v>103</v>
+      </c>
+      <c r="B104">
+        <v>7779051</v>
+      </c>
+      <c r="C104" t="s">
+        <v>68</v>
+      </c>
+      <c r="D104" t="s">
+        <v>69</v>
+      </c>
+      <c r="E104" s="2">
+        <v>45837.47916666666</v>
+      </c>
+      <c r="F104">
+        <v>13</v>
+      </c>
+      <c r="G104" t="s">
+        <v>71</v>
+      </c>
+      <c r="H104" t="s">
+        <v>77</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
+      </c>
+      <c r="J104">
+        <v>2</v>
+      </c>
+      <c r="K104">
+        <v>2</v>
+      </c>
+      <c r="L104">
+        <v>1</v>
+      </c>
+      <c r="M104">
+        <v>3</v>
+      </c>
+      <c r="N104">
+        <v>4</v>
+      </c>
+      <c r="O104" t="s">
+        <v>158</v>
+      </c>
+      <c r="P104" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q104">
+        <v>3.1</v>
+      </c>
+      <c r="R104">
+        <v>2.3</v>
+      </c>
+      <c r="S104">
+        <v>3.2</v>
+      </c>
+      <c r="T104">
+        <v>1.33</v>
+      </c>
+      <c r="U104">
+        <v>3.25</v>
+      </c>
+      <c r="V104">
+        <v>2.5</v>
+      </c>
+      <c r="W104">
+        <v>1.5</v>
+      </c>
+      <c r="X104">
+        <v>6.5</v>
+      </c>
+      <c r="Y104">
+        <v>1.11</v>
+      </c>
+      <c r="Z104">
+        <v>2.33</v>
+      </c>
+      <c r="AA104">
+        <v>3.36</v>
+      </c>
+      <c r="AB104">
+        <v>2.54</v>
+      </c>
+      <c r="AC104">
+        <v>1.05</v>
+      </c>
+      <c r="AD104">
+        <v>10</v>
+      </c>
+      <c r="AE104">
+        <v>1.25</v>
+      </c>
+      <c r="AF104">
+        <v>4</v>
+      </c>
+      <c r="AG104">
+        <v>1.62</v>
+      </c>
+      <c r="AH104">
+        <v>2.15</v>
+      </c>
+      <c r="AI104">
+        <v>1.62</v>
+      </c>
+      <c r="AJ104">
+        <v>2.2</v>
+      </c>
+      <c r="AK104">
+        <v>1.45</v>
+      </c>
+      <c r="AL104">
+        <v>1.25</v>
+      </c>
+      <c r="AM104">
+        <v>1.53</v>
+      </c>
+      <c r="AN104">
+        <v>1.33</v>
+      </c>
+      <c r="AO104">
+        <v>1.43</v>
+      </c>
+      <c r="AP104">
+        <v>1.14</v>
+      </c>
+      <c r="AQ104">
+        <v>1.63</v>
+      </c>
+      <c r="AR104">
+        <v>1.97</v>
+      </c>
+      <c r="AS104">
+        <v>1.56</v>
+      </c>
+      <c r="AT104">
+        <v>3.53</v>
+      </c>
+      <c r="AU104">
+        <v>2</v>
+      </c>
+      <c r="AV104">
+        <v>9</v>
+      </c>
+      <c r="AW104">
+        <v>2</v>
+      </c>
+      <c r="AX104">
+        <v>14</v>
+      </c>
+      <c r="AY104">
+        <v>4</v>
+      </c>
+      <c r="AZ104">
+        <v>23</v>
+      </c>
+      <c r="BA104">
+        <v>1</v>
+      </c>
+      <c r="BB104">
+        <v>4</v>
+      </c>
+      <c r="BC104">
+        <v>5</v>
+      </c>
+      <c r="BD104">
+        <v>1.91</v>
+      </c>
+      <c r="BE104">
+        <v>7</v>
+      </c>
+      <c r="BF104">
+        <v>2.02</v>
+      </c>
+      <c r="BG104">
+        <v>1.1</v>
+      </c>
+      <c r="BH104">
+        <v>5.4</v>
+      </c>
+      <c r="BI104">
+        <v>1.21</v>
+      </c>
+      <c r="BJ104">
+        <v>3.9</v>
+      </c>
+      <c r="BK104">
+        <v>1.35</v>
+      </c>
+      <c r="BL104">
+        <v>2.88</v>
+      </c>
+      <c r="BM104">
+        <v>1.57</v>
+      </c>
+      <c r="BN104">
+        <v>2.23</v>
+      </c>
+      <c r="BO104">
+        <v>1.88</v>
+      </c>
+      <c r="BP104">
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="105" spans="1:68">
+      <c r="A105" s="1">
+        <v>104</v>
+      </c>
+      <c r="B105">
+        <v>7779055</v>
+      </c>
+      <c r="C105" t="s">
+        <v>68</v>
+      </c>
+      <c r="D105" t="s">
+        <v>69</v>
+      </c>
+      <c r="E105" s="2">
+        <v>45837.47916666666</v>
+      </c>
+      <c r="F105">
+        <v>13</v>
+      </c>
+      <c r="G105" t="s">
+        <v>76</v>
+      </c>
+      <c r="H105" t="s">
+        <v>73</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+      <c r="J105">
+        <v>0</v>
+      </c>
+      <c r="K105">
+        <v>0</v>
+      </c>
+      <c r="L105">
+        <v>0</v>
+      </c>
+      <c r="M105">
+        <v>0</v>
+      </c>
+      <c r="N105">
+        <v>0</v>
+      </c>
+      <c r="O105" t="s">
+        <v>86</v>
+      </c>
+      <c r="P105" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q105">
+        <v>4.33</v>
+      </c>
+      <c r="R105">
+        <v>2.25</v>
+      </c>
+      <c r="S105">
+        <v>2.5</v>
+      </c>
+      <c r="T105">
+        <v>1.36</v>
+      </c>
+      <c r="U105">
+        <v>3</v>
+      </c>
+      <c r="V105">
+        <v>2.63</v>
+      </c>
+      <c r="W105">
+        <v>1.44</v>
+      </c>
+      <c r="X105">
+        <v>7</v>
+      </c>
+      <c r="Y105">
+        <v>1.1</v>
+      </c>
+      <c r="Z105">
+        <v>3.45</v>
+      </c>
+      <c r="AA105">
+        <v>3.27</v>
+      </c>
+      <c r="AB105">
+        <v>1.91</v>
+      </c>
+      <c r="AC105">
+        <v>1.06</v>
+      </c>
+      <c r="AD105">
+        <v>9.5</v>
+      </c>
+      <c r="AE105">
+        <v>1.3</v>
+      </c>
+      <c r="AF105">
+        <v>3.55</v>
+      </c>
+      <c r="AG105">
+        <v>1.82</v>
+      </c>
+      <c r="AH105">
+        <v>1.88</v>
+      </c>
+      <c r="AI105">
+        <v>1.75</v>
+      </c>
+      <c r="AJ105">
+        <v>2</v>
+      </c>
+      <c r="AK105">
+        <v>1.8</v>
+      </c>
+      <c r="AL105">
+        <v>1.25</v>
+      </c>
+      <c r="AM105">
+        <v>1.25</v>
+      </c>
+      <c r="AN105">
+        <v>0.33</v>
+      </c>
+      <c r="AO105">
+        <v>1.8</v>
+      </c>
+      <c r="AP105">
+        <v>0.43</v>
+      </c>
+      <c r="AQ105">
+        <v>1.67</v>
+      </c>
+      <c r="AR105">
+        <v>1.52</v>
+      </c>
+      <c r="AS105">
+        <v>1.48</v>
+      </c>
+      <c r="AT105">
+        <v>3</v>
+      </c>
+      <c r="AU105">
+        <v>6</v>
+      </c>
+      <c r="AV105">
+        <v>4</v>
+      </c>
+      <c r="AW105">
+        <v>11</v>
+      </c>
+      <c r="AX105">
+        <v>7</v>
+      </c>
+      <c r="AY105">
+        <v>17</v>
+      </c>
+      <c r="AZ105">
+        <v>11</v>
+      </c>
+      <c r="BA105">
+        <v>9</v>
+      </c>
+      <c r="BB105">
+        <v>8</v>
+      </c>
+      <c r="BC105">
+        <v>17</v>
+      </c>
+      <c r="BD105">
+        <v>2.18</v>
+      </c>
+      <c r="BE105">
+        <v>7</v>
+      </c>
+      <c r="BF105">
+        <v>1.79</v>
+      </c>
+      <c r="BG105">
+        <v>1.18</v>
+      </c>
+      <c r="BH105">
+        <v>4.2</v>
+      </c>
+      <c r="BI105">
+        <v>1.32</v>
+      </c>
+      <c r="BJ105">
+        <v>3.05</v>
+      </c>
+      <c r="BK105">
+        <v>1.52</v>
+      </c>
+      <c r="BL105">
+        <v>2.33</v>
+      </c>
+      <c r="BM105">
+        <v>1.81</v>
+      </c>
+      <c r="BN105">
+        <v>1.88</v>
+      </c>
+      <c r="BO105">
+        <v>2.23</v>
+      </c>
+      <c r="BP105">
+        <v>1.56</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="216">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -493,6 +493,12 @@
     <t>['81']</t>
   </si>
   <si>
+    <t>['73']</t>
+  </si>
+  <si>
+    <t>['4502']</t>
+  </si>
+  <si>
     <t>['45+8']</t>
   </si>
   <si>
@@ -653,6 +659,9 @@
   </si>
   <si>
     <t>['7', '16', '68']</t>
+  </si>
+  <si>
+    <t>['59']</t>
   </si>
 </sst>
 </file>
@@ -1014,7 +1023,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP105"/>
+  <dimension ref="A1:BP107"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1270,7 +1279,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q2">
         <v>3.5</v>
@@ -1351,7 +1360,7 @@
         <v>1</v>
       </c>
       <c r="AQ2">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1888,7 +1897,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q5">
         <v>2.5</v>
@@ -2094,7 +2103,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q6">
         <v>2.6</v>
@@ -2300,7 +2309,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -2506,7 +2515,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -2712,7 +2721,7 @@
         <v>86</v>
       </c>
       <c r="P9" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3124,7 +3133,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q11">
         <v>4</v>
@@ -3536,7 +3545,7 @@
         <v>94</v>
       </c>
       <c r="P13" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -3617,7 +3626,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ13">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3742,7 +3751,7 @@
         <v>86</v>
       </c>
       <c r="P14" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4154,7 +4163,7 @@
         <v>96</v>
       </c>
       <c r="P16" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q16">
         <v>2.55</v>
@@ -4232,7 +4241,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="AQ16">
         <v>1.63</v>
@@ -4360,7 +4369,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -4566,7 +4575,7 @@
         <v>86</v>
       </c>
       <c r="P18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q18">
         <v>2.62</v>
@@ -4853,7 +4862,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ19">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR19">
         <v>2.16</v>
@@ -5184,7 +5193,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5596,7 +5605,7 @@
         <v>86</v>
       </c>
       <c r="P23" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q23">
         <v>2.62</v>
@@ -6089,7 +6098,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ25">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR25">
         <v>1.74</v>
@@ -6214,7 +6223,7 @@
         <v>102</v>
       </c>
       <c r="P26" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q26">
         <v>3.2</v>
@@ -6292,7 +6301,7 @@
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="AQ26">
         <v>1.83</v>
@@ -6420,7 +6429,7 @@
         <v>103</v>
       </c>
       <c r="P27" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q27">
         <v>1.72</v>
@@ -7244,7 +7253,7 @@
         <v>105</v>
       </c>
       <c r="P31" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7450,7 +7459,7 @@
         <v>106</v>
       </c>
       <c r="P32" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q32">
         <v>2.88</v>
@@ -7943,7 +7952,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ34">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR34">
         <v>1.98</v>
@@ -8068,7 +8077,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8274,7 +8283,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q36">
         <v>4.75</v>
@@ -8480,7 +8489,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q37">
         <v>2</v>
@@ -8686,7 +8695,7 @@
         <v>111</v>
       </c>
       <c r="P38" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q38">
         <v>4</v>
@@ -8892,7 +8901,7 @@
         <v>112</v>
       </c>
       <c r="P39" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9510,7 +9519,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q42">
         <v>2.95</v>
@@ -9716,7 +9725,7 @@
         <v>115</v>
       </c>
       <c r="P43" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q43">
         <v>2</v>
@@ -9794,7 +9803,7 @@
         <v>2</v>
       </c>
       <c r="AP43">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="AQ43">
         <v>1.5</v>
@@ -10128,7 +10137,7 @@
         <v>117</v>
       </c>
       <c r="P45" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10209,7 +10218,7 @@
         <v>0.43</v>
       </c>
       <c r="AQ45">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR45">
         <v>1.47</v>
@@ -10952,7 +10961,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q49">
         <v>3</v>
@@ -11158,7 +11167,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q50">
         <v>3.75</v>
@@ -11570,7 +11579,7 @@
         <v>86</v>
       </c>
       <c r="P52" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -11776,7 +11785,7 @@
         <v>86</v>
       </c>
       <c r="P53" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q53">
         <v>5.5</v>
@@ -12060,7 +12069,7 @@
         <v>2</v>
       </c>
       <c r="AP54">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="AQ54">
         <v>1.71</v>
@@ -12188,7 +12197,7 @@
         <v>125</v>
       </c>
       <c r="P55" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q55">
         <v>1.83</v>
@@ -12806,7 +12815,7 @@
         <v>127</v>
       </c>
       <c r="P58" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q58">
         <v>2.38</v>
@@ -13218,7 +13227,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q60">
         <v>3.1</v>
@@ -13505,7 +13514,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ61">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR61">
         <v>1.9</v>
@@ -13836,7 +13845,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q63">
         <v>6</v>
@@ -13917,7 +13926,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ63">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR63">
         <v>1.61</v>
@@ -14042,7 +14051,7 @@
         <v>132</v>
       </c>
       <c r="P64" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14248,7 +14257,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14454,7 +14463,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q66">
         <v>1.83</v>
@@ -14660,7 +14669,7 @@
         <v>135</v>
       </c>
       <c r="P67" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q67">
         <v>3.1</v>
@@ -14866,7 +14875,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q68">
         <v>5.25</v>
@@ -14947,7 +14956,7 @@
         <v>0.43</v>
       </c>
       <c r="AQ68">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR68">
         <v>1.55</v>
@@ -15072,7 +15081,7 @@
         <v>103</v>
       </c>
       <c r="P69" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q69">
         <v>2.38</v>
@@ -15278,7 +15287,7 @@
         <v>137</v>
       </c>
       <c r="P70" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q70">
         <v>2.2</v>
@@ -15484,7 +15493,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q71">
         <v>2.95</v>
@@ -16308,7 +16317,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q75">
         <v>3.95</v>
@@ -16798,7 +16807,7 @@
         <v>1.4</v>
       </c>
       <c r="AP77">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="AQ77">
         <v>1.43</v>
@@ -16926,7 +16935,7 @@
         <v>143</v>
       </c>
       <c r="P78" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q78">
         <v>2.75</v>
@@ -17007,7 +17016,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ78">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR78">
         <v>1.49</v>
@@ -17132,7 +17141,7 @@
         <v>144</v>
       </c>
       <c r="P79" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -17544,7 +17553,7 @@
         <v>146</v>
       </c>
       <c r="P81" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q81">
         <v>2.45</v>
@@ -17956,7 +17965,7 @@
         <v>127</v>
       </c>
       <c r="P83" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q83">
         <v>2.45</v>
@@ -18162,7 +18171,7 @@
         <v>147</v>
       </c>
       <c r="P84" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q84">
         <v>2.5</v>
@@ -18449,7 +18458,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ85">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR85">
         <v>1.69</v>
@@ -18574,7 +18583,7 @@
         <v>118</v>
       </c>
       <c r="P86" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q86">
         <v>4.75</v>
@@ -18780,7 +18789,7 @@
         <v>86</v>
       </c>
       <c r="P87" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q87">
         <v>3.5</v>
@@ -19604,7 +19613,7 @@
         <v>86</v>
       </c>
       <c r="P91" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q91">
         <v>3.4</v>
@@ -19810,7 +19819,7 @@
         <v>86</v>
       </c>
       <c r="P92" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q92">
         <v>2.9</v>
@@ -20222,7 +20231,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -20840,7 +20849,7 @@
         <v>148</v>
       </c>
       <c r="P97" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21124,7 +21133,7 @@
         <v>0.2</v>
       </c>
       <c r="AP98">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="AQ98">
         <v>0.17</v>
@@ -21252,7 +21261,7 @@
         <v>154</v>
       </c>
       <c r="P99" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q99">
         <v>3.45</v>
@@ -21664,7 +21673,7 @@
         <v>156</v>
       </c>
       <c r="P101" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q101">
         <v>3.4</v>
@@ -21870,7 +21879,7 @@
         <v>86</v>
       </c>
       <c r="P102" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22282,7 +22291,7 @@
         <v>158</v>
       </c>
       <c r="P104" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q104">
         <v>3.1</v>
@@ -22644,6 +22653,418 @@
         <v>2.23</v>
       </c>
       <c r="BP105">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="106" spans="1:68">
+      <c r="A106" s="1">
+        <v>105</v>
+      </c>
+      <c r="B106">
+        <v>7779053</v>
+      </c>
+      <c r="C106" t="s">
+        <v>68</v>
+      </c>
+      <c r="D106" t="s">
+        <v>69</v>
+      </c>
+      <c r="E106" s="2">
+        <v>45838.58333333334</v>
+      </c>
+      <c r="F106">
+        <v>13</v>
+      </c>
+      <c r="G106" t="s">
+        <v>84</v>
+      </c>
+      <c r="H106" t="s">
+        <v>85</v>
+      </c>
+      <c r="I106">
+        <v>0</v>
+      </c>
+      <c r="J106">
+        <v>1</v>
+      </c>
+      <c r="K106">
+        <v>1</v>
+      </c>
+      <c r="L106">
+        <v>1</v>
+      </c>
+      <c r="M106">
+        <v>1</v>
+      </c>
+      <c r="N106">
+        <v>2</v>
+      </c>
+      <c r="O106" t="s">
+        <v>159</v>
+      </c>
+      <c r="P106" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q106">
+        <v>3.25</v>
+      </c>
+      <c r="R106">
+        <v>2.2</v>
+      </c>
+      <c r="S106">
+        <v>3.2</v>
+      </c>
+      <c r="T106">
+        <v>1.36</v>
+      </c>
+      <c r="U106">
+        <v>3</v>
+      </c>
+      <c r="V106">
+        <v>2.75</v>
+      </c>
+      <c r="W106">
+        <v>1.4</v>
+      </c>
+      <c r="X106">
+        <v>8</v>
+      </c>
+      <c r="Y106">
+        <v>1.08</v>
+      </c>
+      <c r="Z106">
+        <v>2.56</v>
+      </c>
+      <c r="AA106">
+        <v>3.13</v>
+      </c>
+      <c r="AB106">
+        <v>2.44</v>
+      </c>
+      <c r="AC106">
+        <v>1.06</v>
+      </c>
+      <c r="AD106">
+        <v>9</v>
+      </c>
+      <c r="AE106">
+        <v>1.33</v>
+      </c>
+      <c r="AF106">
+        <v>3.4</v>
+      </c>
+      <c r="AG106">
+        <v>1.88</v>
+      </c>
+      <c r="AH106">
+        <v>1.82</v>
+      </c>
+      <c r="AI106">
+        <v>1.7</v>
+      </c>
+      <c r="AJ106">
+        <v>2.05</v>
+      </c>
+      <c r="AK106">
+        <v>1.49</v>
+      </c>
+      <c r="AL106">
+        <v>1.31</v>
+      </c>
+      <c r="AM106">
+        <v>1.44</v>
+      </c>
+      <c r="AN106">
+        <v>2.67</v>
+      </c>
+      <c r="AO106">
+        <v>1.33</v>
+      </c>
+      <c r="AP106">
+        <v>2.43</v>
+      </c>
+      <c r="AQ106">
+        <v>1.29</v>
+      </c>
+      <c r="AR106">
+        <v>1.34</v>
+      </c>
+      <c r="AS106">
+        <v>1.44</v>
+      </c>
+      <c r="AT106">
+        <v>2.78</v>
+      </c>
+      <c r="AU106">
+        <v>4</v>
+      </c>
+      <c r="AV106">
+        <v>6</v>
+      </c>
+      <c r="AW106">
+        <v>15</v>
+      </c>
+      <c r="AX106">
+        <v>6</v>
+      </c>
+      <c r="AY106">
+        <v>19</v>
+      </c>
+      <c r="AZ106">
+        <v>12</v>
+      </c>
+      <c r="BA106">
+        <v>8</v>
+      </c>
+      <c r="BB106">
+        <v>5</v>
+      </c>
+      <c r="BC106">
+        <v>13</v>
+      </c>
+      <c r="BD106">
+        <v>2.17</v>
+      </c>
+      <c r="BE106">
+        <v>6.75</v>
+      </c>
+      <c r="BF106">
+        <v>1.82</v>
+      </c>
+      <c r="BG106">
+        <v>1.23</v>
+      </c>
+      <c r="BH106">
+        <v>3.7</v>
+      </c>
+      <c r="BI106">
+        <v>1.38</v>
+      </c>
+      <c r="BJ106">
+        <v>2.7</v>
+      </c>
+      <c r="BK106">
+        <v>1.63</v>
+      </c>
+      <c r="BL106">
+        <v>2.12</v>
+      </c>
+      <c r="BM106">
+        <v>1.97</v>
+      </c>
+      <c r="BN106">
+        <v>1.74</v>
+      </c>
+      <c r="BO106">
+        <v>2.43</v>
+      </c>
+      <c r="BP106">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="107" spans="1:68">
+      <c r="A107" s="1">
+        <v>106</v>
+      </c>
+      <c r="B107">
+        <v>7779049</v>
+      </c>
+      <c r="C107" t="s">
+        <v>68</v>
+      </c>
+      <c r="D107" t="s">
+        <v>69</v>
+      </c>
+      <c r="E107" s="2">
+        <v>45838.58333333334</v>
+      </c>
+      <c r="F107">
+        <v>13</v>
+      </c>
+      <c r="G107" t="s">
+        <v>70</v>
+      </c>
+      <c r="H107" t="s">
+        <v>74</v>
+      </c>
+      <c r="I107">
+        <v>1</v>
+      </c>
+      <c r="J107">
+        <v>0</v>
+      </c>
+      <c r="K107">
+        <v>1</v>
+      </c>
+      <c r="L107">
+        <v>1</v>
+      </c>
+      <c r="M107">
+        <v>1</v>
+      </c>
+      <c r="N107">
+        <v>2</v>
+      </c>
+      <c r="O107" t="s">
+        <v>160</v>
+      </c>
+      <c r="P107" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q107">
+        <v>2.25</v>
+      </c>
+      <c r="R107">
+        <v>2.4</v>
+      </c>
+      <c r="S107">
+        <v>4.75</v>
+      </c>
+      <c r="T107">
+        <v>1.3</v>
+      </c>
+      <c r="U107">
+        <v>3.4</v>
+      </c>
+      <c r="V107">
+        <v>2.38</v>
+      </c>
+      <c r="W107">
+        <v>1.53</v>
+      </c>
+      <c r="X107">
+        <v>6</v>
+      </c>
+      <c r="Y107">
+        <v>1.13</v>
+      </c>
+      <c r="Z107">
+        <v>1.65</v>
+      </c>
+      <c r="AA107">
+        <v>3.7</v>
+      </c>
+      <c r="AB107">
+        <v>4.1</v>
+      </c>
+      <c r="AC107">
+        <v>1.04</v>
+      </c>
+      <c r="AD107">
+        <v>11</v>
+      </c>
+      <c r="AE107">
+        <v>1.22</v>
+      </c>
+      <c r="AF107">
+        <v>4.33</v>
+      </c>
+      <c r="AG107">
+        <v>1.65</v>
+      </c>
+      <c r="AH107">
+        <v>2.05</v>
+      </c>
+      <c r="AI107">
+        <v>1.67</v>
+      </c>
+      <c r="AJ107">
+        <v>2.1</v>
+      </c>
+      <c r="AK107">
+        <v>1.21</v>
+      </c>
+      <c r="AL107">
+        <v>1.25</v>
+      </c>
+      <c r="AM107">
+        <v>2</v>
+      </c>
+      <c r="AN107">
+        <v>1</v>
+      </c>
+      <c r="AO107">
+        <v>1.4</v>
+      </c>
+      <c r="AP107">
+        <v>1</v>
+      </c>
+      <c r="AQ107">
+        <v>1.33</v>
+      </c>
+      <c r="AR107">
+        <v>1.58</v>
+      </c>
+      <c r="AS107">
+        <v>1.18</v>
+      </c>
+      <c r="AT107">
+        <v>2.76</v>
+      </c>
+      <c r="AU107">
+        <v>15</v>
+      </c>
+      <c r="AV107">
+        <v>4</v>
+      </c>
+      <c r="AW107">
+        <v>15</v>
+      </c>
+      <c r="AX107">
+        <v>5</v>
+      </c>
+      <c r="AY107">
+        <v>30</v>
+      </c>
+      <c r="AZ107">
+        <v>9</v>
+      </c>
+      <c r="BA107">
+        <v>11</v>
+      </c>
+      <c r="BB107">
+        <v>1</v>
+      </c>
+      <c r="BC107">
+        <v>12</v>
+      </c>
+      <c r="BD107">
+        <v>1.38</v>
+      </c>
+      <c r="BE107">
+        <v>7.5</v>
+      </c>
+      <c r="BF107">
+        <v>3.3</v>
+      </c>
+      <c r="BG107">
+        <v>1.18</v>
+      </c>
+      <c r="BH107">
+        <v>4.2</v>
+      </c>
+      <c r="BI107">
+        <v>1.3</v>
+      </c>
+      <c r="BJ107">
+        <v>3.05</v>
+      </c>
+      <c r="BK107">
+        <v>1.52</v>
+      </c>
+      <c r="BL107">
+        <v>2.33</v>
+      </c>
+      <c r="BM107">
+        <v>1.81</v>
+      </c>
+      <c r="BN107">
+        <v>1.88</v>
+      </c>
+      <c r="BO107">
+        <v>2.23</v>
+      </c>
+      <c r="BP107">
         <v>1.56</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="216">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -475,7 +475,7 @@
     <t>['9', '33', '85']</t>
   </si>
   <si>
-    <t>['74', '9001']</t>
+    <t>['74', '90+1']</t>
   </si>
   <si>
     <t>['7', '34', '65']</t>
@@ -484,7 +484,7 @@
     <t>['30', '59']</t>
   </si>
   <si>
-    <t>['70', '9005']</t>
+    <t>['70', '90+5']</t>
   </si>
   <si>
     <t>['30', '43', '61']</t>
@@ -496,7 +496,7 @@
     <t>['73']</t>
   </si>
   <si>
-    <t>['4502']</t>
+    <t>['45+2']</t>
   </si>
   <si>
     <t>['45+8']</t>
@@ -646,7 +646,7 @@
     <t>['18', '74', '77']</t>
   </si>
   <si>
-    <t>['24', '42', '9008']</t>
+    <t>['24', '42', '90+8']</t>
   </si>
   <si>
     <t>['57']</t>
@@ -1023,7 +1023,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP107"/>
+  <dimension ref="A1:BP109"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1360,7 +1360,7 @@
         <v>1</v>
       </c>
       <c r="AQ2">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1978,7 +1978,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ5">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2799,7 +2799,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ9">
         <v>1.88</v>
@@ -3417,7 +3417,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AQ12">
         <v>1.17</v>
@@ -4656,7 +4656,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ18">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR18">
         <v>2.05</v>
@@ -5477,7 +5477,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ22">
         <v>1.5</v>
@@ -6098,7 +6098,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ25">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AR25">
         <v>1.74</v>
@@ -7125,7 +7125,7 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AQ30">
         <v>1.88</v>
@@ -7952,7 +7952,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ34">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AR34">
         <v>1.98</v>
@@ -8364,7 +8364,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ36">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR36">
         <v>1.54</v>
@@ -9185,7 +9185,7 @@
         <v>1.5</v>
       </c>
       <c r="AP40">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ40">
         <v>1.43</v>
@@ -11863,7 +11863,7 @@
         <v>1.33</v>
       </c>
       <c r="AP53">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AQ53">
         <v>1.83</v>
@@ -12893,7 +12893,7 @@
         <v>0</v>
       </c>
       <c r="AP58">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ58">
         <v>0.17</v>
@@ -13308,7 +13308,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ60">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR60">
         <v>1.84</v>
@@ -13717,7 +13717,7 @@
         <v>1</v>
       </c>
       <c r="AP62">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AQ62">
         <v>1.67</v>
@@ -13926,7 +13926,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ63">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AR63">
         <v>1.61</v>
@@ -14956,7 +14956,7 @@
         <v>0.43</v>
       </c>
       <c r="AQ68">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AR68">
         <v>1.55</v>
@@ -15574,7 +15574,7 @@
         <v>1</v>
       </c>
       <c r="AQ71">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR71">
         <v>1.63</v>
@@ -16395,7 +16395,7 @@
         <v>1.2</v>
       </c>
       <c r="AP75">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AQ75">
         <v>1.63</v>
@@ -17634,7 +17634,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ81">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR81">
         <v>2.05</v>
@@ -18249,7 +18249,7 @@
         <v>1</v>
       </c>
       <c r="AP84">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ84">
         <v>0.86</v>
@@ -18458,7 +18458,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ85">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AR85">
         <v>1.69</v>
@@ -19282,7 +19282,7 @@
         <v>1</v>
       </c>
       <c r="AQ89">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR89">
         <v>1.72</v>
@@ -21751,7 +21751,7 @@
         <v>0.83</v>
       </c>
       <c r="AP101">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AQ101">
         <v>0.86</v>
@@ -22784,7 +22784,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ106">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AR106">
         <v>1.34</v>
@@ -23066,6 +23066,418 @@
       </c>
       <c r="BP107">
         <v>1.56</v>
+      </c>
+    </row>
+    <row r="108" spans="1:68">
+      <c r="A108" s="1">
+        <v>107</v>
+      </c>
+      <c r="B108">
+        <v>7779059</v>
+      </c>
+      <c r="C108" t="s">
+        <v>68</v>
+      </c>
+      <c r="D108" t="s">
+        <v>69</v>
+      </c>
+      <c r="E108" s="2">
+        <v>45843.41666666666</v>
+      </c>
+      <c r="F108">
+        <v>14</v>
+      </c>
+      <c r="G108" t="s">
+        <v>77</v>
+      </c>
+      <c r="H108" t="s">
+        <v>85</v>
+      </c>
+      <c r="I108">
+        <v>0</v>
+      </c>
+      <c r="J108">
+        <v>0</v>
+      </c>
+      <c r="K108">
+        <v>0</v>
+      </c>
+      <c r="L108">
+        <v>0</v>
+      </c>
+      <c r="M108">
+        <v>0</v>
+      </c>
+      <c r="N108">
+        <v>0</v>
+      </c>
+      <c r="O108" t="s">
+        <v>86</v>
+      </c>
+      <c r="P108" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q108">
+        <v>3.2</v>
+      </c>
+      <c r="R108">
+        <v>2.05</v>
+      </c>
+      <c r="S108">
+        <v>3.1</v>
+      </c>
+      <c r="T108">
+        <v>1.4</v>
+      </c>
+      <c r="U108">
+        <v>2.7</v>
+      </c>
+      <c r="V108">
+        <v>2.8</v>
+      </c>
+      <c r="W108">
+        <v>1.37</v>
+      </c>
+      <c r="X108">
+        <v>7.25</v>
+      </c>
+      <c r="Y108">
+        <v>1.08</v>
+      </c>
+      <c r="Z108">
+        <v>2.69</v>
+      </c>
+      <c r="AA108">
+        <v>3.21</v>
+      </c>
+      <c r="AB108">
+        <v>2.29</v>
+      </c>
+      <c r="AC108">
+        <v>1.06</v>
+      </c>
+      <c r="AD108">
+        <v>9</v>
+      </c>
+      <c r="AE108">
+        <v>1.33</v>
+      </c>
+      <c r="AF108">
+        <v>3.35</v>
+      </c>
+      <c r="AG108">
+        <v>1.84</v>
+      </c>
+      <c r="AH108">
+        <v>1.86</v>
+      </c>
+      <c r="AI108">
+        <v>1.75</v>
+      </c>
+      <c r="AJ108">
+        <v>1.95</v>
+      </c>
+      <c r="AK108">
+        <v>1.47</v>
+      </c>
+      <c r="AL108">
+        <v>1.31</v>
+      </c>
+      <c r="AM108">
+        <v>1.46</v>
+      </c>
+      <c r="AN108">
+        <v>1.6</v>
+      </c>
+      <c r="AO108">
+        <v>1.29</v>
+      </c>
+      <c r="AP108">
+        <v>1.5</v>
+      </c>
+      <c r="AQ108">
+        <v>1.25</v>
+      </c>
+      <c r="AR108">
+        <v>2.16</v>
+      </c>
+      <c r="AS108">
+        <v>1.47</v>
+      </c>
+      <c r="AT108">
+        <v>3.63</v>
+      </c>
+      <c r="AU108">
+        <v>4</v>
+      </c>
+      <c r="AV108">
+        <v>2</v>
+      </c>
+      <c r="AW108">
+        <v>17</v>
+      </c>
+      <c r="AX108">
+        <v>9</v>
+      </c>
+      <c r="AY108">
+        <v>21</v>
+      </c>
+      <c r="AZ108">
+        <v>11</v>
+      </c>
+      <c r="BA108">
+        <v>6</v>
+      </c>
+      <c r="BB108">
+        <v>3</v>
+      </c>
+      <c r="BC108">
+        <v>9</v>
+      </c>
+      <c r="BD108">
+        <v>1.98</v>
+      </c>
+      <c r="BE108">
+        <v>6.75</v>
+      </c>
+      <c r="BF108">
+        <v>1.97</v>
+      </c>
+      <c r="BG108">
+        <v>1.19</v>
+      </c>
+      <c r="BH108">
+        <v>4.1</v>
+      </c>
+      <c r="BI108">
+        <v>1.33</v>
+      </c>
+      <c r="BJ108">
+        <v>2.95</v>
+      </c>
+      <c r="BK108">
+        <v>1.54</v>
+      </c>
+      <c r="BL108">
+        <v>2.3</v>
+      </c>
+      <c r="BM108">
+        <v>1.85</v>
+      </c>
+      <c r="BN108">
+        <v>1.83</v>
+      </c>
+      <c r="BO108">
+        <v>2.3</v>
+      </c>
+      <c r="BP108">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="109" spans="1:68">
+      <c r="A109" s="1">
+        <v>108</v>
+      </c>
+      <c r="B109">
+        <v>7779061</v>
+      </c>
+      <c r="C109" t="s">
+        <v>68</v>
+      </c>
+      <c r="D109" t="s">
+        <v>69</v>
+      </c>
+      <c r="E109" s="2">
+        <v>45843.41666666666</v>
+      </c>
+      <c r="F109">
+        <v>14</v>
+      </c>
+      <c r="G109" t="s">
+        <v>80</v>
+      </c>
+      <c r="H109" t="s">
+        <v>84</v>
+      </c>
+      <c r="I109">
+        <v>0</v>
+      </c>
+      <c r="J109">
+        <v>0</v>
+      </c>
+      <c r="K109">
+        <v>0</v>
+      </c>
+      <c r="L109">
+        <v>0</v>
+      </c>
+      <c r="M109">
+        <v>1</v>
+      </c>
+      <c r="N109">
+        <v>1</v>
+      </c>
+      <c r="O109" t="s">
+        <v>86</v>
+      </c>
+      <c r="P109" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q109">
+        <v>4.75</v>
+      </c>
+      <c r="R109">
+        <v>2.2</v>
+      </c>
+      <c r="S109">
+        <v>2.2</v>
+      </c>
+      <c r="T109">
+        <v>1.36</v>
+      </c>
+      <c r="U109">
+        <v>2.9</v>
+      </c>
+      <c r="V109">
+        <v>2.6</v>
+      </c>
+      <c r="W109">
+        <v>1.43</v>
+      </c>
+      <c r="X109">
+        <v>6.5</v>
+      </c>
+      <c r="Y109">
+        <v>1.1</v>
+      </c>
+      <c r="Z109">
+        <v>4.1</v>
+      </c>
+      <c r="AA109">
+        <v>3.45</v>
+      </c>
+      <c r="AB109">
+        <v>1.7</v>
+      </c>
+      <c r="AC109">
+        <v>1.06</v>
+      </c>
+      <c r="AD109">
+        <v>9.5</v>
+      </c>
+      <c r="AE109">
+        <v>1.3</v>
+      </c>
+      <c r="AF109">
+        <v>3.6</v>
+      </c>
+      <c r="AG109">
+        <v>1.86</v>
+      </c>
+      <c r="AH109">
+        <v>1.84</v>
+      </c>
+      <c r="AI109">
+        <v>1.82</v>
+      </c>
+      <c r="AJ109">
+        <v>1.85</v>
+      </c>
+      <c r="AK109">
+        <v>2.1</v>
+      </c>
+      <c r="AL109">
+        <v>1.25</v>
+      </c>
+      <c r="AM109">
+        <v>1.18</v>
+      </c>
+      <c r="AN109">
+        <v>0.83</v>
+      </c>
+      <c r="AO109">
+        <v>2</v>
+      </c>
+      <c r="AP109">
+        <v>0.71</v>
+      </c>
+      <c r="AQ109">
+        <v>2.13</v>
+      </c>
+      <c r="AR109">
+        <v>1.14</v>
+      </c>
+      <c r="AS109">
+        <v>1.71</v>
+      </c>
+      <c r="AT109">
+        <v>2.85</v>
+      </c>
+      <c r="AU109">
+        <v>0</v>
+      </c>
+      <c r="AV109">
+        <v>6</v>
+      </c>
+      <c r="AW109">
+        <v>9</v>
+      </c>
+      <c r="AX109">
+        <v>18</v>
+      </c>
+      <c r="AY109">
+        <v>9</v>
+      </c>
+      <c r="AZ109">
+        <v>24</v>
+      </c>
+      <c r="BA109">
+        <v>3</v>
+      </c>
+      <c r="BB109">
+        <v>7</v>
+      </c>
+      <c r="BC109">
+        <v>10</v>
+      </c>
+      <c r="BD109">
+        <v>2.55</v>
+      </c>
+      <c r="BE109">
+        <v>7</v>
+      </c>
+      <c r="BF109">
+        <v>1.6</v>
+      </c>
+      <c r="BG109">
+        <v>1.17</v>
+      </c>
+      <c r="BH109">
+        <v>4.35</v>
+      </c>
+      <c r="BI109">
+        <v>1.3</v>
+      </c>
+      <c r="BJ109">
+        <v>3.15</v>
+      </c>
+      <c r="BK109">
+        <v>1.5</v>
+      </c>
+      <c r="BL109">
+        <v>2.38</v>
+      </c>
+      <c r="BM109">
+        <v>1.79</v>
+      </c>
+      <c r="BN109">
+        <v>1.91</v>
+      </c>
+      <c r="BO109">
+        <v>2.18</v>
+      </c>
+      <c r="BP109">
+        <v>1.58</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="217">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -497,6 +497,9 @@
   </si>
   <si>
     <t>['45+2']</t>
+  </si>
+  <si>
+    <t>['90+1']</t>
   </si>
   <si>
     <t>['45+8']</t>
@@ -1023,7 +1026,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP109"/>
+  <dimension ref="A1:BP110"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1279,7 +1282,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q2">
         <v>3.5</v>
@@ -1769,7 +1772,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AQ4">
         <v>1.71</v>
@@ -1897,7 +1900,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q5">
         <v>2.5</v>
@@ -2103,7 +2106,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q6">
         <v>2.6</v>
@@ -2309,7 +2312,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -2515,7 +2518,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -2721,7 +2724,7 @@
         <v>86</v>
       </c>
       <c r="P9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3133,7 +3136,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q11">
         <v>4</v>
@@ -3545,7 +3548,7 @@
         <v>94</v>
       </c>
       <c r="P13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -3751,7 +3754,7 @@
         <v>86</v>
       </c>
       <c r="P14" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4038,7 +4041,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ15">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4163,7 +4166,7 @@
         <v>96</v>
       </c>
       <c r="P16" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q16">
         <v>2.55</v>
@@ -4369,7 +4372,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -4575,7 +4578,7 @@
         <v>86</v>
       </c>
       <c r="P18" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q18">
         <v>2.62</v>
@@ -5065,7 +5068,7 @@
         <v>3</v>
       </c>
       <c r="AP20">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AQ20">
         <v>1.5</v>
@@ -5193,7 +5196,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5605,7 +5608,7 @@
         <v>86</v>
       </c>
       <c r="P23" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q23">
         <v>2.62</v>
@@ -6223,7 +6226,7 @@
         <v>102</v>
       </c>
       <c r="P26" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q26">
         <v>3.2</v>
@@ -6429,7 +6432,7 @@
         <v>103</v>
       </c>
       <c r="P27" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q27">
         <v>1.72</v>
@@ -7253,7 +7256,7 @@
         <v>105</v>
       </c>
       <c r="P31" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7334,7 +7337,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ31">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR31">
         <v>1.47</v>
@@ -7459,7 +7462,7 @@
         <v>106</v>
       </c>
       <c r="P32" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q32">
         <v>2.88</v>
@@ -7949,7 +7952,7 @@
         <v>2</v>
       </c>
       <c r="AP34">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AQ34">
         <v>1.25</v>
@@ -8077,7 +8080,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8283,7 +8286,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q36">
         <v>4.75</v>
@@ -8489,7 +8492,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q37">
         <v>2</v>
@@ -8695,7 +8698,7 @@
         <v>111</v>
       </c>
       <c r="P38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q38">
         <v>4</v>
@@ -8901,7 +8904,7 @@
         <v>112</v>
       </c>
       <c r="P39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9519,7 +9522,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q42">
         <v>2.95</v>
@@ -9725,7 +9728,7 @@
         <v>115</v>
       </c>
       <c r="P43" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q43">
         <v>2</v>
@@ -10137,7 +10140,7 @@
         <v>117</v>
       </c>
       <c r="P45" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10961,7 +10964,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q49">
         <v>3</v>
@@ -11167,7 +11170,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q50">
         <v>3.75</v>
@@ -11248,7 +11251,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ50">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR50">
         <v>1.29</v>
@@ -11579,7 +11582,7 @@
         <v>86</v>
       </c>
       <c r="P52" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -11785,7 +11788,7 @@
         <v>86</v>
       </c>
       <c r="P53" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q53">
         <v>5.5</v>
@@ -12197,7 +12200,7 @@
         <v>125</v>
       </c>
       <c r="P55" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q55">
         <v>1.83</v>
@@ -12815,7 +12818,7 @@
         <v>127</v>
       </c>
       <c r="P58" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q58">
         <v>2.38</v>
@@ -12896,7 +12899,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ58">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR58">
         <v>1.92</v>
@@ -13227,7 +13230,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q60">
         <v>3.1</v>
@@ -13511,7 +13514,7 @@
         <v>1</v>
       </c>
       <c r="AP61">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AQ61">
         <v>1.33</v>
@@ -13845,7 +13848,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q63">
         <v>6</v>
@@ -14051,7 +14054,7 @@
         <v>132</v>
       </c>
       <c r="P64" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14257,7 +14260,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14463,7 +14466,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q66">
         <v>1.83</v>
@@ -14541,7 +14544,7 @@
         <v>1.25</v>
       </c>
       <c r="AP66">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AQ66">
         <v>0.86</v>
@@ -14669,7 +14672,7 @@
         <v>135</v>
       </c>
       <c r="P67" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q67">
         <v>3.1</v>
@@ -14875,7 +14878,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q68">
         <v>5.25</v>
@@ -15081,7 +15084,7 @@
         <v>103</v>
       </c>
       <c r="P69" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q69">
         <v>2.38</v>
@@ -15287,7 +15290,7 @@
         <v>137</v>
       </c>
       <c r="P70" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q70">
         <v>2.2</v>
@@ -15493,7 +15496,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q71">
         <v>2.95</v>
@@ -16192,7 +16195,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ74">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR74">
         <v>1.9</v>
@@ -16317,7 +16320,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q75">
         <v>3.95</v>
@@ -16935,7 +16938,7 @@
         <v>143</v>
       </c>
       <c r="P78" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q78">
         <v>2.75</v>
@@ -17141,7 +17144,7 @@
         <v>144</v>
       </c>
       <c r="P79" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -17553,7 +17556,7 @@
         <v>146</v>
       </c>
       <c r="P81" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q81">
         <v>2.45</v>
@@ -17631,7 +17634,7 @@
         <v>2</v>
       </c>
       <c r="AP81">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AQ81">
         <v>2.13</v>
@@ -17965,7 +17968,7 @@
         <v>127</v>
       </c>
       <c r="P83" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q83">
         <v>2.45</v>
@@ -18171,7 +18174,7 @@
         <v>147</v>
       </c>
       <c r="P84" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q84">
         <v>2.5</v>
@@ -18583,7 +18586,7 @@
         <v>118</v>
       </c>
       <c r="P86" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q86">
         <v>4.75</v>
@@ -18789,7 +18792,7 @@
         <v>86</v>
       </c>
       <c r="P87" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q87">
         <v>3.5</v>
@@ -19485,7 +19488,7 @@
         <v>1.8</v>
       </c>
       <c r="AP90">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AQ90">
         <v>1.5</v>
@@ -19613,7 +19616,7 @@
         <v>86</v>
       </c>
       <c r="P91" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q91">
         <v>3.4</v>
@@ -19819,7 +19822,7 @@
         <v>86</v>
       </c>
       <c r="P92" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q92">
         <v>2.9</v>
@@ -20231,7 +20234,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -20849,7 +20852,7 @@
         <v>148</v>
       </c>
       <c r="P97" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21136,7 +21139,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ98">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR98">
         <v>1.34</v>
@@ -21261,7 +21264,7 @@
         <v>154</v>
       </c>
       <c r="P99" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q99">
         <v>3.45</v>
@@ -21545,7 +21548,7 @@
         <v>0.8</v>
       </c>
       <c r="AP100">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AQ100">
         <v>0.67</v>
@@ -21673,7 +21676,7 @@
         <v>156</v>
       </c>
       <c r="P101" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q101">
         <v>3.4</v>
@@ -21879,7 +21882,7 @@
         <v>86</v>
       </c>
       <c r="P102" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22291,7 +22294,7 @@
         <v>158</v>
       </c>
       <c r="P104" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q104">
         <v>3.1</v>
@@ -22909,7 +22912,7 @@
         <v>160</v>
       </c>
       <c r="P107" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q107">
         <v>2.25</v>
@@ -23321,7 +23324,7 @@
         <v>86</v>
       </c>
       <c r="P109" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q109">
         <v>4.75</v>
@@ -23478,6 +23481,212 @@
       </c>
       <c r="BP109">
         <v>1.58</v>
+      </c>
+    </row>
+    <row r="110" spans="1:68">
+      <c r="A110" s="1">
+        <v>109</v>
+      </c>
+      <c r="B110">
+        <v>7779057</v>
+      </c>
+      <c r="C110" t="s">
+        <v>68</v>
+      </c>
+      <c r="D110" t="s">
+        <v>69</v>
+      </c>
+      <c r="E110" s="2">
+        <v>45843.52083333334</v>
+      </c>
+      <c r="F110">
+        <v>14</v>
+      </c>
+      <c r="G110" t="s">
+        <v>72</v>
+      </c>
+      <c r="H110" t="s">
+        <v>76</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
+      <c r="J110">
+        <v>0</v>
+      </c>
+      <c r="K110">
+        <v>0</v>
+      </c>
+      <c r="L110">
+        <v>1</v>
+      </c>
+      <c r="M110">
+        <v>0</v>
+      </c>
+      <c r="N110">
+        <v>1</v>
+      </c>
+      <c r="O110" t="s">
+        <v>161</v>
+      </c>
+      <c r="P110" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q110">
+        <v>1.8</v>
+      </c>
+      <c r="R110">
+        <v>2.6</v>
+      </c>
+      <c r="S110">
+        <v>7.5</v>
+      </c>
+      <c r="T110">
+        <v>1.29</v>
+      </c>
+      <c r="U110">
+        <v>3.5</v>
+      </c>
+      <c r="V110">
+        <v>2.25</v>
+      </c>
+      <c r="W110">
+        <v>1.57</v>
+      </c>
+      <c r="X110">
+        <v>5.5</v>
+      </c>
+      <c r="Y110">
+        <v>1.14</v>
+      </c>
+      <c r="Z110">
+        <v>1.33</v>
+      </c>
+      <c r="AA110">
+        <v>4.5</v>
+      </c>
+      <c r="AB110">
+        <v>7</v>
+      </c>
+      <c r="AC110">
+        <v>1.03</v>
+      </c>
+      <c r="AD110">
+        <v>12</v>
+      </c>
+      <c r="AE110">
+        <v>1.2</v>
+      </c>
+      <c r="AF110">
+        <v>4.5</v>
+      </c>
+      <c r="AG110">
+        <v>1.52</v>
+      </c>
+      <c r="AH110">
+        <v>2.35</v>
+      </c>
+      <c r="AI110">
+        <v>1.91</v>
+      </c>
+      <c r="AJ110">
+        <v>1.91</v>
+      </c>
+      <c r="AK110">
+        <v>1.09</v>
+      </c>
+      <c r="AL110">
+        <v>1.17</v>
+      </c>
+      <c r="AM110">
+        <v>2.95</v>
+      </c>
+      <c r="AN110">
+        <v>2.38</v>
+      </c>
+      <c r="AO110">
+        <v>0.17</v>
+      </c>
+      <c r="AP110">
+        <v>2.44</v>
+      </c>
+      <c r="AQ110">
+        <v>0.14</v>
+      </c>
+      <c r="AR110">
+        <v>2.17</v>
+      </c>
+      <c r="AS110">
+        <v>1.58</v>
+      </c>
+      <c r="AT110">
+        <v>3.75</v>
+      </c>
+      <c r="AU110">
+        <v>7</v>
+      </c>
+      <c r="AV110">
+        <v>0</v>
+      </c>
+      <c r="AW110">
+        <v>11</v>
+      </c>
+      <c r="AX110">
+        <v>11</v>
+      </c>
+      <c r="AY110">
+        <v>18</v>
+      </c>
+      <c r="AZ110">
+        <v>11</v>
+      </c>
+      <c r="BA110">
+        <v>9</v>
+      </c>
+      <c r="BB110">
+        <v>3</v>
+      </c>
+      <c r="BC110">
+        <v>12</v>
+      </c>
+      <c r="BD110">
+        <v>1.29</v>
+      </c>
+      <c r="BE110">
+        <v>8</v>
+      </c>
+      <c r="BF110">
+        <v>3.8</v>
+      </c>
+      <c r="BG110">
+        <v>1.15</v>
+      </c>
+      <c r="BH110">
+        <v>4.55</v>
+      </c>
+      <c r="BI110">
+        <v>1.29</v>
+      </c>
+      <c r="BJ110">
+        <v>3.2</v>
+      </c>
+      <c r="BK110">
+        <v>1.47</v>
+      </c>
+      <c r="BL110">
+        <v>2.48</v>
+      </c>
+      <c r="BM110">
+        <v>1.74</v>
+      </c>
+      <c r="BN110">
+        <v>1.98</v>
+      </c>
+      <c r="BO110">
+        <v>2.08</v>
+      </c>
+      <c r="BP110">
+        <v>1.65</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
@@ -21569,13 +21569,13 @@
         <v>0</v>
       </c>
       <c r="AW100">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX100">
         <v>5</v>
       </c>
       <c r="AY100">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ100">
         <v>5</v>
@@ -21769,22 +21769,22 @@
         <v>2.3</v>
       </c>
       <c r="AU101">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV101">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW101">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AX101">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AY101">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AZ101">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="BA101">
         <v>6</v>
@@ -21975,22 +21975,22 @@
         <v>3.29</v>
       </c>
       <c r="AU102">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV102">
         <v>6</v>
       </c>
       <c r="AW102">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AX102">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY102">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AZ102">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA102">
         <v>10</v>
@@ -22181,22 +22181,22 @@
         <v>2.98</v>
       </c>
       <c r="AU103">
+        <v>6</v>
+      </c>
+      <c r="AV103">
+        <v>0</v>
+      </c>
+      <c r="AW103">
         <v>5</v>
       </c>
-      <c r="AV103">
-        <v>0</v>
-      </c>
-      <c r="AW103">
-        <v>10</v>
-      </c>
       <c r="AX103">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AY103">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ103">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BA103">
         <v>2</v>
@@ -22390,19 +22390,19 @@
         <v>2</v>
       </c>
       <c r="AV104">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX104">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AY104">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ104">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="BA104">
         <v>1</v>
@@ -22593,22 +22593,22 @@
         <v>3</v>
       </c>
       <c r="AU105">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV105">
         <v>4</v>
       </c>
       <c r="AW105">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AX105">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY105">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AZ105">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA105">
         <v>9</v>
@@ -22799,22 +22799,22 @@
         <v>2.78</v>
       </c>
       <c r="AU106">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV106">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AW106">
+        <v>12</v>
+      </c>
+      <c r="AX106">
+        <v>3</v>
+      </c>
+      <c r="AY106">
         <v>15</v>
       </c>
-      <c r="AX106">
-        <v>6</v>
-      </c>
-      <c r="AY106">
-        <v>19</v>
-      </c>
       <c r="AZ106">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA106">
         <v>8</v>
@@ -23005,22 +23005,22 @@
         <v>2.76</v>
       </c>
       <c r="AU107">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AV107">
         <v>4</v>
       </c>
       <c r="AW107">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AX107">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY107">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="AZ107">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA107">
         <v>11</v>
@@ -23205,10 +23205,10 @@
         <v>2.16</v>
       </c>
       <c r="AS108">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AT108">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="AU108">
         <v>4</v>
@@ -23408,13 +23408,13 @@
         <v>2.13</v>
       </c>
       <c r="AR109">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AS109">
         <v>1.71</v>
       </c>
       <c r="AT109">
-        <v>2.85</v>
+        <v>2.74</v>
       </c>
       <c r="AU109">
         <v>0</v>
@@ -23614,13 +23614,13 @@
         <v>0.14</v>
       </c>
       <c r="AR110">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
       <c r="AS110">
         <v>1.58</v>
       </c>
       <c r="AT110">
-        <v>3.75</v>
+        <v>3.64</v>
       </c>
       <c r="AU110">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
@@ -21569,13 +21569,13 @@
         <v>0</v>
       </c>
       <c r="AW100">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX100">
         <v>5</v>
       </c>
       <c r="AY100">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ100">
         <v>5</v>
@@ -21769,22 +21769,22 @@
         <v>2.3</v>
       </c>
       <c r="AU101">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV101">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW101">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AX101">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AY101">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AZ101">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="BA101">
         <v>6</v>
@@ -21975,22 +21975,22 @@
         <v>3.29</v>
       </c>
       <c r="AU102">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV102">
         <v>6</v>
       </c>
       <c r="AW102">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AX102">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY102">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AZ102">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA102">
         <v>10</v>
@@ -22181,22 +22181,22 @@
         <v>2.98</v>
       </c>
       <c r="AU103">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV103">
         <v>0</v>
       </c>
       <c r="AW103">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AX103">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AY103">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AZ103">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BA103">
         <v>2</v>
@@ -22390,19 +22390,19 @@
         <v>2</v>
       </c>
       <c r="AV104">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW104">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX104">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AY104">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ104">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="BA104">
         <v>1</v>
@@ -22593,22 +22593,22 @@
         <v>3</v>
       </c>
       <c r="AU105">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV105">
         <v>4</v>
       </c>
       <c r="AW105">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AX105">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY105">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AZ105">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA105">
         <v>9</v>
@@ -22799,22 +22799,22 @@
         <v>2.78</v>
       </c>
       <c r="AU106">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV106">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AW106">
+        <v>15</v>
+      </c>
+      <c r="AX106">
+        <v>6</v>
+      </c>
+      <c r="AY106">
+        <v>19</v>
+      </c>
+      <c r="AZ106">
         <v>12</v>
-      </c>
-      <c r="AX106">
-        <v>3</v>
-      </c>
-      <c r="AY106">
-        <v>15</v>
-      </c>
-      <c r="AZ106">
-        <v>11</v>
       </c>
       <c r="BA106">
         <v>8</v>
@@ -23005,22 +23005,22 @@
         <v>2.76</v>
       </c>
       <c r="AU107">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AV107">
         <v>4</v>
       </c>
       <c r="AW107">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="AX107">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY107">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="AZ107">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA107">
         <v>11</v>
@@ -23205,10 +23205,10 @@
         <v>2.16</v>
       </c>
       <c r="AS108">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AT108">
-        <v>3.6</v>
+        <v>3.63</v>
       </c>
       <c r="AU108">
         <v>4</v>
@@ -23408,13 +23408,13 @@
         <v>2.13</v>
       </c>
       <c r="AR109">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AS109">
         <v>1.71</v>
       </c>
       <c r="AT109">
-        <v>2.74</v>
+        <v>2.85</v>
       </c>
       <c r="AU109">
         <v>0</v>
@@ -23614,13 +23614,13 @@
         <v>0.14</v>
       </c>
       <c r="AR110">
-        <v>2.06</v>
+        <v>2.17</v>
       </c>
       <c r="AS110">
         <v>1.58</v>
       </c>
       <c r="AT110">
-        <v>3.64</v>
+        <v>3.75</v>
       </c>
       <c r="AU110">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="220">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -502,10 +502,16 @@
     <t>['90+1']</t>
   </si>
   <si>
-    <t>['45+8']</t>
+    <t>['38', '87', '90+3']</t>
   </si>
   <si>
     <t>['20', '29']</t>
+  </si>
+  <si>
+    <t>['10', '24', '26', '53', '88']</t>
+  </si>
+  <si>
+    <t>['45+8']</t>
   </si>
   <si>
     <t>['31', '78', '90']</t>
@@ -665,6 +671,9 @@
   </si>
   <si>
     <t>['59']</t>
+  </si>
+  <si>
+    <t>['4']</t>
   </si>
 </sst>
 </file>
@@ -1026,7 +1035,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP110"/>
+  <dimension ref="A1:BP114"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1282,7 +1291,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="Q2">
         <v>3.5</v>
@@ -1360,7 +1369,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ2">
         <v>1.25</v>
@@ -1978,7 +1987,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AQ5">
         <v>2.13</v>
@@ -2106,7 +2115,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q6">
         <v>2.6</v>
@@ -2312,7 +2321,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -2390,10 +2399,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
+        <v>1.5</v>
+      </c>
+      <c r="AQ7">
         <v>1.29</v>
-      </c>
-      <c r="AQ7">
-        <v>1.5</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2518,7 +2527,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -2599,7 +2608,7 @@
         <v>0.43</v>
       </c>
       <c r="AQ8">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2724,7 +2733,7 @@
         <v>86</v>
       </c>
       <c r="P9" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -2805,7 +2814,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ9">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3008,7 +3017,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ10">
         <v>0.67</v>
@@ -3136,7 +3145,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q11">
         <v>4</v>
@@ -3423,7 +3432,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ12">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3548,7 +3557,7 @@
         <v>94</v>
       </c>
       <c r="P13" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -3754,7 +3763,7 @@
         <v>86</v>
       </c>
       <c r="P14" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4166,7 +4175,7 @@
         <v>96</v>
       </c>
       <c r="P16" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q16">
         <v>2.55</v>
@@ -4372,7 +4381,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -4578,7 +4587,7 @@
         <v>86</v>
       </c>
       <c r="P18" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q18">
         <v>2.62</v>
@@ -4862,7 +4871,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AQ19">
         <v>1.33</v>
@@ -5196,7 +5205,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5483,7 +5492,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ22">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AR22">
         <v>1.54</v>
@@ -5608,7 +5617,7 @@
         <v>86</v>
       </c>
       <c r="P23" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q23">
         <v>2.62</v>
@@ -5892,7 +5901,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ24">
         <v>0.71</v>
@@ -6226,7 +6235,7 @@
         <v>102</v>
       </c>
       <c r="P26" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q26">
         <v>3.2</v>
@@ -6432,7 +6441,7 @@
         <v>103</v>
       </c>
       <c r="P27" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q27">
         <v>1.72</v>
@@ -6513,7 +6522,7 @@
         <v>2</v>
       </c>
       <c r="AQ27">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR27">
         <v>2.77</v>
@@ -7131,7 +7140,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ30">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AR30">
         <v>1.48</v>
@@ -7256,7 +7265,7 @@
         <v>105</v>
       </c>
       <c r="P31" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7462,7 +7471,7 @@
         <v>106</v>
       </c>
       <c r="P32" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q32">
         <v>2.88</v>
@@ -7540,10 +7549,10 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ32">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR32">
         <v>1.43</v>
@@ -7746,7 +7755,7 @@
         <v>1</v>
       </c>
       <c r="AP33">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ33">
         <v>1.63</v>
@@ -8080,7 +8089,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8158,10 +8167,10 @@
         <v>2</v>
       </c>
       <c r="AP35">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AQ35">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR35">
         <v>1.66</v>
@@ -8286,7 +8295,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q36">
         <v>4.75</v>
@@ -8364,7 +8373,7 @@
         <v>2</v>
       </c>
       <c r="AP36">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ36">
         <v>2.13</v>
@@ -8492,7 +8501,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q37">
         <v>2</v>
@@ -8573,7 +8582,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ37">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AR37">
         <v>1.56</v>
@@ -8698,7 +8707,7 @@
         <v>111</v>
       </c>
       <c r="P38" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q38">
         <v>4</v>
@@ -8779,7 +8788,7 @@
         <v>0.43</v>
       </c>
       <c r="AQ38">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AR38">
         <v>1.5</v>
@@ -8904,7 +8913,7 @@
         <v>112</v>
       </c>
       <c r="P39" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9394,7 +9403,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ41">
         <v>0.71</v>
@@ -9522,7 +9531,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q42">
         <v>2.95</v>
@@ -9728,7 +9737,7 @@
         <v>115</v>
       </c>
       <c r="P43" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q43">
         <v>2</v>
@@ -9809,7 +9818,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ43">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AR43">
         <v>1.41</v>
@@ -10140,7 +10149,7 @@
         <v>117</v>
       </c>
       <c r="P45" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10630,7 +10639,7 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ47">
         <v>1.63</v>
@@ -10964,7 +10973,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q49">
         <v>3</v>
@@ -11045,7 +11054,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ49">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR49">
         <v>1.44</v>
@@ -11170,7 +11179,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q50">
         <v>3.75</v>
@@ -11248,7 +11257,7 @@
         <v>0</v>
       </c>
       <c r="AP50">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ50">
         <v>0.14</v>
@@ -11454,10 +11463,10 @@
         <v>3</v>
       </c>
       <c r="AP51">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ51">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AR51">
         <v>1.87</v>
@@ -11582,7 +11591,7 @@
         <v>86</v>
       </c>
       <c r="P52" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -11663,7 +11672,7 @@
         <v>1</v>
       </c>
       <c r="AQ52">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR52">
         <v>1.74</v>
@@ -11788,7 +11797,7 @@
         <v>86</v>
       </c>
       <c r="P53" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q53">
         <v>5.5</v>
@@ -12200,7 +12209,7 @@
         <v>125</v>
       </c>
       <c r="P55" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q55">
         <v>1.83</v>
@@ -12484,7 +12493,7 @@
         <v>1</v>
       </c>
       <c r="AP56">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AQ56">
         <v>1.63</v>
@@ -12818,7 +12827,7 @@
         <v>127</v>
       </c>
       <c r="P58" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q58">
         <v>2.38</v>
@@ -13105,7 +13114,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ59">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR59">
         <v>1.46</v>
@@ -13230,7 +13239,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q60">
         <v>3.1</v>
@@ -13848,7 +13857,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q63">
         <v>6</v>
@@ -14054,7 +14063,7 @@
         <v>132</v>
       </c>
       <c r="P64" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14132,7 +14141,7 @@
         <v>1.5</v>
       </c>
       <c r="AP64">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ64">
         <v>1.5</v>
@@ -14260,7 +14269,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14338,7 +14347,7 @@
         <v>0.75</v>
       </c>
       <c r="AP65">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ65">
         <v>1.63</v>
@@ -14466,7 +14475,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q66">
         <v>1.83</v>
@@ -14547,7 +14556,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ66">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR66">
         <v>2.05</v>
@@ -14672,7 +14681,7 @@
         <v>135</v>
       </c>
       <c r="P67" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q67">
         <v>3.1</v>
@@ -14753,7 +14762,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ67">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AR67">
         <v>1.87</v>
@@ -14878,7 +14887,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q68">
         <v>5.25</v>
@@ -15084,7 +15093,7 @@
         <v>103</v>
       </c>
       <c r="P69" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q69">
         <v>2.38</v>
@@ -15165,7 +15174,7 @@
         <v>1</v>
       </c>
       <c r="AQ69">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AR69">
         <v>1.75</v>
@@ -15290,7 +15299,7 @@
         <v>137</v>
       </c>
       <c r="P70" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q70">
         <v>2.2</v>
@@ -15368,7 +15377,7 @@
         <v>1.75</v>
       </c>
       <c r="AP70">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AQ70">
         <v>1.43</v>
@@ -15496,7 +15505,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q71">
         <v>2.95</v>
@@ -15574,7 +15583,7 @@
         <v>1.75</v>
       </c>
       <c r="AP71">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ71">
         <v>2.13</v>
@@ -15780,7 +15789,7 @@
         <v>0</v>
       </c>
       <c r="AP72">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ72">
         <v>0.71</v>
@@ -16320,7 +16329,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q75">
         <v>3.95</v>
@@ -16938,7 +16947,7 @@
         <v>143</v>
       </c>
       <c r="P78" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q78">
         <v>2.75</v>
@@ -17144,7 +17153,7 @@
         <v>144</v>
       </c>
       <c r="P79" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -17428,7 +17437,7 @@
         <v>2</v>
       </c>
       <c r="AP80">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AQ80">
         <v>1.5</v>
@@ -17556,7 +17565,7 @@
         <v>146</v>
       </c>
       <c r="P81" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q81">
         <v>2.45</v>
@@ -17843,7 +17852,7 @@
         <v>2</v>
       </c>
       <c r="AQ82">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AR82">
         <v>2.4</v>
@@ -17968,7 +17977,7 @@
         <v>127</v>
       </c>
       <c r="P83" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q83">
         <v>2.45</v>
@@ -18174,7 +18183,7 @@
         <v>147</v>
       </c>
       <c r="P84" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q84">
         <v>2.5</v>
@@ -18255,7 +18264,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ84">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR84">
         <v>2.01</v>
@@ -18458,7 +18467,7 @@
         <v>1.6</v>
       </c>
       <c r="AP85">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ85">
         <v>1.25</v>
@@ -18586,7 +18595,7 @@
         <v>118</v>
       </c>
       <c r="P86" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q86">
         <v>4.75</v>
@@ -18664,7 +18673,7 @@
         <v>1.5</v>
       </c>
       <c r="AP86">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ86">
         <v>1.67</v>
@@ -18792,7 +18801,7 @@
         <v>86</v>
       </c>
       <c r="P87" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q87">
         <v>3.5</v>
@@ -18873,7 +18882,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ87">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AR87">
         <v>1.8</v>
@@ -19076,10 +19085,10 @@
         <v>1.5</v>
       </c>
       <c r="AP88">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ88">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR88">
         <v>1.53</v>
@@ -19491,7 +19500,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ90">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AR90">
         <v>2.14</v>
@@ -19616,7 +19625,7 @@
         <v>86</v>
       </c>
       <c r="P91" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q91">
         <v>3.4</v>
@@ -19822,7 +19831,7 @@
         <v>86</v>
       </c>
       <c r="P92" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q92">
         <v>2.9</v>
@@ -19900,7 +19909,7 @@
         <v>1.6</v>
       </c>
       <c r="AP92">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AQ92">
         <v>1.83</v>
@@ -20234,7 +20243,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -20518,7 +20527,7 @@
         <v>1.8</v>
       </c>
       <c r="AP95">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ95">
         <v>1.5</v>
@@ -20727,7 +20736,7 @@
         <v>2</v>
       </c>
       <c r="AQ96">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR96">
         <v>2.35</v>
@@ -20852,7 +20861,7 @@
         <v>148</v>
       </c>
       <c r="P97" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21264,7 +21273,7 @@
         <v>154</v>
       </c>
       <c r="P99" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q99">
         <v>3.45</v>
@@ -21345,7 +21354,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ99">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AR99">
         <v>1.73</v>
@@ -21676,7 +21685,7 @@
         <v>156</v>
       </c>
       <c r="P101" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q101">
         <v>3.4</v>
@@ -21757,7 +21766,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ101">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR101">
         <v>1.03</v>
@@ -21882,7 +21891,7 @@
         <v>86</v>
       </c>
       <c r="P102" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22294,7 +22303,7 @@
         <v>158</v>
       </c>
       <c r="P104" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q104">
         <v>3.1</v>
@@ -22912,7 +22921,7 @@
         <v>160</v>
       </c>
       <c r="P107" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q107">
         <v>2.25</v>
@@ -22990,7 +22999,7 @@
         <v>1.4</v>
       </c>
       <c r="AP107">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ107">
         <v>1.33</v>
@@ -23324,7 +23333,7 @@
         <v>86</v>
       </c>
       <c r="P109" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q109">
         <v>4.75</v>
@@ -23687,6 +23696,830 @@
       </c>
       <c r="BP110">
         <v>1.65</v>
+      </c>
+    </row>
+    <row r="111" spans="1:68">
+      <c r="A111" s="1">
+        <v>110</v>
+      </c>
+      <c r="B111">
+        <v>7779060</v>
+      </c>
+      <c r="C111" t="s">
+        <v>68</v>
+      </c>
+      <c r="D111" t="s">
+        <v>69</v>
+      </c>
+      <c r="E111" s="2">
+        <v>45844.375</v>
+      </c>
+      <c r="F111">
+        <v>14</v>
+      </c>
+      <c r="G111" t="s">
+        <v>78</v>
+      </c>
+      <c r="H111" t="s">
+        <v>79</v>
+      </c>
+      <c r="I111">
+        <v>1</v>
+      </c>
+      <c r="J111">
+        <v>1</v>
+      </c>
+      <c r="K111">
+        <v>2</v>
+      </c>
+      <c r="L111">
+        <v>3</v>
+      </c>
+      <c r="M111">
+        <v>1</v>
+      </c>
+      <c r="N111">
+        <v>4</v>
+      </c>
+      <c r="O111" t="s">
+        <v>162</v>
+      </c>
+      <c r="P111" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q111">
+        <v>2.38</v>
+      </c>
+      <c r="R111">
+        <v>2.38</v>
+      </c>
+      <c r="S111">
+        <v>4.33</v>
+      </c>
+      <c r="T111">
+        <v>1.3</v>
+      </c>
+      <c r="U111">
+        <v>3.4</v>
+      </c>
+      <c r="V111">
+        <v>2.5</v>
+      </c>
+      <c r="W111">
+        <v>1.5</v>
+      </c>
+      <c r="X111">
+        <v>6</v>
+      </c>
+      <c r="Y111">
+        <v>1.13</v>
+      </c>
+      <c r="Z111">
+        <v>1.64</v>
+      </c>
+      <c r="AA111">
+        <v>3.68</v>
+      </c>
+      <c r="AB111">
+        <v>4.2</v>
+      </c>
+      <c r="AC111">
+        <v>1.01</v>
+      </c>
+      <c r="AD111">
+        <v>13</v>
+      </c>
+      <c r="AE111">
+        <v>1.17</v>
+      </c>
+      <c r="AF111">
+        <v>4.5</v>
+      </c>
+      <c r="AG111">
+        <v>1.65</v>
+      </c>
+      <c r="AH111">
+        <v>2.1</v>
+      </c>
+      <c r="AI111">
+        <v>1.62</v>
+      </c>
+      <c r="AJ111">
+        <v>2.2</v>
+      </c>
+      <c r="AK111">
+        <v>1.22</v>
+      </c>
+      <c r="AL111">
+        <v>1.25</v>
+      </c>
+      <c r="AM111">
+        <v>2</v>
+      </c>
+      <c r="AN111">
+        <v>1.17</v>
+      </c>
+      <c r="AO111">
+        <v>0.86</v>
+      </c>
+      <c r="AP111">
+        <v>1.43</v>
+      </c>
+      <c r="AQ111">
+        <v>0.75</v>
+      </c>
+      <c r="AR111">
+        <v>1.57</v>
+      </c>
+      <c r="AS111">
+        <v>1.39</v>
+      </c>
+      <c r="AT111">
+        <v>2.96</v>
+      </c>
+      <c r="AU111">
+        <v>6</v>
+      </c>
+      <c r="AV111">
+        <v>5</v>
+      </c>
+      <c r="AW111">
+        <v>6</v>
+      </c>
+      <c r="AX111">
+        <v>6</v>
+      </c>
+      <c r="AY111">
+        <v>12</v>
+      </c>
+      <c r="AZ111">
+        <v>11</v>
+      </c>
+      <c r="BA111">
+        <v>4</v>
+      </c>
+      <c r="BB111">
+        <v>5</v>
+      </c>
+      <c r="BC111">
+        <v>9</v>
+      </c>
+      <c r="BD111">
+        <v>1.43</v>
+      </c>
+      <c r="BE111">
+        <v>7.5</v>
+      </c>
+      <c r="BF111">
+        <v>3.05</v>
+      </c>
+      <c r="BG111">
+        <v>1.14</v>
+      </c>
+      <c r="BH111">
+        <v>4.8</v>
+      </c>
+      <c r="BI111">
+        <v>1.25</v>
+      </c>
+      <c r="BJ111">
+        <v>3.4</v>
+      </c>
+      <c r="BK111">
+        <v>1.44</v>
+      </c>
+      <c r="BL111">
+        <v>2.55</v>
+      </c>
+      <c r="BM111">
+        <v>1.68</v>
+      </c>
+      <c r="BN111">
+        <v>2.05</v>
+      </c>
+      <c r="BO111">
+        <v>2.05</v>
+      </c>
+      <c r="BP111">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="112" spans="1:68">
+      <c r="A112" s="1">
+        <v>111</v>
+      </c>
+      <c r="B112">
+        <v>7779063</v>
+      </c>
+      <c r="C112" t="s">
+        <v>68</v>
+      </c>
+      <c r="D112" t="s">
+        <v>69</v>
+      </c>
+      <c r="E112" s="2">
+        <v>45844.375</v>
+      </c>
+      <c r="F112">
+        <v>14</v>
+      </c>
+      <c r="G112" t="s">
+        <v>75</v>
+      </c>
+      <c r="H112" t="s">
+        <v>81</v>
+      </c>
+      <c r="I112">
+        <v>2</v>
+      </c>
+      <c r="J112">
+        <v>0</v>
+      </c>
+      <c r="K112">
+        <v>2</v>
+      </c>
+      <c r="L112">
+        <v>2</v>
+      </c>
+      <c r="M112">
+        <v>0</v>
+      </c>
+      <c r="N112">
+        <v>2</v>
+      </c>
+      <c r="O112" t="s">
+        <v>163</v>
+      </c>
+      <c r="P112" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q112">
+        <v>5.5</v>
+      </c>
+      <c r="R112">
+        <v>2.1</v>
+      </c>
+      <c r="S112">
+        <v>2.3</v>
+      </c>
+      <c r="T112">
+        <v>1.44</v>
+      </c>
+      <c r="U112">
+        <v>2.63</v>
+      </c>
+      <c r="V112">
+        <v>3.25</v>
+      </c>
+      <c r="W112">
+        <v>1.33</v>
+      </c>
+      <c r="X112">
+        <v>9</v>
+      </c>
+      <c r="Y112">
+        <v>1.07</v>
+      </c>
+      <c r="Z112">
+        <v>4.8</v>
+      </c>
+      <c r="AA112">
+        <v>3.34</v>
+      </c>
+      <c r="AB112">
+        <v>1.64</v>
+      </c>
+      <c r="AC112">
+        <v>1.07</v>
+      </c>
+      <c r="AD112">
+        <v>8.5</v>
+      </c>
+      <c r="AE112">
+        <v>1.38</v>
+      </c>
+      <c r="AF112">
+        <v>3.1</v>
+      </c>
+      <c r="AG112">
+        <v>1.93</v>
+      </c>
+      <c r="AH112">
+        <v>1.77</v>
+      </c>
+      <c r="AI112">
+        <v>2.05</v>
+      </c>
+      <c r="AJ112">
+        <v>1.7</v>
+      </c>
+      <c r="AK112">
+        <v>2.15</v>
+      </c>
+      <c r="AL112">
+        <v>1.22</v>
+      </c>
+      <c r="AM112">
+        <v>1.14</v>
+      </c>
+      <c r="AN112">
+        <v>1.29</v>
+      </c>
+      <c r="AO112">
+        <v>1.88</v>
+      </c>
+      <c r="AP112">
+        <v>1.5</v>
+      </c>
+      <c r="AQ112">
+        <v>1.67</v>
+      </c>
+      <c r="AR112">
+        <v>1.29</v>
+      </c>
+      <c r="AS112">
+        <v>1.2</v>
+      </c>
+      <c r="AT112">
+        <v>2.49</v>
+      </c>
+      <c r="AU112">
+        <v>3</v>
+      </c>
+      <c r="AV112">
+        <v>7</v>
+      </c>
+      <c r="AW112">
+        <v>5</v>
+      </c>
+      <c r="AX112">
+        <v>9</v>
+      </c>
+      <c r="AY112">
+        <v>8</v>
+      </c>
+      <c r="AZ112">
+        <v>16</v>
+      </c>
+      <c r="BA112">
+        <v>2</v>
+      </c>
+      <c r="BB112">
+        <v>8</v>
+      </c>
+      <c r="BC112">
+        <v>10</v>
+      </c>
+      <c r="BD112">
+        <v>3.2</v>
+      </c>
+      <c r="BE112">
+        <v>7.5</v>
+      </c>
+      <c r="BF112">
+        <v>1.4</v>
+      </c>
+      <c r="BG112">
+        <v>1.28</v>
+      </c>
+      <c r="BH112">
+        <v>3.3</v>
+      </c>
+      <c r="BI112">
+        <v>1.48</v>
+      </c>
+      <c r="BJ112">
+        <v>2.43</v>
+      </c>
+      <c r="BK112">
+        <v>1.76</v>
+      </c>
+      <c r="BL112">
+        <v>1.93</v>
+      </c>
+      <c r="BM112">
+        <v>2.18</v>
+      </c>
+      <c r="BN112">
+        <v>1.58</v>
+      </c>
+      <c r="BO112">
+        <v>2.8</v>
+      </c>
+      <c r="BP112">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="113" spans="1:68">
+      <c r="A113" s="1">
+        <v>112</v>
+      </c>
+      <c r="B113">
+        <v>7779058</v>
+      </c>
+      <c r="C113" t="s">
+        <v>68</v>
+      </c>
+      <c r="D113" t="s">
+        <v>69</v>
+      </c>
+      <c r="E113" s="2">
+        <v>45844.47916666666</v>
+      </c>
+      <c r="F113">
+        <v>14</v>
+      </c>
+      <c r="G113" t="s">
+        <v>73</v>
+      </c>
+      <c r="H113" t="s">
+        <v>71</v>
+      </c>
+      <c r="I113">
+        <v>0</v>
+      </c>
+      <c r="J113">
+        <v>1</v>
+      </c>
+      <c r="K113">
+        <v>1</v>
+      </c>
+      <c r="L113">
+        <v>0</v>
+      </c>
+      <c r="M113">
+        <v>2</v>
+      </c>
+      <c r="N113">
+        <v>2</v>
+      </c>
+      <c r="O113" t="s">
+        <v>86</v>
+      </c>
+      <c r="P113" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q113">
+        <v>2.3</v>
+      </c>
+      <c r="R113">
+        <v>2.4</v>
+      </c>
+      <c r="S113">
+        <v>4.33</v>
+      </c>
+      <c r="T113">
+        <v>1.29</v>
+      </c>
+      <c r="U113">
+        <v>3.5</v>
+      </c>
+      <c r="V113">
+        <v>2.25</v>
+      </c>
+      <c r="W113">
+        <v>1.57</v>
+      </c>
+      <c r="X113">
+        <v>5.5</v>
+      </c>
+      <c r="Y113">
+        <v>1.14</v>
+      </c>
+      <c r="Z113">
+        <v>1.85</v>
+      </c>
+      <c r="AA113">
+        <v>3.55</v>
+      </c>
+      <c r="AB113">
+        <v>3.38</v>
+      </c>
+      <c r="AC113">
+        <v>1.04</v>
+      </c>
+      <c r="AD113">
+        <v>11</v>
+      </c>
+      <c r="AE113">
+        <v>1.2</v>
+      </c>
+      <c r="AF113">
+        <v>4.5</v>
+      </c>
+      <c r="AG113">
+        <v>1.55</v>
+      </c>
+      <c r="AH113">
+        <v>2.2</v>
+      </c>
+      <c r="AI113">
+        <v>1.57</v>
+      </c>
+      <c r="AJ113">
+        <v>2.25</v>
+      </c>
+      <c r="AK113">
+        <v>1.22</v>
+      </c>
+      <c r="AL113">
+        <v>1.2</v>
+      </c>
+      <c r="AM113">
+        <v>1.95</v>
+      </c>
+      <c r="AN113">
+        <v>2.29</v>
+      </c>
+      <c r="AO113">
+        <v>1.17</v>
+      </c>
+      <c r="AP113">
+        <v>2</v>
+      </c>
+      <c r="AQ113">
+        <v>1.43</v>
+      </c>
+      <c r="AR113">
+        <v>1.6</v>
+      </c>
+      <c r="AS113">
+        <v>1.75</v>
+      </c>
+      <c r="AT113">
+        <v>3.35</v>
+      </c>
+      <c r="AU113">
+        <v>4</v>
+      </c>
+      <c r="AV113">
+        <v>5</v>
+      </c>
+      <c r="AW113">
+        <v>9</v>
+      </c>
+      <c r="AX113">
+        <v>7</v>
+      </c>
+      <c r="AY113">
+        <v>13</v>
+      </c>
+      <c r="AZ113">
+        <v>12</v>
+      </c>
+      <c r="BA113">
+        <v>16</v>
+      </c>
+      <c r="BB113">
+        <v>0</v>
+      </c>
+      <c r="BC113">
+        <v>16</v>
+      </c>
+      <c r="BD113">
+        <v>1.71</v>
+      </c>
+      <c r="BE113">
+        <v>7</v>
+      </c>
+      <c r="BF113">
+        <v>2.33</v>
+      </c>
+      <c r="BG113">
+        <v>1.16</v>
+      </c>
+      <c r="BH113">
+        <v>4.6</v>
+      </c>
+      <c r="BI113">
+        <v>1.28</v>
+      </c>
+      <c r="BJ113">
+        <v>3.3</v>
+      </c>
+      <c r="BK113">
+        <v>1.47</v>
+      </c>
+      <c r="BL113">
+        <v>2.48</v>
+      </c>
+      <c r="BM113">
+        <v>1.74</v>
+      </c>
+      <c r="BN113">
+        <v>1.97</v>
+      </c>
+      <c r="BO113">
+        <v>2.12</v>
+      </c>
+      <c r="BP113">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="114" spans="1:68">
+      <c r="A114" s="1">
+        <v>113</v>
+      </c>
+      <c r="B114">
+        <v>7779056</v>
+      </c>
+      <c r="C114" t="s">
+        <v>68</v>
+      </c>
+      <c r="D114" t="s">
+        <v>69</v>
+      </c>
+      <c r="E114" s="2">
+        <v>45844.47916666666</v>
+      </c>
+      <c r="F114">
+        <v>14</v>
+      </c>
+      <c r="G114" t="s">
+        <v>70</v>
+      </c>
+      <c r="H114" t="s">
+        <v>83</v>
+      </c>
+      <c r="I114">
+        <v>3</v>
+      </c>
+      <c r="J114">
+        <v>0</v>
+      </c>
+      <c r="K114">
+        <v>3</v>
+      </c>
+      <c r="L114">
+        <v>5</v>
+      </c>
+      <c r="M114">
+        <v>1</v>
+      </c>
+      <c r="N114">
+        <v>6</v>
+      </c>
+      <c r="O114" t="s">
+        <v>164</v>
+      </c>
+      <c r="P114" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q114">
+        <v>2.2</v>
+      </c>
+      <c r="R114">
+        <v>2.3</v>
+      </c>
+      <c r="S114">
+        <v>5.5</v>
+      </c>
+      <c r="T114">
+        <v>1.36</v>
+      </c>
+      <c r="U114">
+        <v>3</v>
+      </c>
+      <c r="V114">
+        <v>2.63</v>
+      </c>
+      <c r="W114">
+        <v>1.44</v>
+      </c>
+      <c r="X114">
+        <v>7</v>
+      </c>
+      <c r="Y114">
+        <v>1.1</v>
+      </c>
+      <c r="Z114">
+        <v>1.79</v>
+      </c>
+      <c r="AA114">
+        <v>3.5</v>
+      </c>
+      <c r="AB114">
+        <v>3.64</v>
+      </c>
+      <c r="AC114">
+        <v>1.05</v>
+      </c>
+      <c r="AD114">
+        <v>10</v>
+      </c>
+      <c r="AE114">
+        <v>1.28</v>
+      </c>
+      <c r="AF114">
+        <v>3.75</v>
+      </c>
+      <c r="AG114">
+        <v>1.82</v>
+      </c>
+      <c r="AH114">
+        <v>1.88</v>
+      </c>
+      <c r="AI114">
+        <v>1.91</v>
+      </c>
+      <c r="AJ114">
+        <v>1.91</v>
+      </c>
+      <c r="AK114">
+        <v>1.17</v>
+      </c>
+      <c r="AL114">
+        <v>1.2</v>
+      </c>
+      <c r="AM114">
+        <v>2.2</v>
+      </c>
+      <c r="AN114">
+        <v>1</v>
+      </c>
+      <c r="AO114">
+        <v>1.5</v>
+      </c>
+      <c r="AP114">
+        <v>1.25</v>
+      </c>
+      <c r="AQ114">
+        <v>1.29</v>
+      </c>
+      <c r="AR114">
+        <v>1.85</v>
+      </c>
+      <c r="AS114">
+        <v>1.41</v>
+      </c>
+      <c r="AT114">
+        <v>3.26</v>
+      </c>
+      <c r="AU114">
+        <v>9</v>
+      </c>
+      <c r="AV114">
+        <v>5</v>
+      </c>
+      <c r="AW114">
+        <v>10</v>
+      </c>
+      <c r="AX114">
+        <v>9</v>
+      </c>
+      <c r="AY114">
+        <v>19</v>
+      </c>
+      <c r="AZ114">
+        <v>14</v>
+      </c>
+      <c r="BA114">
+        <v>7</v>
+      </c>
+      <c r="BB114">
+        <v>4</v>
+      </c>
+      <c r="BC114">
+        <v>11</v>
+      </c>
+      <c r="BD114">
+        <v>1.36</v>
+      </c>
+      <c r="BE114">
+        <v>7.5</v>
+      </c>
+      <c r="BF114">
+        <v>3.4</v>
+      </c>
+      <c r="BG114">
+        <v>1.2</v>
+      </c>
+      <c r="BH114">
+        <v>3.95</v>
+      </c>
+      <c r="BI114">
+        <v>1.35</v>
+      </c>
+      <c r="BJ114">
+        <v>2.9</v>
+      </c>
+      <c r="BK114">
+        <v>1.56</v>
+      </c>
+      <c r="BL114">
+        <v>2.23</v>
+      </c>
+      <c r="BM114">
+        <v>1.89</v>
+      </c>
+      <c r="BN114">
+        <v>1.8</v>
+      </c>
+      <c r="BO114">
+        <v>2.33</v>
+      </c>
+      <c r="BP114">
+        <v>1.52</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="220">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1035,7 +1035,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP114"/>
+  <dimension ref="A1:BP115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1578,7 +1578,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ3">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2193,7 +2193,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ6">
         <v>0.71</v>
@@ -5698,7 +5698,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ23">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR23">
         <v>1.22</v>
@@ -6931,7 +6931,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ29">
         <v>0.67</v>
@@ -8991,7 +8991,7 @@
         <v>1.5</v>
       </c>
       <c r="AP39">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ39">
         <v>1.71</v>
@@ -9200,7 +9200,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ40">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR40">
         <v>1.88</v>
@@ -11669,7 +11669,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ52">
         <v>1.43</v>
@@ -12290,7 +12290,7 @@
         <v>2</v>
       </c>
       <c r="AQ55">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR55">
         <v>2.33</v>
@@ -15171,7 +15171,7 @@
         <v>1.5</v>
       </c>
       <c r="AP69">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ69">
         <v>1.29</v>
@@ -15380,7 +15380,7 @@
         <v>2</v>
       </c>
       <c r="AQ70">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR70">
         <v>1.63</v>
@@ -16822,7 +16822,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ77">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR77">
         <v>1.37</v>
@@ -19291,7 +19291,7 @@
         <v>2.17</v>
       </c>
       <c r="AP89">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ89">
         <v>2.13</v>
@@ -20321,7 +20321,7 @@
         <v>1.17</v>
       </c>
       <c r="AP94">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ94">
         <v>1.63</v>
@@ -21972,7 +21972,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ102">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR102">
         <v>1.6</v>
@@ -24520,6 +24520,212 @@
       </c>
       <c r="BP114">
         <v>1.52</v>
+      </c>
+    </row>
+    <row r="115" spans="1:68">
+      <c r="A115" s="1">
+        <v>114</v>
+      </c>
+      <c r="B115">
+        <v>7779062</v>
+      </c>
+      <c r="C115" t="s">
+        <v>68</v>
+      </c>
+      <c r="D115" t="s">
+        <v>69</v>
+      </c>
+      <c r="E115" s="2">
+        <v>45845.58333333334</v>
+      </c>
+      <c r="F115">
+        <v>14</v>
+      </c>
+      <c r="G115" t="s">
+        <v>74</v>
+      </c>
+      <c r="H115" t="s">
+        <v>82</v>
+      </c>
+      <c r="I115">
+        <v>0</v>
+      </c>
+      <c r="J115">
+        <v>0</v>
+      </c>
+      <c r="K115">
+        <v>0</v>
+      </c>
+      <c r="L115">
+        <v>0</v>
+      </c>
+      <c r="M115">
+        <v>1</v>
+      </c>
+      <c r="N115">
+        <v>1</v>
+      </c>
+      <c r="O115" t="s">
+        <v>86</v>
+      </c>
+      <c r="P115" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q115">
+        <v>3</v>
+      </c>
+      <c r="R115">
+        <v>2.4</v>
+      </c>
+      <c r="S115">
+        <v>3</v>
+      </c>
+      <c r="T115">
+        <v>1.25</v>
+      </c>
+      <c r="U115">
+        <v>3.75</v>
+      </c>
+      <c r="V115">
+        <v>2.2</v>
+      </c>
+      <c r="W115">
+        <v>1.62</v>
+      </c>
+      <c r="X115">
+        <v>5</v>
+      </c>
+      <c r="Y115">
+        <v>1.17</v>
+      </c>
+      <c r="Z115">
+        <v>2.37</v>
+      </c>
+      <c r="AA115">
+        <v>3.5</v>
+      </c>
+      <c r="AB115">
+        <v>2.42</v>
+      </c>
+      <c r="AC115">
+        <v>1.01</v>
+      </c>
+      <c r="AD115">
+        <v>17</v>
+      </c>
+      <c r="AE115">
+        <v>1.18</v>
+      </c>
+      <c r="AF115">
+        <v>5</v>
+      </c>
+      <c r="AG115">
+        <v>1.65</v>
+      </c>
+      <c r="AH115">
+        <v>2.1</v>
+      </c>
+      <c r="AI115">
+        <v>1.44</v>
+      </c>
+      <c r="AJ115">
+        <v>2.63</v>
+      </c>
+      <c r="AK115">
+        <v>1.48</v>
+      </c>
+      <c r="AL115">
+        <v>1.22</v>
+      </c>
+      <c r="AM115">
+        <v>1.5</v>
+      </c>
+      <c r="AN115">
+        <v>1</v>
+      </c>
+      <c r="AO115">
+        <v>1.43</v>
+      </c>
+      <c r="AP115">
+        <v>0.88</v>
+      </c>
+      <c r="AQ115">
+        <v>1.63</v>
+      </c>
+      <c r="AR115">
+        <v>1.73</v>
+      </c>
+      <c r="AS115">
+        <v>1.64</v>
+      </c>
+      <c r="AT115">
+        <v>3.37</v>
+      </c>
+      <c r="AU115">
+        <v>5</v>
+      </c>
+      <c r="AV115">
+        <v>4</v>
+      </c>
+      <c r="AW115">
+        <v>10</v>
+      </c>
+      <c r="AX115">
+        <v>10</v>
+      </c>
+      <c r="AY115">
+        <v>15</v>
+      </c>
+      <c r="AZ115">
+        <v>14</v>
+      </c>
+      <c r="BA115">
+        <v>9</v>
+      </c>
+      <c r="BB115">
+        <v>4</v>
+      </c>
+      <c r="BC115">
+        <v>13</v>
+      </c>
+      <c r="BD115">
+        <v>1.95</v>
+      </c>
+      <c r="BE115">
+        <v>6.75</v>
+      </c>
+      <c r="BF115">
+        <v>2</v>
+      </c>
+      <c r="BG115">
+        <v>1.13</v>
+      </c>
+      <c r="BH115">
+        <v>4.9</v>
+      </c>
+      <c r="BI115">
+        <v>1.24</v>
+      </c>
+      <c r="BJ115">
+        <v>3.55</v>
+      </c>
+      <c r="BK115">
+        <v>1.41</v>
+      </c>
+      <c r="BL115">
+        <v>2.65</v>
+      </c>
+      <c r="BM115">
+        <v>1.66</v>
+      </c>
+      <c r="BN115">
+        <v>2.08</v>
+      </c>
+      <c r="BO115">
+        <v>1.98</v>
+      </c>
+      <c r="BP115">
+        <v>1.72</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="221">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -675,6 +675,9 @@
   <si>
     <t>['4']</t>
   </si>
+  <si>
+    <t>['40', '45']</t>
+  </si>
 </sst>
 </file>
 
@@ -1035,7 +1038,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP115"/>
+  <dimension ref="A1:BP116"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3017,7 +3020,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ10">
         <v>0.67</v>
@@ -4462,7 +4465,7 @@
         <v>2</v>
       </c>
       <c r="AQ17">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -6728,7 +6731,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ28">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AR28">
         <v>1.15</v>
@@ -7549,7 +7552,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ32">
         <v>1.43</v>
@@ -10024,7 +10027,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ44">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AR44">
         <v>1.7</v>
@@ -10639,7 +10642,7 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ47">
         <v>1.63</v>
@@ -13732,7 +13735,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ62">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AR62">
         <v>1.23</v>
@@ -14141,7 +14144,7 @@
         <v>1.5</v>
       </c>
       <c r="AP64">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ64">
         <v>1.5</v>
@@ -15789,7 +15792,7 @@
         <v>0</v>
       </c>
       <c r="AP72">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ72">
         <v>0.71</v>
@@ -18467,7 +18470,7 @@
         <v>1.6</v>
       </c>
       <c r="AP85">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ85">
         <v>1.25</v>
@@ -18676,7 +18679,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ86">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AR86">
         <v>1.3</v>
@@ -22590,7 +22593,7 @@
         <v>0.43</v>
       </c>
       <c r="AQ105">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AR105">
         <v>1.52</v>
@@ -23823,7 +23826,7 @@
         <v>0.86</v>
       </c>
       <c r="AP111">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ111">
         <v>0.75</v>
@@ -24726,6 +24729,212 @@
       </c>
       <c r="BP115">
         <v>1.72</v>
+      </c>
+    </row>
+    <row r="116" spans="1:68">
+      <c r="A116" s="1">
+        <v>115</v>
+      </c>
+      <c r="B116">
+        <v>7779067</v>
+      </c>
+      <c r="C116" t="s">
+        <v>68</v>
+      </c>
+      <c r="D116" t="s">
+        <v>69</v>
+      </c>
+      <c r="E116" s="2">
+        <v>45850.41666666666</v>
+      </c>
+      <c r="F116">
+        <v>15</v>
+      </c>
+      <c r="G116" t="s">
+        <v>78</v>
+      </c>
+      <c r="H116" t="s">
+        <v>73</v>
+      </c>
+      <c r="I116">
+        <v>1</v>
+      </c>
+      <c r="J116">
+        <v>2</v>
+      </c>
+      <c r="K116">
+        <v>3</v>
+      </c>
+      <c r="L116">
+        <v>1</v>
+      </c>
+      <c r="M116">
+        <v>2</v>
+      </c>
+      <c r="N116">
+        <v>3</v>
+      </c>
+      <c r="O116" t="s">
+        <v>123</v>
+      </c>
+      <c r="P116" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q116">
+        <v>3</v>
+      </c>
+      <c r="R116">
+        <v>2.25</v>
+      </c>
+      <c r="S116">
+        <v>3.25</v>
+      </c>
+      <c r="T116">
+        <v>1.33</v>
+      </c>
+      <c r="U116">
+        <v>3.25</v>
+      </c>
+      <c r="V116">
+        <v>2.63</v>
+      </c>
+      <c r="W116">
+        <v>1.44</v>
+      </c>
+      <c r="X116">
+        <v>7</v>
+      </c>
+      <c r="Y116">
+        <v>1.1</v>
+      </c>
+      <c r="Z116">
+        <v>2.4</v>
+      </c>
+      <c r="AA116">
+        <v>3.33</v>
+      </c>
+      <c r="AB116">
+        <v>2.49</v>
+      </c>
+      <c r="AC116">
+        <v>1.05</v>
+      </c>
+      <c r="AD116">
+        <v>10</v>
+      </c>
+      <c r="AE116">
+        <v>1.28</v>
+      </c>
+      <c r="AF116">
+        <v>3.8</v>
+      </c>
+      <c r="AG116">
+        <v>1.76</v>
+      </c>
+      <c r="AH116">
+        <v>1.94</v>
+      </c>
+      <c r="AI116">
+        <v>1.67</v>
+      </c>
+      <c r="AJ116">
+        <v>2.1</v>
+      </c>
+      <c r="AK116">
+        <v>1.44</v>
+      </c>
+      <c r="AL116">
+        <v>1.25</v>
+      </c>
+      <c r="AM116">
+        <v>1.53</v>
+      </c>
+      <c r="AN116">
+        <v>1.43</v>
+      </c>
+      <c r="AO116">
+        <v>1.67</v>
+      </c>
+      <c r="AP116">
+        <v>1.25</v>
+      </c>
+      <c r="AQ116">
+        <v>1.86</v>
+      </c>
+      <c r="AR116">
+        <v>1.55</v>
+      </c>
+      <c r="AS116">
+        <v>1.43</v>
+      </c>
+      <c r="AT116">
+        <v>2.98</v>
+      </c>
+      <c r="AU116">
+        <v>7</v>
+      </c>
+      <c r="AV116">
+        <v>4</v>
+      </c>
+      <c r="AW116">
+        <v>11</v>
+      </c>
+      <c r="AX116">
+        <v>7</v>
+      </c>
+      <c r="AY116">
+        <v>18</v>
+      </c>
+      <c r="AZ116">
+        <v>11</v>
+      </c>
+      <c r="BA116">
+        <v>7</v>
+      </c>
+      <c r="BB116">
+        <v>4</v>
+      </c>
+      <c r="BC116">
+        <v>11</v>
+      </c>
+      <c r="BD116">
+        <v>1.72</v>
+      </c>
+      <c r="BE116">
+        <v>6.75</v>
+      </c>
+      <c r="BF116">
+        <v>2.33</v>
+      </c>
+      <c r="BG116">
+        <v>1.15</v>
+      </c>
+      <c r="BH116">
+        <v>4.6</v>
+      </c>
+      <c r="BI116">
+        <v>1.27</v>
+      </c>
+      <c r="BJ116">
+        <v>3.3</v>
+      </c>
+      <c r="BK116">
+        <v>1.48</v>
+      </c>
+      <c r="BL116">
+        <v>2.48</v>
+      </c>
+      <c r="BM116">
+        <v>1.75</v>
+      </c>
+      <c r="BN116">
+        <v>1.95</v>
+      </c>
+      <c r="BO116">
+        <v>2.17</v>
+      </c>
+      <c r="BP116">
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="222">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -509,6 +509,9 @@
   </si>
   <si>
     <t>['10', '24', '26', '53', '88']</t>
+  </si>
+  <si>
+    <t>['32', '49', '81']</t>
   </si>
   <si>
     <t>['45+8']</t>
@@ -1038,7 +1041,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP116"/>
+  <dimension ref="A1:BP117"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1294,7 +1297,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q2">
         <v>3.5</v>
@@ -2118,7 +2121,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q6">
         <v>2.6</v>
@@ -2324,7 +2327,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -2530,7 +2533,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -2736,7 +2739,7 @@
         <v>86</v>
       </c>
       <c r="P9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3148,7 +3151,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q11">
         <v>4</v>
@@ -3560,7 +3563,7 @@
         <v>94</v>
       </c>
       <c r="P13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -3641,7 +3644,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ13">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3766,7 +3769,7 @@
         <v>86</v>
       </c>
       <c r="P14" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4178,7 +4181,7 @@
         <v>96</v>
       </c>
       <c r="P16" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q16">
         <v>2.55</v>
@@ -4384,7 +4387,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -4462,7 +4465,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ17">
         <v>1.86</v>
@@ -4590,7 +4593,7 @@
         <v>86</v>
       </c>
       <c r="P18" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q18">
         <v>2.62</v>
@@ -4877,7 +4880,7 @@
         <v>2</v>
       </c>
       <c r="AQ19">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR19">
         <v>2.16</v>
@@ -5208,7 +5211,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5620,7 +5623,7 @@
         <v>86</v>
       </c>
       <c r="P23" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q23">
         <v>2.62</v>
@@ -6238,7 +6241,7 @@
         <v>102</v>
       </c>
       <c r="P26" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q26">
         <v>3.2</v>
@@ -6444,7 +6447,7 @@
         <v>103</v>
       </c>
       <c r="P27" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q27">
         <v>1.72</v>
@@ -6522,7 +6525,7 @@
         <v>3</v>
       </c>
       <c r="AP27">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ27">
         <v>0.75</v>
@@ -7268,7 +7271,7 @@
         <v>105</v>
       </c>
       <c r="P31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7474,7 +7477,7 @@
         <v>106</v>
       </c>
       <c r="P32" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q32">
         <v>2.88</v>
@@ -8092,7 +8095,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8298,7 +8301,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q36">
         <v>4.75</v>
@@ -8504,7 +8507,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q37">
         <v>2</v>
@@ -8710,7 +8713,7 @@
         <v>111</v>
       </c>
       <c r="P38" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q38">
         <v>4</v>
@@ -8916,7 +8919,7 @@
         <v>112</v>
       </c>
       <c r="P39" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9534,7 +9537,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q42">
         <v>2.95</v>
@@ -9740,7 +9743,7 @@
         <v>115</v>
       </c>
       <c r="P43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q43">
         <v>2</v>
@@ -10152,7 +10155,7 @@
         <v>117</v>
       </c>
       <c r="P45" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10233,7 +10236,7 @@
         <v>0.43</v>
       </c>
       <c r="AQ45">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR45">
         <v>1.47</v>
@@ -10848,7 +10851,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ48">
         <v>0.71</v>
@@ -10976,7 +10979,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q49">
         <v>3</v>
@@ -11182,7 +11185,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q50">
         <v>3.75</v>
@@ -11594,7 +11597,7 @@
         <v>86</v>
       </c>
       <c r="P52" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -11800,7 +11803,7 @@
         <v>86</v>
       </c>
       <c r="P53" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q53">
         <v>5.5</v>
@@ -12212,7 +12215,7 @@
         <v>125</v>
       </c>
       <c r="P55" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q55">
         <v>1.83</v>
@@ -12290,7 +12293,7 @@
         <v>1.33</v>
       </c>
       <c r="AP55">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ55">
         <v>1.63</v>
@@ -12830,7 +12833,7 @@
         <v>127</v>
       </c>
       <c r="P58" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q58">
         <v>2.38</v>
@@ -13242,7 +13245,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q60">
         <v>3.1</v>
@@ -13529,7 +13532,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ61">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR61">
         <v>1.9</v>
@@ -13860,7 +13863,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q63">
         <v>6</v>
@@ -14066,7 +14069,7 @@
         <v>132</v>
       </c>
       <c r="P64" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14272,7 +14275,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14478,7 +14481,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q66">
         <v>1.83</v>
@@ -14684,7 +14687,7 @@
         <v>135</v>
       </c>
       <c r="P67" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q67">
         <v>3.1</v>
@@ -14890,7 +14893,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q68">
         <v>5.25</v>
@@ -15096,7 +15099,7 @@
         <v>103</v>
       </c>
       <c r="P69" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q69">
         <v>2.38</v>
@@ -15302,7 +15305,7 @@
         <v>137</v>
       </c>
       <c r="P70" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q70">
         <v>2.2</v>
@@ -15508,7 +15511,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q71">
         <v>2.95</v>
@@ -16332,7 +16335,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q75">
         <v>3.95</v>
@@ -16616,7 +16619,7 @@
         <v>1</v>
       </c>
       <c r="AP76">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ76">
         <v>0.67</v>
@@ -16950,7 +16953,7 @@
         <v>143</v>
       </c>
       <c r="P78" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q78">
         <v>2.75</v>
@@ -17031,7 +17034,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ78">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR78">
         <v>1.49</v>
@@ -17156,7 +17159,7 @@
         <v>144</v>
       </c>
       <c r="P79" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -17568,7 +17571,7 @@
         <v>146</v>
       </c>
       <c r="P81" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q81">
         <v>2.45</v>
@@ -17852,7 +17855,7 @@
         <v>2.2</v>
       </c>
       <c r="AP82">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ82">
         <v>1.67</v>
@@ -17980,7 +17983,7 @@
         <v>127</v>
       </c>
       <c r="P83" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q83">
         <v>2.45</v>
@@ -18186,7 +18189,7 @@
         <v>147</v>
       </c>
       <c r="P84" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q84">
         <v>2.5</v>
@@ -18598,7 +18601,7 @@
         <v>118</v>
       </c>
       <c r="P86" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q86">
         <v>4.75</v>
@@ -18804,7 +18807,7 @@
         <v>86</v>
       </c>
       <c r="P87" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q87">
         <v>3.5</v>
@@ -19628,7 +19631,7 @@
         <v>86</v>
       </c>
       <c r="P91" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q91">
         <v>3.4</v>
@@ -19834,7 +19837,7 @@
         <v>86</v>
       </c>
       <c r="P92" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q92">
         <v>2.9</v>
@@ -20246,7 +20249,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -20736,7 +20739,7 @@
         <v>1.4</v>
       </c>
       <c r="AP96">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ96">
         <v>1.43</v>
@@ -20864,7 +20867,7 @@
         <v>148</v>
       </c>
       <c r="P97" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21276,7 +21279,7 @@
         <v>154</v>
       </c>
       <c r="P99" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q99">
         <v>3.45</v>
@@ -21688,7 +21691,7 @@
         <v>156</v>
       </c>
       <c r="P101" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q101">
         <v>3.4</v>
@@ -21894,7 +21897,7 @@
         <v>86</v>
       </c>
       <c r="P102" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22306,7 +22309,7 @@
         <v>158</v>
       </c>
       <c r="P104" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q104">
         <v>3.1</v>
@@ -22924,7 +22927,7 @@
         <v>160</v>
       </c>
       <c r="P107" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q107">
         <v>2.25</v>
@@ -23005,7 +23008,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ107">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR107">
         <v>1.58</v>
@@ -23336,7 +23339,7 @@
         <v>86</v>
       </c>
       <c r="P109" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q109">
         <v>4.75</v>
@@ -23748,7 +23751,7 @@
         <v>162</v>
       </c>
       <c r="P111" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q111">
         <v>2.38</v>
@@ -24366,7 +24369,7 @@
         <v>164</v>
       </c>
       <c r="P114" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q114">
         <v>2.2</v>
@@ -24572,7 +24575,7 @@
         <v>86</v>
       </c>
       <c r="P115" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -24778,7 +24781,7 @@
         <v>123</v>
       </c>
       <c r="P116" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q116">
         <v>3</v>
@@ -24935,6 +24938,212 @@
       </c>
       <c r="BP116">
         <v>1.6</v>
+      </c>
+    </row>
+    <row r="117" spans="1:68">
+      <c r="A117" s="1">
+        <v>116</v>
+      </c>
+      <c r="B117">
+        <v>7779069</v>
+      </c>
+      <c r="C117" t="s">
+        <v>68</v>
+      </c>
+      <c r="D117" t="s">
+        <v>69</v>
+      </c>
+      <c r="E117" s="2">
+        <v>45850.52083333334</v>
+      </c>
+      <c r="F117">
+        <v>15</v>
+      </c>
+      <c r="G117" t="s">
+        <v>85</v>
+      </c>
+      <c r="H117" t="s">
+        <v>74</v>
+      </c>
+      <c r="I117">
+        <v>1</v>
+      </c>
+      <c r="J117">
+        <v>0</v>
+      </c>
+      <c r="K117">
+        <v>1</v>
+      </c>
+      <c r="L117">
+        <v>3</v>
+      </c>
+      <c r="M117">
+        <v>1</v>
+      </c>
+      <c r="N117">
+        <v>4</v>
+      </c>
+      <c r="O117" t="s">
+        <v>165</v>
+      </c>
+      <c r="P117" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q117">
+        <v>1.67</v>
+      </c>
+      <c r="R117">
+        <v>2.88</v>
+      </c>
+      <c r="S117">
+        <v>7.5</v>
+      </c>
+      <c r="T117">
+        <v>1.22</v>
+      </c>
+      <c r="U117">
+        <v>4</v>
+      </c>
+      <c r="V117">
+        <v>2</v>
+      </c>
+      <c r="W117">
+        <v>1.73</v>
+      </c>
+      <c r="X117">
+        <v>4.33</v>
+      </c>
+      <c r="Y117">
+        <v>1.2</v>
+      </c>
+      <c r="Z117">
+        <v>1.46</v>
+      </c>
+      <c r="AA117">
+        <v>3.93</v>
+      </c>
+      <c r="AB117">
+        <v>5.6</v>
+      </c>
+      <c r="AC117">
+        <v>1.03</v>
+      </c>
+      <c r="AD117">
+        <v>13</v>
+      </c>
+      <c r="AE117">
+        <v>1.13</v>
+      </c>
+      <c r="AF117">
+        <v>6</v>
+      </c>
+      <c r="AG117">
+        <v>1.61</v>
+      </c>
+      <c r="AH117">
+        <v>2.05</v>
+      </c>
+      <c r="AI117">
+        <v>1.8</v>
+      </c>
+      <c r="AJ117">
+        <v>1.95</v>
+      </c>
+      <c r="AK117">
+        <v>1.07</v>
+      </c>
+      <c r="AL117">
+        <v>1.1</v>
+      </c>
+      <c r="AM117">
+        <v>3.3</v>
+      </c>
+      <c r="AN117">
+        <v>2</v>
+      </c>
+      <c r="AO117">
+        <v>1.33</v>
+      </c>
+      <c r="AP117">
+        <v>2.13</v>
+      </c>
+      <c r="AQ117">
+        <v>1.14</v>
+      </c>
+      <c r="AR117">
+        <v>2.35</v>
+      </c>
+      <c r="AS117">
+        <v>1.15</v>
+      </c>
+      <c r="AT117">
+        <v>3.5</v>
+      </c>
+      <c r="AU117">
+        <v>8</v>
+      </c>
+      <c r="AV117">
+        <v>7</v>
+      </c>
+      <c r="AW117">
+        <v>9</v>
+      </c>
+      <c r="AX117">
+        <v>5</v>
+      </c>
+      <c r="AY117">
+        <v>17</v>
+      </c>
+      <c r="AZ117">
+        <v>12</v>
+      </c>
+      <c r="BA117">
+        <v>4</v>
+      </c>
+      <c r="BB117">
+        <v>2</v>
+      </c>
+      <c r="BC117">
+        <v>6</v>
+      </c>
+      <c r="BD117">
+        <v>1.16</v>
+      </c>
+      <c r="BE117">
+        <v>9.5</v>
+      </c>
+      <c r="BF117">
+        <v>5.4</v>
+      </c>
+      <c r="BG117">
+        <v>1.12</v>
+      </c>
+      <c r="BH117">
+        <v>5</v>
+      </c>
+      <c r="BI117">
+        <v>1.24</v>
+      </c>
+      <c r="BJ117">
+        <v>3.5</v>
+      </c>
+      <c r="BK117">
+        <v>1.44</v>
+      </c>
+      <c r="BL117">
+        <v>2.6</v>
+      </c>
+      <c r="BM117">
+        <v>1.71</v>
+      </c>
+      <c r="BN117">
+        <v>2.06</v>
+      </c>
+      <c r="BO117">
+        <v>2.1</v>
+      </c>
+      <c r="BP117">
+        <v>1.68</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="225">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -514,6 +514,12 @@
     <t>['32', '49', '81']</t>
   </si>
   <si>
+    <t>['62', '78']</t>
+  </si>
+  <si>
+    <t>['30', '60', '81']</t>
+  </si>
+  <si>
     <t>['45+8']</t>
   </si>
   <si>
@@ -680,6 +686,9 @@
   </si>
   <si>
     <t>['40', '45']</t>
+  </si>
+  <si>
+    <t>['52', '85']</t>
   </si>
 </sst>
 </file>
@@ -1041,7 +1050,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP117"/>
+  <dimension ref="A1:BP119"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1297,7 +1306,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q2">
         <v>3.5</v>
@@ -2121,7 +2130,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q6">
         <v>2.6</v>
@@ -2202,7 +2211,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ6">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2327,7 +2336,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -2533,7 +2542,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -2739,7 +2748,7 @@
         <v>86</v>
       </c>
       <c r="P9" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -2817,7 +2826,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ9">
         <v>1.67</v>
@@ -3151,7 +3160,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q11">
         <v>4</v>
@@ -3563,7 +3572,7 @@
         <v>94</v>
       </c>
       <c r="P13" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -3769,7 +3778,7 @@
         <v>86</v>
       </c>
       <c r="P14" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -3847,10 +3856,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AQ14">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4181,7 +4190,7 @@
         <v>96</v>
       </c>
       <c r="P16" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q16">
         <v>2.55</v>
@@ -4387,7 +4396,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -4593,7 +4602,7 @@
         <v>86</v>
       </c>
       <c r="P18" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q18">
         <v>2.62</v>
@@ -5211,7 +5220,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5495,7 +5504,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ22">
         <v>1.29</v>
@@ -5623,7 +5632,7 @@
         <v>86</v>
       </c>
       <c r="P23" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q23">
         <v>2.62</v>
@@ -5910,7 +5919,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ24">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR24">
         <v>0.88</v>
@@ -6241,7 +6250,7 @@
         <v>102</v>
       </c>
       <c r="P26" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q26">
         <v>3.2</v>
@@ -6322,7 +6331,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ26">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AR26">
         <v>1.49</v>
@@ -6447,7 +6456,7 @@
         <v>103</v>
       </c>
       <c r="P27" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q27">
         <v>1.72</v>
@@ -7271,7 +7280,7 @@
         <v>105</v>
       </c>
       <c r="P31" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7349,7 +7358,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AQ31">
         <v>0.14</v>
@@ -7477,7 +7486,7 @@
         <v>106</v>
       </c>
       <c r="P32" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q32">
         <v>2.88</v>
@@ -8095,7 +8104,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8301,7 +8310,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q36">
         <v>4.75</v>
@@ -8507,7 +8516,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q37">
         <v>2</v>
@@ -8713,7 +8722,7 @@
         <v>111</v>
       </c>
       <c r="P38" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q38">
         <v>4</v>
@@ -8919,7 +8928,7 @@
         <v>112</v>
       </c>
       <c r="P39" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9203,7 +9212,7 @@
         <v>1.5</v>
       </c>
       <c r="AP40">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ40">
         <v>1.63</v>
@@ -9412,7 +9421,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ41">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR41">
         <v>1.44</v>
@@ -9537,7 +9546,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q42">
         <v>2.95</v>
@@ -9618,7 +9627,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ42">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AR42">
         <v>1.86</v>
@@ -9743,7 +9752,7 @@
         <v>115</v>
       </c>
       <c r="P43" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q43">
         <v>2</v>
@@ -10155,7 +10164,7 @@
         <v>117</v>
       </c>
       <c r="P45" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10854,7 +10863,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ48">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR48">
         <v>2.55</v>
@@ -10979,7 +10988,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q49">
         <v>3</v>
@@ -11185,7 +11194,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q50">
         <v>3.75</v>
@@ -11597,7 +11606,7 @@
         <v>86</v>
       </c>
       <c r="P52" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -11803,7 +11812,7 @@
         <v>86</v>
       </c>
       <c r="P53" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q53">
         <v>5.5</v>
@@ -11884,7 +11893,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ53">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AR53">
         <v>1.36</v>
@@ -12215,7 +12224,7 @@
         <v>125</v>
       </c>
       <c r="P55" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q55">
         <v>1.83</v>
@@ -12705,7 +12714,7 @@
         <v>0.33</v>
       </c>
       <c r="AP57">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AQ57">
         <v>0.67</v>
@@ -12833,7 +12842,7 @@
         <v>127</v>
       </c>
       <c r="P58" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q58">
         <v>2.38</v>
@@ -12911,7 +12920,7 @@
         <v>0</v>
       </c>
       <c r="AP58">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ58">
         <v>0.14</v>
@@ -13245,7 +13254,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q60">
         <v>3.1</v>
@@ -13863,7 +13872,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q63">
         <v>6</v>
@@ -14069,7 +14078,7 @@
         <v>132</v>
       </c>
       <c r="P64" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14275,7 +14284,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14481,7 +14490,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q66">
         <v>1.83</v>
@@ -14687,7 +14696,7 @@
         <v>135</v>
       </c>
       <c r="P67" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q67">
         <v>3.1</v>
@@ -14893,7 +14902,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q68">
         <v>5.25</v>
@@ -15099,7 +15108,7 @@
         <v>103</v>
       </c>
       <c r="P69" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q69">
         <v>2.38</v>
@@ -15305,7 +15314,7 @@
         <v>137</v>
       </c>
       <c r="P70" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q70">
         <v>2.2</v>
@@ -15511,7 +15520,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q71">
         <v>2.95</v>
@@ -15798,7 +15807,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ72">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR72">
         <v>1.65</v>
@@ -16004,7 +16013,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ73">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AR73">
         <v>1.73</v>
@@ -16335,7 +16344,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q75">
         <v>3.95</v>
@@ -16953,7 +16962,7 @@
         <v>143</v>
       </c>
       <c r="P78" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q78">
         <v>2.75</v>
@@ -17159,7 +17168,7 @@
         <v>144</v>
       </c>
       <c r="P79" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -17571,7 +17580,7 @@
         <v>146</v>
       </c>
       <c r="P81" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q81">
         <v>2.45</v>
@@ -17983,7 +17992,7 @@
         <v>127</v>
       </c>
       <c r="P83" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q83">
         <v>2.45</v>
@@ -18064,7 +18073,7 @@
         <v>0.43</v>
       </c>
       <c r="AQ83">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR83">
         <v>1.49</v>
@@ -18189,7 +18198,7 @@
         <v>147</v>
       </c>
       <c r="P84" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q84">
         <v>2.5</v>
@@ -18267,7 +18276,7 @@
         <v>1</v>
       </c>
       <c r="AP84">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ84">
         <v>0.75</v>
@@ -18601,7 +18610,7 @@
         <v>118</v>
       </c>
       <c r="P86" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q86">
         <v>4.75</v>
@@ -18807,7 +18816,7 @@
         <v>86</v>
       </c>
       <c r="P87" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q87">
         <v>3.5</v>
@@ -18885,7 +18894,7 @@
         <v>2</v>
       </c>
       <c r="AP87">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AQ87">
         <v>1.67</v>
@@ -19631,7 +19640,7 @@
         <v>86</v>
       </c>
       <c r="P91" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q91">
         <v>3.4</v>
@@ -19709,7 +19718,7 @@
         <v>1.5</v>
       </c>
       <c r="AP91">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AQ91">
         <v>1.5</v>
@@ -19837,7 +19846,7 @@
         <v>86</v>
       </c>
       <c r="P92" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q92">
         <v>2.9</v>
@@ -19918,7 +19927,7 @@
         <v>2</v>
       </c>
       <c r="AQ92">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AR92">
         <v>1.6</v>
@@ -20124,7 +20133,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ93">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR93">
         <v>1.6</v>
@@ -20249,7 +20258,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -20867,7 +20876,7 @@
         <v>148</v>
       </c>
       <c r="P97" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -20945,7 +20954,7 @@
         <v>1.8</v>
       </c>
       <c r="AP97">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AQ97">
         <v>1.71</v>
@@ -21279,7 +21288,7 @@
         <v>154</v>
       </c>
       <c r="P99" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q99">
         <v>3.45</v>
@@ -21691,7 +21700,7 @@
         <v>156</v>
       </c>
       <c r="P101" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q101">
         <v>3.4</v>
@@ -21897,7 +21906,7 @@
         <v>86</v>
       </c>
       <c r="P102" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22309,7 +22318,7 @@
         <v>158</v>
       </c>
       <c r="P104" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q104">
         <v>3.1</v>
@@ -22927,7 +22936,7 @@
         <v>160</v>
       </c>
       <c r="P107" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q107">
         <v>2.25</v>
@@ -23211,7 +23220,7 @@
         <v>1.29</v>
       </c>
       <c r="AP108">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ108">
         <v>1.25</v>
@@ -23339,7 +23348,7 @@
         <v>86</v>
       </c>
       <c r="P109" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q109">
         <v>4.75</v>
@@ -23751,7 +23760,7 @@
         <v>162</v>
       </c>
       <c r="P111" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q111">
         <v>2.38</v>
@@ -24369,7 +24378,7 @@
         <v>164</v>
       </c>
       <c r="P114" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q114">
         <v>2.2</v>
@@ -24575,7 +24584,7 @@
         <v>86</v>
       </c>
       <c r="P115" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -24781,7 +24790,7 @@
         <v>123</v>
       </c>
       <c r="P116" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q116">
         <v>3</v>
@@ -25144,6 +25153,418 @@
       </c>
       <c r="BP117">
         <v>1.68</v>
+      </c>
+    </row>
+    <row r="118" spans="1:68">
+      <c r="A118" s="1">
+        <v>117</v>
+      </c>
+      <c r="B118">
+        <v>7779065</v>
+      </c>
+      <c r="C118" t="s">
+        <v>68</v>
+      </c>
+      <c r="D118" t="s">
+        <v>69</v>
+      </c>
+      <c r="E118" s="2">
+        <v>45851.375</v>
+      </c>
+      <c r="F118">
+        <v>15</v>
+      </c>
+      <c r="G118" t="s">
+        <v>82</v>
+      </c>
+      <c r="H118" t="s">
+        <v>80</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+      <c r="J118">
+        <v>0</v>
+      </c>
+      <c r="K118">
+        <v>0</v>
+      </c>
+      <c r="L118">
+        <v>2</v>
+      </c>
+      <c r="M118">
+        <v>0</v>
+      </c>
+      <c r="N118">
+        <v>2</v>
+      </c>
+      <c r="O118" t="s">
+        <v>166</v>
+      </c>
+      <c r="P118" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q118">
+        <v>2.25</v>
+      </c>
+      <c r="R118">
+        <v>2.38</v>
+      </c>
+      <c r="S118">
+        <v>4.75</v>
+      </c>
+      <c r="T118">
+        <v>1.3</v>
+      </c>
+      <c r="U118">
+        <v>3.4</v>
+      </c>
+      <c r="V118">
+        <v>2.5</v>
+      </c>
+      <c r="W118">
+        <v>1.5</v>
+      </c>
+      <c r="X118">
+        <v>6</v>
+      </c>
+      <c r="Y118">
+        <v>1.13</v>
+      </c>
+      <c r="Z118">
+        <v>1.76</v>
+      </c>
+      <c r="AA118">
+        <v>3.5</v>
+      </c>
+      <c r="AB118">
+        <v>3.77</v>
+      </c>
+      <c r="AC118">
+        <v>1.04</v>
+      </c>
+      <c r="AD118">
+        <v>11</v>
+      </c>
+      <c r="AE118">
+        <v>1.22</v>
+      </c>
+      <c r="AF118">
+        <v>4.2</v>
+      </c>
+      <c r="AG118">
+        <v>1.68</v>
+      </c>
+      <c r="AH118">
+        <v>2.05</v>
+      </c>
+      <c r="AI118">
+        <v>1.7</v>
+      </c>
+      <c r="AJ118">
+        <v>2.05</v>
+      </c>
+      <c r="AK118">
+        <v>1.2</v>
+      </c>
+      <c r="AL118">
+        <v>1.2</v>
+      </c>
+      <c r="AM118">
+        <v>2.05</v>
+      </c>
+      <c r="AN118">
+        <v>0.5</v>
+      </c>
+      <c r="AO118">
+        <v>0.71</v>
+      </c>
+      <c r="AP118">
+        <v>0.86</v>
+      </c>
+      <c r="AQ118">
+        <v>0.63</v>
+      </c>
+      <c r="AR118">
+        <v>1.72</v>
+      </c>
+      <c r="AS118">
+        <v>1.01</v>
+      </c>
+      <c r="AT118">
+        <v>2.73</v>
+      </c>
+      <c r="AU118">
+        <v>9</v>
+      </c>
+      <c r="AV118">
+        <v>4</v>
+      </c>
+      <c r="AW118">
+        <v>5</v>
+      </c>
+      <c r="AX118">
+        <v>5</v>
+      </c>
+      <c r="AY118">
+        <v>14</v>
+      </c>
+      <c r="AZ118">
+        <v>9</v>
+      </c>
+      <c r="BA118">
+        <v>12</v>
+      </c>
+      <c r="BB118">
+        <v>7</v>
+      </c>
+      <c r="BC118">
+        <v>19</v>
+      </c>
+      <c r="BD118">
+        <v>1.49</v>
+      </c>
+      <c r="BE118">
+        <v>7</v>
+      </c>
+      <c r="BF118">
+        <v>2.9</v>
+      </c>
+      <c r="BG118">
+        <v>1.09</v>
+      </c>
+      <c r="BH118">
+        <v>5.8</v>
+      </c>
+      <c r="BI118">
+        <v>1.19</v>
+      </c>
+      <c r="BJ118">
+        <v>4.1</v>
+      </c>
+      <c r="BK118">
+        <v>1.32</v>
+      </c>
+      <c r="BL118">
+        <v>3.05</v>
+      </c>
+      <c r="BM118">
+        <v>1.5</v>
+      </c>
+      <c r="BN118">
+        <v>2.33</v>
+      </c>
+      <c r="BO118">
+        <v>1.8</v>
+      </c>
+      <c r="BP118">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="119" spans="1:68">
+      <c r="A119" s="1">
+        <v>118</v>
+      </c>
+      <c r="B119">
+        <v>7779066</v>
+      </c>
+      <c r="C119" t="s">
+        <v>68</v>
+      </c>
+      <c r="D119" t="s">
+        <v>69</v>
+      </c>
+      <c r="E119" s="2">
+        <v>45851.375</v>
+      </c>
+      <c r="F119">
+        <v>15</v>
+      </c>
+      <c r="G119" t="s">
+        <v>77</v>
+      </c>
+      <c r="H119" t="s">
+        <v>72</v>
+      </c>
+      <c r="I119">
+        <v>1</v>
+      </c>
+      <c r="J119">
+        <v>0</v>
+      </c>
+      <c r="K119">
+        <v>1</v>
+      </c>
+      <c r="L119">
+        <v>3</v>
+      </c>
+      <c r="M119">
+        <v>2</v>
+      </c>
+      <c r="N119">
+        <v>5</v>
+      </c>
+      <c r="O119" t="s">
+        <v>167</v>
+      </c>
+      <c r="P119" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q119">
+        <v>3.4</v>
+      </c>
+      <c r="R119">
+        <v>2.2</v>
+      </c>
+      <c r="S119">
+        <v>3.1</v>
+      </c>
+      <c r="T119">
+        <v>1.4</v>
+      </c>
+      <c r="U119">
+        <v>2.75</v>
+      </c>
+      <c r="V119">
+        <v>2.75</v>
+      </c>
+      <c r="W119">
+        <v>1.4</v>
+      </c>
+      <c r="X119">
+        <v>8</v>
+      </c>
+      <c r="Y119">
+        <v>1.08</v>
+      </c>
+      <c r="Z119">
+        <v>2.63</v>
+      </c>
+      <c r="AA119">
+        <v>3.19</v>
+      </c>
+      <c r="AB119">
+        <v>2.35</v>
+      </c>
+      <c r="AC119">
+        <v>1.06</v>
+      </c>
+      <c r="AD119">
+        <v>9</v>
+      </c>
+      <c r="AE119">
+        <v>1.3</v>
+      </c>
+      <c r="AF119">
+        <v>3.5</v>
+      </c>
+      <c r="AG119">
+        <v>1.84</v>
+      </c>
+      <c r="AH119">
+        <v>1.86</v>
+      </c>
+      <c r="AI119">
+        <v>1.75</v>
+      </c>
+      <c r="AJ119">
+        <v>2</v>
+      </c>
+      <c r="AK119">
+        <v>1.53</v>
+      </c>
+      <c r="AL119">
+        <v>1.25</v>
+      </c>
+      <c r="AM119">
+        <v>1.42</v>
+      </c>
+      <c r="AN119">
+        <v>1.5</v>
+      </c>
+      <c r="AO119">
+        <v>1.83</v>
+      </c>
+      <c r="AP119">
+        <v>1.71</v>
+      </c>
+      <c r="AQ119">
+        <v>1.57</v>
+      </c>
+      <c r="AR119">
+        <v>2.15</v>
+      </c>
+      <c r="AS119">
+        <v>1.86</v>
+      </c>
+      <c r="AT119">
+        <v>4.01</v>
+      </c>
+      <c r="AU119">
+        <v>12</v>
+      </c>
+      <c r="AV119">
+        <v>5</v>
+      </c>
+      <c r="AW119">
+        <v>8</v>
+      </c>
+      <c r="AX119">
+        <v>3</v>
+      </c>
+      <c r="AY119">
+        <v>20</v>
+      </c>
+      <c r="AZ119">
+        <v>8</v>
+      </c>
+      <c r="BA119">
+        <v>11</v>
+      </c>
+      <c r="BB119">
+        <v>1</v>
+      </c>
+      <c r="BC119">
+        <v>12</v>
+      </c>
+      <c r="BD119">
+        <v>1.95</v>
+      </c>
+      <c r="BE119">
+        <v>6.4</v>
+      </c>
+      <c r="BF119">
+        <v>2.05</v>
+      </c>
+      <c r="BG119">
+        <v>1.14</v>
+      </c>
+      <c r="BH119">
+        <v>4.8</v>
+      </c>
+      <c r="BI119">
+        <v>1.27</v>
+      </c>
+      <c r="BJ119">
+        <v>3.3</v>
+      </c>
+      <c r="BK119">
+        <v>1.45</v>
+      </c>
+      <c r="BL119">
+        <v>2.55</v>
+      </c>
+      <c r="BM119">
+        <v>1.73</v>
+      </c>
+      <c r="BN119">
+        <v>1.98</v>
+      </c>
+      <c r="BO119">
+        <v>2.12</v>
+      </c>
+      <c r="BP119">
+        <v>1.63</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="228">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -520,6 +520,12 @@
     <t>['30', '60', '81']</t>
   </si>
   <si>
+    <t>['30', '64', '90+2']</t>
+  </si>
+  <si>
+    <t>['17', '19', '45', '48']</t>
+  </si>
+  <si>
     <t>['45+8']</t>
   </si>
   <si>
@@ -689,6 +695,9 @@
   </si>
   <si>
     <t>['52', '85']</t>
+  </si>
+  <si>
+    <t>['90+3']</t>
   </si>
 </sst>
 </file>
@@ -1050,7 +1059,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP119"/>
+  <dimension ref="A1:BP122"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1306,7 +1315,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q2">
         <v>3.5</v>
@@ -1590,7 +1599,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ3">
         <v>1.63</v>
@@ -2130,7 +2139,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q6">
         <v>2.6</v>
@@ -2336,7 +2345,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -2417,7 +2426,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ7">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2542,7 +2551,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -2620,7 +2629,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="AQ8">
         <v>0.75</v>
@@ -2748,7 +2757,7 @@
         <v>86</v>
       </c>
       <c r="P9" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3035,7 +3044,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ10">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3160,7 +3169,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q11">
         <v>4</v>
@@ -3241,7 +3250,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ11">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3572,7 +3581,7 @@
         <v>94</v>
       </c>
       <c r="P13" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -3650,7 +3659,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ13">
         <v>1.14</v>
@@ -3778,7 +3787,7 @@
         <v>86</v>
       </c>
       <c r="P14" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4190,7 +4199,7 @@
         <v>96</v>
       </c>
       <c r="P16" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q16">
         <v>2.55</v>
@@ -4396,7 +4405,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -4602,7 +4611,7 @@
         <v>86</v>
       </c>
       <c r="P18" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q18">
         <v>2.62</v>
@@ -4680,7 +4689,7 @@
         <v>1</v>
       </c>
       <c r="AP18">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ18">
         <v>2.13</v>
@@ -5095,7 +5104,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ20">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AR20">
         <v>2.25</v>
@@ -5220,7 +5229,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5298,7 +5307,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="AQ21">
         <v>1.71</v>
@@ -5507,7 +5516,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ22">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR22">
         <v>1.54</v>
@@ -5632,7 +5641,7 @@
         <v>86</v>
       </c>
       <c r="P23" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q23">
         <v>2.62</v>
@@ -6122,7 +6131,7 @@
         <v>3</v>
       </c>
       <c r="AP25">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ25">
         <v>1.25</v>
@@ -6250,7 +6259,7 @@
         <v>102</v>
       </c>
       <c r="P26" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q26">
         <v>3.2</v>
@@ -6456,7 +6465,7 @@
         <v>103</v>
       </c>
       <c r="P27" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q27">
         <v>1.72</v>
@@ -6949,7 +6958,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ29">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR29">
         <v>1.64</v>
@@ -7280,7 +7289,7 @@
         <v>105</v>
       </c>
       <c r="P31" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7486,7 +7495,7 @@
         <v>106</v>
       </c>
       <c r="P32" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q32">
         <v>2.88</v>
@@ -8104,7 +8113,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8310,7 +8319,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q36">
         <v>4.75</v>
@@ -8516,7 +8525,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q37">
         <v>2</v>
@@ -8594,10 +8603,10 @@
         <v>1.5</v>
       </c>
       <c r="AP37">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ37">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR37">
         <v>1.56</v>
@@ -8722,7 +8731,7 @@
         <v>111</v>
       </c>
       <c r="P38" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q38">
         <v>4</v>
@@ -8800,7 +8809,7 @@
         <v>3</v>
       </c>
       <c r="AP38">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="AQ38">
         <v>1.67</v>
@@ -8928,7 +8937,7 @@
         <v>112</v>
       </c>
       <c r="P39" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9546,7 +9555,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q42">
         <v>2.95</v>
@@ -9624,7 +9633,7 @@
         <v>1.5</v>
       </c>
       <c r="AP42">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ42">
         <v>1.57</v>
@@ -9752,7 +9761,7 @@
         <v>115</v>
       </c>
       <c r="P43" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q43">
         <v>2</v>
@@ -9833,7 +9842,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ43">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR43">
         <v>1.41</v>
@@ -10036,7 +10045,7 @@
         <v>1.5</v>
       </c>
       <c r="AP44">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ44">
         <v>1.86</v>
@@ -10164,7 +10173,7 @@
         <v>117</v>
       </c>
       <c r="P45" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10242,7 +10251,7 @@
         <v>0</v>
       </c>
       <c r="AP45">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="AQ45">
         <v>1.14</v>
@@ -10451,7 +10460,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ46">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR46">
         <v>1.57</v>
@@ -10988,7 +10997,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q49">
         <v>3</v>
@@ -11194,7 +11203,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q50">
         <v>3.75</v>
@@ -11606,7 +11615,7 @@
         <v>86</v>
       </c>
       <c r="P52" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -11812,7 +11821,7 @@
         <v>86</v>
       </c>
       <c r="P53" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q53">
         <v>5.5</v>
@@ -12224,7 +12233,7 @@
         <v>125</v>
       </c>
       <c r="P55" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q55">
         <v>1.83</v>
@@ -12717,7 +12726,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ57">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR57">
         <v>1.8</v>
@@ -12842,7 +12851,7 @@
         <v>127</v>
       </c>
       <c r="P58" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q58">
         <v>2.38</v>
@@ -13254,7 +13263,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q60">
         <v>3.1</v>
@@ -13332,7 +13341,7 @@
         <v>2.33</v>
       </c>
       <c r="AP60">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ60">
         <v>2.13</v>
@@ -13872,7 +13881,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q63">
         <v>6</v>
@@ -14078,7 +14087,7 @@
         <v>132</v>
       </c>
       <c r="P64" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14159,7 +14168,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ64">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AR64">
         <v>1.67</v>
@@ -14284,7 +14293,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14490,7 +14499,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q66">
         <v>1.83</v>
@@ -14696,7 +14705,7 @@
         <v>135</v>
       </c>
       <c r="P67" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q67">
         <v>3.1</v>
@@ -14774,7 +14783,7 @@
         <v>2.5</v>
       </c>
       <c r="AP67">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ67">
         <v>1.67</v>
@@ -14902,7 +14911,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q68">
         <v>5.25</v>
@@ -14980,7 +14989,7 @@
         <v>1.75</v>
       </c>
       <c r="AP68">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="AQ68">
         <v>1.25</v>
@@ -15108,7 +15117,7 @@
         <v>103</v>
       </c>
       <c r="P69" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q69">
         <v>2.38</v>
@@ -15189,7 +15198,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ69">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR69">
         <v>1.75</v>
@@ -15314,7 +15323,7 @@
         <v>137</v>
       </c>
       <c r="P70" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q70">
         <v>2.2</v>
@@ -15520,7 +15529,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q71">
         <v>2.95</v>
@@ -16010,7 +16019,7 @@
         <v>1.75</v>
       </c>
       <c r="AP73">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ73">
         <v>1.57</v>
@@ -16216,7 +16225,7 @@
         <v>0.25</v>
       </c>
       <c r="AP74">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ74">
         <v>0.14</v>
@@ -16344,7 +16353,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q75">
         <v>3.95</v>
@@ -16631,7 +16640,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ76">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR76">
         <v>2.52</v>
@@ -16962,7 +16971,7 @@
         <v>143</v>
       </c>
       <c r="P78" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q78">
         <v>2.75</v>
@@ -17168,7 +17177,7 @@
         <v>144</v>
       </c>
       <c r="P79" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -17455,7 +17464,7 @@
         <v>2</v>
       </c>
       <c r="AQ80">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AR80">
         <v>1.63</v>
@@ -17580,7 +17589,7 @@
         <v>146</v>
       </c>
       <c r="P81" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q81">
         <v>2.45</v>
@@ -17992,7 +18001,7 @@
         <v>127</v>
       </c>
       <c r="P83" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q83">
         <v>2.45</v>
@@ -18070,7 +18079,7 @@
         <v>0.6</v>
       </c>
       <c r="AP83">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="AQ83">
         <v>0.63</v>
@@ -18198,7 +18207,7 @@
         <v>147</v>
       </c>
       <c r="P84" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q84">
         <v>2.5</v>
@@ -18610,7 +18619,7 @@
         <v>118</v>
       </c>
       <c r="P86" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q86">
         <v>4.75</v>
@@ -18816,7 +18825,7 @@
         <v>86</v>
       </c>
       <c r="P87" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q87">
         <v>3.5</v>
@@ -19515,7 +19524,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ90">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR90">
         <v>2.14</v>
@@ -19640,7 +19649,7 @@
         <v>86</v>
       </c>
       <c r="P91" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q91">
         <v>3.4</v>
@@ -19721,7 +19730,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ91">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AR91">
         <v>1.72</v>
@@ -19846,7 +19855,7 @@
         <v>86</v>
       </c>
       <c r="P92" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q92">
         <v>2.9</v>
@@ -20258,7 +20267,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -20545,7 +20554,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ95">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AR95">
         <v>1.29</v>
@@ -20876,7 +20885,7 @@
         <v>148</v>
       </c>
       <c r="P97" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21288,7 +21297,7 @@
         <v>154</v>
       </c>
       <c r="P99" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q99">
         <v>3.45</v>
@@ -21575,7 +21584,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ100">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR100">
         <v>2.06</v>
@@ -21700,7 +21709,7 @@
         <v>156</v>
       </c>
       <c r="P101" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q101">
         <v>3.4</v>
@@ -21906,7 +21915,7 @@
         <v>86</v>
       </c>
       <c r="P102" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22190,7 +22199,7 @@
         <v>2</v>
       </c>
       <c r="AP103">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ103">
         <v>1.71</v>
@@ -22318,7 +22327,7 @@
         <v>158</v>
       </c>
       <c r="P104" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q104">
         <v>3.1</v>
@@ -22396,7 +22405,7 @@
         <v>1.43</v>
       </c>
       <c r="AP104">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ104">
         <v>1.63</v>
@@ -22602,7 +22611,7 @@
         <v>1.8</v>
       </c>
       <c r="AP105">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="AQ105">
         <v>1.86</v>
@@ -22936,7 +22945,7 @@
         <v>160</v>
       </c>
       <c r="P107" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q107">
         <v>2.25</v>
@@ -23348,7 +23357,7 @@
         <v>86</v>
       </c>
       <c r="P109" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q109">
         <v>4.75</v>
@@ -23760,7 +23769,7 @@
         <v>162</v>
       </c>
       <c r="P111" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q111">
         <v>2.38</v>
@@ -24378,7 +24387,7 @@
         <v>164</v>
       </c>
       <c r="P114" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q114">
         <v>2.2</v>
@@ -24459,7 +24468,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ114">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR114">
         <v>1.85</v>
@@ -24584,7 +24593,7 @@
         <v>86</v>
       </c>
       <c r="P115" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -24790,7 +24799,7 @@
         <v>123</v>
       </c>
       <c r="P116" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q116">
         <v>3</v>
@@ -25408,7 +25417,7 @@
         <v>167</v>
       </c>
       <c r="P119" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q119">
         <v>3.4</v>
@@ -25565,6 +25574,624 @@
       </c>
       <c r="BP119">
         <v>1.63</v>
+      </c>
+    </row>
+    <row r="120" spans="1:68">
+      <c r="A120" s="1">
+        <v>119</v>
+      </c>
+      <c r="B120">
+        <v>7779071</v>
+      </c>
+      <c r="C120" t="s">
+        <v>68</v>
+      </c>
+      <c r="D120" t="s">
+        <v>69</v>
+      </c>
+      <c r="E120" s="2">
+        <v>45851.47916666666</v>
+      </c>
+      <c r="F120">
+        <v>15</v>
+      </c>
+      <c r="G120" t="s">
+        <v>76</v>
+      </c>
+      <c r="H120" t="s">
+        <v>70</v>
+      </c>
+      <c r="I120">
+        <v>0</v>
+      </c>
+      <c r="J120">
+        <v>0</v>
+      </c>
+      <c r="K120">
+        <v>0</v>
+      </c>
+      <c r="L120">
+        <v>1</v>
+      </c>
+      <c r="M120">
+        <v>0</v>
+      </c>
+      <c r="N120">
+        <v>1</v>
+      </c>
+      <c r="O120" t="s">
+        <v>101</v>
+      </c>
+      <c r="P120" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q120">
+        <v>4.75</v>
+      </c>
+      <c r="R120">
+        <v>2.2</v>
+      </c>
+      <c r="S120">
+        <v>2.4</v>
+      </c>
+      <c r="T120">
+        <v>1.36</v>
+      </c>
+      <c r="U120">
+        <v>3</v>
+      </c>
+      <c r="V120">
+        <v>2.75</v>
+      </c>
+      <c r="W120">
+        <v>1.4</v>
+      </c>
+      <c r="X120">
+        <v>8</v>
+      </c>
+      <c r="Y120">
+        <v>1.08</v>
+      </c>
+      <c r="Z120">
+        <v>3.82</v>
+      </c>
+      <c r="AA120">
+        <v>3.37</v>
+      </c>
+      <c r="AB120">
+        <v>1.78</v>
+      </c>
+      <c r="AC120">
+        <v>1.06</v>
+      </c>
+      <c r="AD120">
+        <v>9</v>
+      </c>
+      <c r="AE120">
+        <v>1.3</v>
+      </c>
+      <c r="AF120">
+        <v>3.45</v>
+      </c>
+      <c r="AG120">
+        <v>1.91</v>
+      </c>
+      <c r="AH120">
+        <v>1.79</v>
+      </c>
+      <c r="AI120">
+        <v>1.8</v>
+      </c>
+      <c r="AJ120">
+        <v>1.95</v>
+      </c>
+      <c r="AK120">
+        <v>1.93</v>
+      </c>
+      <c r="AL120">
+        <v>1.22</v>
+      </c>
+      <c r="AM120">
+        <v>1.2</v>
+      </c>
+      <c r="AN120">
+        <v>0.43</v>
+      </c>
+      <c r="AO120">
+        <v>1.5</v>
+      </c>
+      <c r="AP120">
+        <v>0.75</v>
+      </c>
+      <c r="AQ120">
+        <v>1.29</v>
+      </c>
+      <c r="AR120">
+        <v>1.58</v>
+      </c>
+      <c r="AS120">
+        <v>1.23</v>
+      </c>
+      <c r="AT120">
+        <v>2.81</v>
+      </c>
+      <c r="AU120">
+        <v>4</v>
+      </c>
+      <c r="AV120">
+        <v>6</v>
+      </c>
+      <c r="AW120">
+        <v>7</v>
+      </c>
+      <c r="AX120">
+        <v>15</v>
+      </c>
+      <c r="AY120">
+        <v>11</v>
+      </c>
+      <c r="AZ120">
+        <v>21</v>
+      </c>
+      <c r="BA120">
+        <v>8</v>
+      </c>
+      <c r="BB120">
+        <v>8</v>
+      </c>
+      <c r="BC120">
+        <v>16</v>
+      </c>
+      <c r="BD120">
+        <v>2.55</v>
+      </c>
+      <c r="BE120">
+        <v>6.4</v>
+      </c>
+      <c r="BF120">
+        <v>1.65</v>
+      </c>
+      <c r="BG120">
+        <v>1.27</v>
+      </c>
+      <c r="BH120">
+        <v>3.3</v>
+      </c>
+      <c r="BI120">
+        <v>1.49</v>
+      </c>
+      <c r="BJ120">
+        <v>2.43</v>
+      </c>
+      <c r="BK120">
+        <v>1.79</v>
+      </c>
+      <c r="BL120">
+        <v>1.9</v>
+      </c>
+      <c r="BM120">
+        <v>2.25</v>
+      </c>
+      <c r="BN120">
+        <v>1.56</v>
+      </c>
+      <c r="BO120">
+        <v>2.9</v>
+      </c>
+      <c r="BP120">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="121" spans="1:68">
+      <c r="A121" s="1">
+        <v>120</v>
+      </c>
+      <c r="B121">
+        <v>7779064</v>
+      </c>
+      <c r="C121" t="s">
+        <v>68</v>
+      </c>
+      <c r="D121" t="s">
+        <v>69</v>
+      </c>
+      <c r="E121" s="2">
+        <v>45851.47916666666</v>
+      </c>
+      <c r="F121">
+        <v>15</v>
+      </c>
+      <c r="G121" t="s">
+        <v>81</v>
+      </c>
+      <c r="H121" t="s">
+        <v>83</v>
+      </c>
+      <c r="I121">
+        <v>1</v>
+      </c>
+      <c r="J121">
+        <v>0</v>
+      </c>
+      <c r="K121">
+        <v>1</v>
+      </c>
+      <c r="L121">
+        <v>3</v>
+      </c>
+      <c r="M121">
+        <v>0</v>
+      </c>
+      <c r="N121">
+        <v>3</v>
+      </c>
+      <c r="O121" t="s">
+        <v>168</v>
+      </c>
+      <c r="P121" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q121">
+        <v>2.05</v>
+      </c>
+      <c r="R121">
+        <v>2.3</v>
+      </c>
+      <c r="S121">
+        <v>6</v>
+      </c>
+      <c r="T121">
+        <v>1.36</v>
+      </c>
+      <c r="U121">
+        <v>3</v>
+      </c>
+      <c r="V121">
+        <v>2.75</v>
+      </c>
+      <c r="W121">
+        <v>1.4</v>
+      </c>
+      <c r="X121">
+        <v>7</v>
+      </c>
+      <c r="Y121">
+        <v>1.1</v>
+      </c>
+      <c r="Z121">
+        <v>1.51</v>
+      </c>
+      <c r="AA121">
+        <v>3.76</v>
+      </c>
+      <c r="AB121">
+        <v>5.3</v>
+      </c>
+      <c r="AC121">
+        <v>1.05</v>
+      </c>
+      <c r="AD121">
+        <v>10</v>
+      </c>
+      <c r="AE121">
+        <v>1.3</v>
+      </c>
+      <c r="AF121">
+        <v>3.6</v>
+      </c>
+      <c r="AG121">
+        <v>1.9</v>
+      </c>
+      <c r="AH121">
+        <v>1.8</v>
+      </c>
+      <c r="AI121">
+        <v>1.95</v>
+      </c>
+      <c r="AJ121">
+        <v>1.8</v>
+      </c>
+      <c r="AK121">
+        <v>1.11</v>
+      </c>
+      <c r="AL121">
+        <v>1.18</v>
+      </c>
+      <c r="AM121">
+        <v>2.45</v>
+      </c>
+      <c r="AN121">
+        <v>2.33</v>
+      </c>
+      <c r="AO121">
+        <v>1.29</v>
+      </c>
+      <c r="AP121">
+        <v>2.43</v>
+      </c>
+      <c r="AQ121">
+        <v>1.13</v>
+      </c>
+      <c r="AR121">
+        <v>1.72</v>
+      </c>
+      <c r="AS121">
+        <v>1.43</v>
+      </c>
+      <c r="AT121">
+        <v>3.15</v>
+      </c>
+      <c r="AU121">
+        <v>5</v>
+      </c>
+      <c r="AV121">
+        <v>2</v>
+      </c>
+      <c r="AW121">
+        <v>8</v>
+      </c>
+      <c r="AX121">
+        <v>5</v>
+      </c>
+      <c r="AY121">
+        <v>13</v>
+      </c>
+      <c r="AZ121">
+        <v>7</v>
+      </c>
+      <c r="BA121">
+        <v>5</v>
+      </c>
+      <c r="BB121">
+        <v>1</v>
+      </c>
+      <c r="BC121">
+        <v>6</v>
+      </c>
+      <c r="BD121">
+        <v>1.34</v>
+      </c>
+      <c r="BE121">
+        <v>7</v>
+      </c>
+      <c r="BF121">
+        <v>3.65</v>
+      </c>
+      <c r="BG121">
+        <v>1.16</v>
+      </c>
+      <c r="BH121">
+        <v>4.4</v>
+      </c>
+      <c r="BI121">
+        <v>1.29</v>
+      </c>
+      <c r="BJ121">
+        <v>3.15</v>
+      </c>
+      <c r="BK121">
+        <v>1.49</v>
+      </c>
+      <c r="BL121">
+        <v>2.4</v>
+      </c>
+      <c r="BM121">
+        <v>1.78</v>
+      </c>
+      <c r="BN121">
+        <v>1.92</v>
+      </c>
+      <c r="BO121">
+        <v>2.2</v>
+      </c>
+      <c r="BP121">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="122" spans="1:68">
+      <c r="A122" s="1">
+        <v>121</v>
+      </c>
+      <c r="B122">
+        <v>7779068</v>
+      </c>
+      <c r="C122" t="s">
+        <v>68</v>
+      </c>
+      <c r="D122" t="s">
+        <v>69</v>
+      </c>
+      <c r="E122" s="2">
+        <v>45851.5625</v>
+      </c>
+      <c r="F122">
+        <v>15</v>
+      </c>
+      <c r="G122" t="s">
+        <v>71</v>
+      </c>
+      <c r="H122" t="s">
+        <v>75</v>
+      </c>
+      <c r="I122">
+        <v>3</v>
+      </c>
+      <c r="J122">
+        <v>0</v>
+      </c>
+      <c r="K122">
+        <v>3</v>
+      </c>
+      <c r="L122">
+        <v>4</v>
+      </c>
+      <c r="M122">
+        <v>1</v>
+      </c>
+      <c r="N122">
+        <v>5</v>
+      </c>
+      <c r="O122" t="s">
+        <v>169</v>
+      </c>
+      <c r="P122" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q122">
+        <v>2.2</v>
+      </c>
+      <c r="R122">
+        <v>2.38</v>
+      </c>
+      <c r="S122">
+        <v>4.75</v>
+      </c>
+      <c r="T122">
+        <v>1.3</v>
+      </c>
+      <c r="U122">
+        <v>3.4</v>
+      </c>
+      <c r="V122">
+        <v>2.5</v>
+      </c>
+      <c r="W122">
+        <v>1.5</v>
+      </c>
+      <c r="X122">
+        <v>6</v>
+      </c>
+      <c r="Y122">
+        <v>1.13</v>
+      </c>
+      <c r="Z122">
+        <v>1.56</v>
+      </c>
+      <c r="AA122">
+        <v>4.1</v>
+      </c>
+      <c r="AB122">
+        <v>4.3</v>
+      </c>
+      <c r="AC122">
+        <v>1.04</v>
+      </c>
+      <c r="AD122">
+        <v>11</v>
+      </c>
+      <c r="AE122">
+        <v>1.22</v>
+      </c>
+      <c r="AF122">
+        <v>4.33</v>
+      </c>
+      <c r="AG122">
+        <v>1.63</v>
+      </c>
+      <c r="AH122">
+        <v>2.13</v>
+      </c>
+      <c r="AI122">
+        <v>1.7</v>
+      </c>
+      <c r="AJ122">
+        <v>2.05</v>
+      </c>
+      <c r="AK122">
+        <v>1.17</v>
+      </c>
+      <c r="AL122">
+        <v>1.18</v>
+      </c>
+      <c r="AM122">
+        <v>2.2</v>
+      </c>
+      <c r="AN122">
+        <v>1.14</v>
+      </c>
+      <c r="AO122">
+        <v>0.67</v>
+      </c>
+      <c r="AP122">
+        <v>1.38</v>
+      </c>
+      <c r="AQ122">
+        <v>0.57</v>
+      </c>
+      <c r="AR122">
+        <v>1.77</v>
+      </c>
+      <c r="AS122">
+        <v>0.78</v>
+      </c>
+      <c r="AT122">
+        <v>2.55</v>
+      </c>
+      <c r="AU122">
+        <v>6</v>
+      </c>
+      <c r="AV122">
+        <v>7</v>
+      </c>
+      <c r="AW122">
+        <v>12</v>
+      </c>
+      <c r="AX122">
+        <v>5</v>
+      </c>
+      <c r="AY122">
+        <v>18</v>
+      </c>
+      <c r="AZ122">
+        <v>12</v>
+      </c>
+      <c r="BA122">
+        <v>7</v>
+      </c>
+      <c r="BB122">
+        <v>1</v>
+      </c>
+      <c r="BC122">
+        <v>8</v>
+      </c>
+      <c r="BD122">
+        <v>1.33</v>
+      </c>
+      <c r="BE122">
+        <v>7</v>
+      </c>
+      <c r="BF122">
+        <v>3.65</v>
+      </c>
+      <c r="BG122">
+        <v>1.2</v>
+      </c>
+      <c r="BH122">
+        <v>4</v>
+      </c>
+      <c r="BI122">
+        <v>1.34</v>
+      </c>
+      <c r="BJ122">
+        <v>2.9</v>
+      </c>
+      <c r="BK122">
+        <v>1.58</v>
+      </c>
+      <c r="BL122">
+        <v>2.2</v>
+      </c>
+      <c r="BM122">
+        <v>1.92</v>
+      </c>
+      <c r="BN122">
+        <v>1.77</v>
+      </c>
+      <c r="BO122">
+        <v>2.4</v>
+      </c>
+      <c r="BP122">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="229">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -699,6 +699,9 @@
   <si>
     <t>['90+3']</t>
   </si>
+  <si>
+    <t>['7', '16']</t>
+  </si>
 </sst>
 </file>
 
@@ -1059,7 +1062,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP122"/>
+  <dimension ref="A1:BP123"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2014,7 +2017,7 @@
         <v>2</v>
       </c>
       <c r="AQ5">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -3247,7 +3250,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ11">
         <v>1.29</v>
@@ -4692,7 +4695,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ18">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR18">
         <v>2.05</v>
@@ -5719,7 +5722,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ23">
         <v>1.63</v>
@@ -8400,7 +8403,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ36">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR36">
         <v>1.54</v>
@@ -10457,7 +10460,7 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ46">
         <v>0.57</v>
@@ -13135,7 +13138,7 @@
         <v>2</v>
       </c>
       <c r="AP59">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ59">
         <v>1.43</v>
@@ -13344,7 +13347,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ60">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR60">
         <v>1.84</v>
@@ -15610,7 +15613,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ71">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR71">
         <v>1.63</v>
@@ -17049,7 +17052,7 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ78">
         <v>1.14</v>
@@ -17670,7 +17673,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ81">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR81">
         <v>2.05</v>
@@ -19318,7 +19321,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ89">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR89">
         <v>1.72</v>
@@ -21375,7 +21378,7 @@
         <v>2.14</v>
       </c>
       <c r="AP99">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ99">
         <v>1.67</v>
@@ -23438,7 +23441,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ109">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR109">
         <v>1.14</v>
@@ -26192,6 +26195,212 @@
       </c>
       <c r="BP122">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="123" spans="1:68">
+      <c r="A123" s="1">
+        <v>122</v>
+      </c>
+      <c r="B123">
+        <v>7779070</v>
+      </c>
+      <c r="C123" t="s">
+        <v>68</v>
+      </c>
+      <c r="D123" t="s">
+        <v>69</v>
+      </c>
+      <c r="E123" s="2">
+        <v>45852.58333333334</v>
+      </c>
+      <c r="F123">
+        <v>15</v>
+      </c>
+      <c r="G123" t="s">
+        <v>79</v>
+      </c>
+      <c r="H123" t="s">
+        <v>84</v>
+      </c>
+      <c r="I123">
+        <v>0</v>
+      </c>
+      <c r="J123">
+        <v>2</v>
+      </c>
+      <c r="K123">
+        <v>2</v>
+      </c>
+      <c r="L123">
+        <v>1</v>
+      </c>
+      <c r="M123">
+        <v>2</v>
+      </c>
+      <c r="N123">
+        <v>3</v>
+      </c>
+      <c r="O123" t="s">
+        <v>111</v>
+      </c>
+      <c r="P123" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q123">
+        <v>4</v>
+      </c>
+      <c r="R123">
+        <v>2.38</v>
+      </c>
+      <c r="S123">
+        <v>2.5</v>
+      </c>
+      <c r="T123">
+        <v>1.3</v>
+      </c>
+      <c r="U123">
+        <v>3.4</v>
+      </c>
+      <c r="V123">
+        <v>2.38</v>
+      </c>
+      <c r="W123">
+        <v>1.53</v>
+      </c>
+      <c r="X123">
+        <v>6</v>
+      </c>
+      <c r="Y123">
+        <v>1.13</v>
+      </c>
+      <c r="Z123">
+        <v>3.3</v>
+      </c>
+      <c r="AA123">
+        <v>3.5</v>
+      </c>
+      <c r="AB123">
+        <v>1.89</v>
+      </c>
+      <c r="AC123">
+        <v>1.04</v>
+      </c>
+      <c r="AD123">
+        <v>11</v>
+      </c>
+      <c r="AE123">
+        <v>1.22</v>
+      </c>
+      <c r="AF123">
+        <v>4.33</v>
+      </c>
+      <c r="AG123">
+        <v>1.56</v>
+      </c>
+      <c r="AH123">
+        <v>2.27</v>
+      </c>
+      <c r="AI123">
+        <v>1.57</v>
+      </c>
+      <c r="AJ123">
+        <v>2.25</v>
+      </c>
+      <c r="AK123">
+        <v>1.77</v>
+      </c>
+      <c r="AL123">
+        <v>1.27</v>
+      </c>
+      <c r="AM123">
+        <v>1.3</v>
+      </c>
+      <c r="AN123">
+        <v>1.17</v>
+      </c>
+      <c r="AO123">
+        <v>2.13</v>
+      </c>
+      <c r="AP123">
+        <v>1</v>
+      </c>
+      <c r="AQ123">
+        <v>2.22</v>
+      </c>
+      <c r="AR123">
+        <v>1.73</v>
+      </c>
+      <c r="AS123">
+        <v>1.8</v>
+      </c>
+      <c r="AT123">
+        <v>3.53</v>
+      </c>
+      <c r="AU123">
+        <v>8</v>
+      </c>
+      <c r="AV123">
+        <v>5</v>
+      </c>
+      <c r="AW123">
+        <v>7</v>
+      </c>
+      <c r="AX123">
+        <v>4</v>
+      </c>
+      <c r="AY123">
+        <v>15</v>
+      </c>
+      <c r="AZ123">
+        <v>9</v>
+      </c>
+      <c r="BA123">
+        <v>6</v>
+      </c>
+      <c r="BB123">
+        <v>3</v>
+      </c>
+      <c r="BC123">
+        <v>9</v>
+      </c>
+      <c r="BD123">
+        <v>2.23</v>
+      </c>
+      <c r="BE123">
+        <v>6.75</v>
+      </c>
+      <c r="BF123">
+        <v>1.79</v>
+      </c>
+      <c r="BG123">
+        <v>1.13</v>
+      </c>
+      <c r="BH123">
+        <v>4.9</v>
+      </c>
+      <c r="BI123">
+        <v>1.24</v>
+      </c>
+      <c r="BJ123">
+        <v>3.55</v>
+      </c>
+      <c r="BK123">
+        <v>1.43</v>
+      </c>
+      <c r="BL123">
+        <v>2.63</v>
+      </c>
+      <c r="BM123">
+        <v>1.68</v>
+      </c>
+      <c r="BN123">
+        <v>2.05</v>
+      </c>
+      <c r="BO123">
+        <v>2.05</v>
+      </c>
+      <c r="BP123">
+        <v>1.68</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="232">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -526,6 +526,9 @@
     <t>['17', '19', '45', '48']</t>
   </si>
   <si>
+    <t>['11']</t>
+  </si>
+  <si>
     <t>['45+8']</t>
   </si>
   <si>
@@ -701,6 +704,12 @@
   </si>
   <si>
     <t>['7', '16']</t>
+  </si>
+  <si>
+    <t>['24', '67']</t>
+  </si>
+  <si>
+    <t>['15', '52', '61']</t>
   </si>
 </sst>
 </file>
@@ -1062,7 +1071,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP123"/>
+  <dimension ref="A1:BP126"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1318,7 +1327,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q2">
         <v>3.5</v>
@@ -1396,10 +1405,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ2">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2142,7 +2151,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q6">
         <v>2.6</v>
@@ -2348,7 +2357,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -2554,7 +2563,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -2760,7 +2769,7 @@
         <v>86</v>
       </c>
       <c r="P9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3172,7 +3181,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q11">
         <v>4</v>
@@ -3456,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AQ12">
         <v>1.43</v>
@@ -3584,7 +3593,7 @@
         <v>94</v>
       </c>
       <c r="P13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -3790,7 +3799,7 @@
         <v>86</v>
       </c>
       <c r="P14" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4074,7 +4083,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AQ15">
         <v>0.14</v>
@@ -4202,7 +4211,7 @@
         <v>96</v>
       </c>
       <c r="P16" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q16">
         <v>2.55</v>
@@ -4283,7 +4292,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ16">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4408,7 +4417,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -4489,7 +4498,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ17">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4614,7 +4623,7 @@
         <v>86</v>
       </c>
       <c r="P18" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q18">
         <v>2.62</v>
@@ -5232,7 +5241,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5644,7 +5653,7 @@
         <v>86</v>
       </c>
       <c r="P23" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q23">
         <v>2.62</v>
@@ -6137,7 +6146,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ25">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR25">
         <v>1.74</v>
@@ -6262,7 +6271,7 @@
         <v>102</v>
       </c>
       <c r="P26" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q26">
         <v>3.2</v>
@@ -6468,7 +6477,7 @@
         <v>103</v>
       </c>
       <c r="P27" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q27">
         <v>1.72</v>
@@ -6752,10 +6761,10 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AQ28">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AR28">
         <v>1.15</v>
@@ -7164,7 +7173,7 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AQ30">
         <v>1.67</v>
@@ -7292,7 +7301,7 @@
         <v>105</v>
       </c>
       <c r="P31" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7498,7 +7507,7 @@
         <v>106</v>
       </c>
       <c r="P32" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q32">
         <v>2.88</v>
@@ -7782,10 +7791,10 @@
         <v>1</v>
       </c>
       <c r="AP33">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ33">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR33">
         <v>1.7</v>
@@ -7991,7 +8000,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ34">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR34">
         <v>1.98</v>
@@ -8116,7 +8125,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8322,7 +8331,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q36">
         <v>4.75</v>
@@ -8528,7 +8537,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q37">
         <v>2</v>
@@ -8734,7 +8743,7 @@
         <v>111</v>
       </c>
       <c r="P38" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q38">
         <v>4</v>
@@ -8940,7 +8949,7 @@
         <v>112</v>
       </c>
       <c r="P39" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9430,7 +9439,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ41">
         <v>0.63</v>
@@ -9558,7 +9567,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q42">
         <v>2.95</v>
@@ -9764,7 +9773,7 @@
         <v>115</v>
       </c>
       <c r="P43" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q43">
         <v>2</v>
@@ -10051,7 +10060,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ44">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AR44">
         <v>1.7</v>
@@ -10176,7 +10185,7 @@
         <v>117</v>
       </c>
       <c r="P45" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10669,7 +10678,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ47">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR47">
         <v>1.75</v>
@@ -11000,7 +11009,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q49">
         <v>3</v>
@@ -11078,7 +11087,7 @@
         <v>1.33</v>
       </c>
       <c r="AP49">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AQ49">
         <v>0.75</v>
@@ -11206,7 +11215,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q50">
         <v>3.75</v>
@@ -11490,7 +11499,7 @@
         <v>3</v>
       </c>
       <c r="AP51">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ51">
         <v>1.67</v>
@@ -11618,7 +11627,7 @@
         <v>86</v>
       </c>
       <c r="P52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -11824,7 +11833,7 @@
         <v>86</v>
       </c>
       <c r="P53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q53">
         <v>5.5</v>
@@ -11902,7 +11911,7 @@
         <v>1.33</v>
       </c>
       <c r="AP53">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AQ53">
         <v>1.57</v>
@@ -12236,7 +12245,7 @@
         <v>125</v>
       </c>
       <c r="P55" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q55">
         <v>1.83</v>
@@ -12523,7 +12532,7 @@
         <v>2</v>
       </c>
       <c r="AQ56">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR56">
         <v>1.76</v>
@@ -12854,7 +12863,7 @@
         <v>127</v>
       </c>
       <c r="P58" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q58">
         <v>2.38</v>
@@ -13266,7 +13275,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q60">
         <v>3.1</v>
@@ -13756,10 +13765,10 @@
         <v>1</v>
       </c>
       <c r="AP62">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AQ62">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AR62">
         <v>1.23</v>
@@ -13884,7 +13893,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q63">
         <v>6</v>
@@ -13962,10 +13971,10 @@
         <v>1.33</v>
       </c>
       <c r="AP63">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AQ63">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR63">
         <v>1.61</v>
@@ -14090,7 +14099,7 @@
         <v>132</v>
       </c>
       <c r="P64" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14296,7 +14305,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14377,7 +14386,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ65">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR65">
         <v>1.28</v>
@@ -14502,7 +14511,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q66">
         <v>1.83</v>
@@ -14708,7 +14717,7 @@
         <v>135</v>
       </c>
       <c r="P67" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q67">
         <v>3.1</v>
@@ -14914,7 +14923,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q68">
         <v>5.25</v>
@@ -14995,7 +15004,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ68">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR68">
         <v>1.55</v>
@@ -15120,7 +15129,7 @@
         <v>103</v>
       </c>
       <c r="P69" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q69">
         <v>2.38</v>
@@ -15326,7 +15335,7 @@
         <v>137</v>
       </c>
       <c r="P70" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q70">
         <v>2.2</v>
@@ -15532,7 +15541,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q71">
         <v>2.95</v>
@@ -15610,7 +15619,7 @@
         <v>1.75</v>
       </c>
       <c r="AP71">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ71">
         <v>2.22</v>
@@ -16356,7 +16365,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q75">
         <v>3.95</v>
@@ -16434,10 +16443,10 @@
         <v>1.2</v>
       </c>
       <c r="AP75">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AQ75">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR75">
         <v>1.1</v>
@@ -16974,7 +16983,7 @@
         <v>143</v>
       </c>
       <c r="P78" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q78">
         <v>2.75</v>
@@ -17180,7 +17189,7 @@
         <v>144</v>
       </c>
       <c r="P79" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -17258,7 +17267,7 @@
         <v>1.5</v>
       </c>
       <c r="AP79">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AQ79">
         <v>1.71</v>
@@ -17592,7 +17601,7 @@
         <v>146</v>
       </c>
       <c r="P81" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q81">
         <v>2.45</v>
@@ -18004,7 +18013,7 @@
         <v>127</v>
       </c>
       <c r="P83" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q83">
         <v>2.45</v>
@@ -18210,7 +18219,7 @@
         <v>147</v>
       </c>
       <c r="P84" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q84">
         <v>2.5</v>
@@ -18497,7 +18506,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ85">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR85">
         <v>1.69</v>
@@ -18622,7 +18631,7 @@
         <v>118</v>
       </c>
       <c r="P86" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q86">
         <v>4.75</v>
@@ -18703,7 +18712,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ86">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AR86">
         <v>1.3</v>
@@ -18828,7 +18837,7 @@
         <v>86</v>
       </c>
       <c r="P87" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q87">
         <v>3.5</v>
@@ -19112,7 +19121,7 @@
         <v>1.5</v>
       </c>
       <c r="AP88">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ88">
         <v>1.43</v>
@@ -19652,7 +19661,7 @@
         <v>86</v>
       </c>
       <c r="P91" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q91">
         <v>3.4</v>
@@ -19858,7 +19867,7 @@
         <v>86</v>
       </c>
       <c r="P92" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q92">
         <v>2.9</v>
@@ -20142,7 +20151,7 @@
         <v>0.67</v>
       </c>
       <c r="AP93">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AQ93">
         <v>0.63</v>
@@ -20270,7 +20279,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -20351,7 +20360,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ94">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR94">
         <v>1.73</v>
@@ -20888,7 +20897,7 @@
         <v>148</v>
       </c>
       <c r="P97" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21300,7 +21309,7 @@
         <v>154</v>
       </c>
       <c r="P99" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q99">
         <v>3.45</v>
@@ -21712,7 +21721,7 @@
         <v>156</v>
       </c>
       <c r="P101" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q101">
         <v>3.4</v>
@@ -21790,7 +21799,7 @@
         <v>0.83</v>
       </c>
       <c r="AP101">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AQ101">
         <v>0.75</v>
@@ -21918,7 +21927,7 @@
         <v>86</v>
       </c>
       <c r="P102" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -21996,7 +22005,7 @@
         <v>1.17</v>
       </c>
       <c r="AP102">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AQ102">
         <v>1.63</v>
@@ -22330,7 +22339,7 @@
         <v>158</v>
       </c>
       <c r="P104" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q104">
         <v>3.1</v>
@@ -22411,7 +22420,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ104">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR104">
         <v>1.97</v>
@@ -22617,7 +22626,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ105">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AR105">
         <v>1.52</v>
@@ -22823,7 +22832,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ106">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR106">
         <v>1.34</v>
@@ -22948,7 +22957,7 @@
         <v>160</v>
       </c>
       <c r="P107" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q107">
         <v>2.25</v>
@@ -23026,7 +23035,7 @@
         <v>1.4</v>
       </c>
       <c r="AP107">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ107">
         <v>1.14</v>
@@ -23235,7 +23244,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ108">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR108">
         <v>2.16</v>
@@ -23360,7 +23369,7 @@
         <v>86</v>
       </c>
       <c r="P109" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q109">
         <v>4.75</v>
@@ -23438,7 +23447,7 @@
         <v>2</v>
       </c>
       <c r="AP109">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AQ109">
         <v>2.22</v>
@@ -23772,7 +23781,7 @@
         <v>162</v>
       </c>
       <c r="P111" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q111">
         <v>2.38</v>
@@ -24390,7 +24399,7 @@
         <v>164</v>
       </c>
       <c r="P114" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q114">
         <v>2.2</v>
@@ -24468,7 +24477,7 @@
         <v>1.5</v>
       </c>
       <c r="AP114">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ114">
         <v>1.13</v>
@@ -24596,7 +24605,7 @@
         <v>86</v>
       </c>
       <c r="P115" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -24802,7 +24811,7 @@
         <v>123</v>
       </c>
       <c r="P116" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q116">
         <v>3</v>
@@ -24883,7 +24892,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ116">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AR116">
         <v>1.55</v>
@@ -25420,7 +25429,7 @@
         <v>167</v>
       </c>
       <c r="P119" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q119">
         <v>3.4</v>
@@ -26038,7 +26047,7 @@
         <v>169</v>
       </c>
       <c r="P122" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q122">
         <v>2.2</v>
@@ -26244,7 +26253,7 @@
         <v>111</v>
       </c>
       <c r="P123" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q123">
         <v>4</v>
@@ -26401,6 +26410,624 @@
       </c>
       <c r="BP123">
         <v>1.68</v>
+      </c>
+    </row>
+    <row r="124" spans="1:68">
+      <c r="A124" s="1">
+        <v>123</v>
+      </c>
+      <c r="B124">
+        <v>7779072</v>
+      </c>
+      <c r="C124" t="s">
+        <v>68</v>
+      </c>
+      <c r="D124" t="s">
+        <v>69</v>
+      </c>
+      <c r="E124" s="2">
+        <v>45857.41666666666</v>
+      </c>
+      <c r="F124">
+        <v>16</v>
+      </c>
+      <c r="G124" t="s">
+        <v>70</v>
+      </c>
+      <c r="H124" t="s">
+        <v>73</v>
+      </c>
+      <c r="I124">
+        <v>1</v>
+      </c>
+      <c r="J124">
+        <v>0</v>
+      </c>
+      <c r="K124">
+        <v>1</v>
+      </c>
+      <c r="L124">
+        <v>1</v>
+      </c>
+      <c r="M124">
+        <v>0</v>
+      </c>
+      <c r="N124">
+        <v>1</v>
+      </c>
+      <c r="O124" t="s">
+        <v>170</v>
+      </c>
+      <c r="P124" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q124">
+        <v>2.75</v>
+      </c>
+      <c r="R124">
+        <v>2.25</v>
+      </c>
+      <c r="S124">
+        <v>3.6</v>
+      </c>
+      <c r="T124">
+        <v>1.33</v>
+      </c>
+      <c r="U124">
+        <v>3.25</v>
+      </c>
+      <c r="V124">
+        <v>2.63</v>
+      </c>
+      <c r="W124">
+        <v>1.44</v>
+      </c>
+      <c r="X124">
+        <v>7</v>
+      </c>
+      <c r="Y124">
+        <v>1.1</v>
+      </c>
+      <c r="Z124">
+        <v>2.09</v>
+      </c>
+      <c r="AA124">
+        <v>3.25</v>
+      </c>
+      <c r="AB124">
+        <v>2.98</v>
+      </c>
+      <c r="AC124">
+        <v>1.01</v>
+      </c>
+      <c r="AD124">
+        <v>11</v>
+      </c>
+      <c r="AE124">
+        <v>1.22</v>
+      </c>
+      <c r="AF124">
+        <v>3.64</v>
+      </c>
+      <c r="AG124">
+        <v>1.77</v>
+      </c>
+      <c r="AH124">
+        <v>1.93</v>
+      </c>
+      <c r="AI124">
+        <v>1.67</v>
+      </c>
+      <c r="AJ124">
+        <v>2.1</v>
+      </c>
+      <c r="AK124">
+        <v>1.33</v>
+      </c>
+      <c r="AL124">
+        <v>1.27</v>
+      </c>
+      <c r="AM124">
+        <v>1.7</v>
+      </c>
+      <c r="AN124">
+        <v>1.25</v>
+      </c>
+      <c r="AO124">
+        <v>1.86</v>
+      </c>
+      <c r="AP124">
+        <v>1.44</v>
+      </c>
+      <c r="AQ124">
+        <v>1.63</v>
+      </c>
+      <c r="AR124">
+        <v>1.89</v>
+      </c>
+      <c r="AS124">
+        <v>1.42</v>
+      </c>
+      <c r="AT124">
+        <v>3.31</v>
+      </c>
+      <c r="AU124">
+        <v>8</v>
+      </c>
+      <c r="AV124">
+        <v>6</v>
+      </c>
+      <c r="AW124">
+        <v>11</v>
+      </c>
+      <c r="AX124">
+        <v>6</v>
+      </c>
+      <c r="AY124">
+        <v>19</v>
+      </c>
+      <c r="AZ124">
+        <v>12</v>
+      </c>
+      <c r="BA124">
+        <v>7</v>
+      </c>
+      <c r="BB124">
+        <v>1</v>
+      </c>
+      <c r="BC124">
+        <v>8</v>
+      </c>
+      <c r="BD124">
+        <v>1.61</v>
+      </c>
+      <c r="BE124">
+        <v>6.75</v>
+      </c>
+      <c r="BF124">
+        <v>2.55</v>
+      </c>
+      <c r="BG124">
+        <v>1.16</v>
+      </c>
+      <c r="BH124">
+        <v>4.4</v>
+      </c>
+      <c r="BI124">
+        <v>1.29</v>
+      </c>
+      <c r="BJ124">
+        <v>3.15</v>
+      </c>
+      <c r="BK124">
+        <v>1.5</v>
+      </c>
+      <c r="BL124">
+        <v>2.4</v>
+      </c>
+      <c r="BM124">
+        <v>1.79</v>
+      </c>
+      <c r="BN124">
+        <v>1.9</v>
+      </c>
+      <c r="BO124">
+        <v>2.23</v>
+      </c>
+      <c r="BP124">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="125" spans="1:68">
+      <c r="A125" s="1">
+        <v>124</v>
+      </c>
+      <c r="B125">
+        <v>7779074</v>
+      </c>
+      <c r="C125" t="s">
+        <v>68</v>
+      </c>
+      <c r="D125" t="s">
+        <v>69</v>
+      </c>
+      <c r="E125" s="2">
+        <v>45857.41666666666</v>
+      </c>
+      <c r="F125">
+        <v>16</v>
+      </c>
+      <c r="G125" t="s">
+        <v>80</v>
+      </c>
+      <c r="H125" t="s">
+        <v>85</v>
+      </c>
+      <c r="I125">
+        <v>0</v>
+      </c>
+      <c r="J125">
+        <v>1</v>
+      </c>
+      <c r="K125">
+        <v>1</v>
+      </c>
+      <c r="L125">
+        <v>0</v>
+      </c>
+      <c r="M125">
+        <v>2</v>
+      </c>
+      <c r="N125">
+        <v>2</v>
+      </c>
+      <c r="O125" t="s">
+        <v>86</v>
+      </c>
+      <c r="P125" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q125">
+        <v>5.75</v>
+      </c>
+      <c r="R125">
+        <v>2.4</v>
+      </c>
+      <c r="S125">
+        <v>1.9</v>
+      </c>
+      <c r="T125">
+        <v>1.3</v>
+      </c>
+      <c r="U125">
+        <v>3.2</v>
+      </c>
+      <c r="V125">
+        <v>2.38</v>
+      </c>
+      <c r="W125">
+        <v>1.53</v>
+      </c>
+      <c r="X125">
+        <v>5.75</v>
+      </c>
+      <c r="Y125">
+        <v>1.07</v>
+      </c>
+      <c r="Z125">
+        <v>5.9</v>
+      </c>
+      <c r="AA125">
+        <v>4.2</v>
+      </c>
+      <c r="AB125">
+        <v>1.4</v>
+      </c>
+      <c r="AC125">
+        <v>1.04</v>
+      </c>
+      <c r="AD125">
+        <v>11</v>
+      </c>
+      <c r="AE125">
+        <v>1.22</v>
+      </c>
+      <c r="AF125">
+        <v>4.33</v>
+      </c>
+      <c r="AG125">
+        <v>1.65</v>
+      </c>
+      <c r="AH125">
+        <v>2.1</v>
+      </c>
+      <c r="AI125">
+        <v>1.77</v>
+      </c>
+      <c r="AJ125">
+        <v>1.9</v>
+      </c>
+      <c r="AK125">
+        <v>2.7</v>
+      </c>
+      <c r="AL125">
+        <v>1.15</v>
+      </c>
+      <c r="AM125">
+        <v>1.1</v>
+      </c>
+      <c r="AN125">
+        <v>0.71</v>
+      </c>
+      <c r="AO125">
+        <v>1.25</v>
+      </c>
+      <c r="AP125">
+        <v>0.63</v>
+      </c>
+      <c r="AQ125">
+        <v>1.44</v>
+      </c>
+      <c r="AR125">
+        <v>1.1</v>
+      </c>
+      <c r="AS125">
+        <v>1.42</v>
+      </c>
+      <c r="AT125">
+        <v>2.52</v>
+      </c>
+      <c r="AU125">
+        <v>2</v>
+      </c>
+      <c r="AV125">
+        <v>6</v>
+      </c>
+      <c r="AW125">
+        <v>9</v>
+      </c>
+      <c r="AX125">
+        <v>8</v>
+      </c>
+      <c r="AY125">
+        <v>11</v>
+      </c>
+      <c r="AZ125">
+        <v>14</v>
+      </c>
+      <c r="BA125">
+        <v>1</v>
+      </c>
+      <c r="BB125">
+        <v>5</v>
+      </c>
+      <c r="BC125">
+        <v>6</v>
+      </c>
+      <c r="BD125">
+        <v>4.3</v>
+      </c>
+      <c r="BE125">
+        <v>8</v>
+      </c>
+      <c r="BF125">
+        <v>1.25</v>
+      </c>
+      <c r="BG125">
+        <v>1.09</v>
+      </c>
+      <c r="BH125">
+        <v>5.8</v>
+      </c>
+      <c r="BI125">
+        <v>1.19</v>
+      </c>
+      <c r="BJ125">
+        <v>4.1</v>
+      </c>
+      <c r="BK125">
+        <v>1.33</v>
+      </c>
+      <c r="BL125">
+        <v>2.95</v>
+      </c>
+      <c r="BM125">
+        <v>1.53</v>
+      </c>
+      <c r="BN125">
+        <v>2.32</v>
+      </c>
+      <c r="BO125">
+        <v>1.82</v>
+      </c>
+      <c r="BP125">
+        <v>1.86</v>
+      </c>
+    </row>
+    <row r="126" spans="1:68">
+      <c r="A126" s="1">
+        <v>125</v>
+      </c>
+      <c r="B126">
+        <v>7779079</v>
+      </c>
+      <c r="C126" t="s">
+        <v>68</v>
+      </c>
+      <c r="D126" t="s">
+        <v>69</v>
+      </c>
+      <c r="E126" s="2">
+        <v>45857.52083333334</v>
+      </c>
+      <c r="F126">
+        <v>16</v>
+      </c>
+      <c r="G126" t="s">
+        <v>83</v>
+      </c>
+      <c r="H126" t="s">
+        <v>77</v>
+      </c>
+      <c r="I126">
+        <v>0</v>
+      </c>
+      <c r="J126">
+        <v>1</v>
+      </c>
+      <c r="K126">
+        <v>1</v>
+      </c>
+      <c r="L126">
+        <v>0</v>
+      </c>
+      <c r="M126">
+        <v>3</v>
+      </c>
+      <c r="N126">
+        <v>3</v>
+      </c>
+      <c r="O126" t="s">
+        <v>86</v>
+      </c>
+      <c r="P126" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q126">
+        <v>4.33</v>
+      </c>
+      <c r="R126">
+        <v>2.25</v>
+      </c>
+      <c r="S126">
+        <v>2.5</v>
+      </c>
+      <c r="T126">
+        <v>1.36</v>
+      </c>
+      <c r="U126">
+        <v>3</v>
+      </c>
+      <c r="V126">
+        <v>2.63</v>
+      </c>
+      <c r="W126">
+        <v>1.44</v>
+      </c>
+      <c r="X126">
+        <v>7</v>
+      </c>
+      <c r="Y126">
+        <v>1.1</v>
+      </c>
+      <c r="Z126">
+        <v>3.25</v>
+      </c>
+      <c r="AA126">
+        <v>3.3</v>
+      </c>
+      <c r="AB126">
+        <v>1.97</v>
+      </c>
+      <c r="AC126">
+        <v>1.04</v>
+      </c>
+      <c r="AD126">
+        <v>9.75</v>
+      </c>
+      <c r="AE126">
+        <v>1.27</v>
+      </c>
+      <c r="AF126">
+        <v>3.67</v>
+      </c>
+      <c r="AG126">
+        <v>1.83</v>
+      </c>
+      <c r="AH126">
+        <v>1.87</v>
+      </c>
+      <c r="AI126">
+        <v>1.75</v>
+      </c>
+      <c r="AJ126">
+        <v>2</v>
+      </c>
+      <c r="AK126">
+        <v>1.83</v>
+      </c>
+      <c r="AL126">
+        <v>1.27</v>
+      </c>
+      <c r="AM126">
+        <v>1.26</v>
+      </c>
+      <c r="AN126">
+        <v>0.71</v>
+      </c>
+      <c r="AO126">
+        <v>1.63</v>
+      </c>
+      <c r="AP126">
+        <v>0.63</v>
+      </c>
+      <c r="AQ126">
+        <v>1.78</v>
+      </c>
+      <c r="AR126">
+        <v>1.62</v>
+      </c>
+      <c r="AS126">
+        <v>1.72</v>
+      </c>
+      <c r="AT126">
+        <v>3.34</v>
+      </c>
+      <c r="AU126">
+        <v>9</v>
+      </c>
+      <c r="AV126">
+        <v>5</v>
+      </c>
+      <c r="AW126">
+        <v>8</v>
+      </c>
+      <c r="AX126">
+        <v>8</v>
+      </c>
+      <c r="AY126">
+        <v>17</v>
+      </c>
+      <c r="AZ126">
+        <v>13</v>
+      </c>
+      <c r="BA126">
+        <v>6</v>
+      </c>
+      <c r="BB126">
+        <v>1</v>
+      </c>
+      <c r="BC126">
+        <v>7</v>
+      </c>
+      <c r="BD126">
+        <v>3.2</v>
+      </c>
+      <c r="BE126">
+        <v>7.5</v>
+      </c>
+      <c r="BF126">
+        <v>1.4</v>
+      </c>
+      <c r="BG126">
+        <v>1.08</v>
+      </c>
+      <c r="BH126">
+        <v>6.1</v>
+      </c>
+      <c r="BI126">
+        <v>1.18</v>
+      </c>
+      <c r="BJ126">
+        <v>4.2</v>
+      </c>
+      <c r="BK126">
+        <v>1.3</v>
+      </c>
+      <c r="BL126">
+        <v>3.05</v>
+      </c>
+      <c r="BM126">
+        <v>1.5</v>
+      </c>
+      <c r="BN126">
+        <v>2.38</v>
+      </c>
+      <c r="BO126">
+        <v>1.79</v>
+      </c>
+      <c r="BP126">
+        <v>1.91</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="235">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -529,6 +529,12 @@
     <t>['11']</t>
   </si>
   <si>
+    <t>['55', '83']</t>
+  </si>
+  <si>
+    <t>['54', '72', '76']</t>
+  </si>
+  <si>
     <t>['45+8']</t>
   </si>
   <si>
@@ -710,6 +716,9 @@
   </si>
   <si>
     <t>['15', '52', '61']</t>
+  </si>
+  <si>
+    <t>['43', '45+7']</t>
   </si>
 </sst>
 </file>
@@ -1071,7 +1080,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP126"/>
+  <dimension ref="A1:BP130"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1327,7 +1336,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q2">
         <v>3.5</v>
@@ -1614,7 +1623,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ3">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1817,10 +1826,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AQ4">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2151,7 +2160,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q6">
         <v>2.6</v>
@@ -2357,7 +2366,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -2435,7 +2444,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ7">
         <v>1.13</v>
@@ -2563,7 +2572,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -2769,7 +2778,7 @@
         <v>86</v>
       </c>
       <c r="P9" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -2850,7 +2859,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ9">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3181,7 +3190,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q11">
         <v>4</v>
@@ -3259,7 +3268,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ11">
         <v>1.29</v>
@@ -3468,7 +3477,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ12">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3593,7 +3602,7 @@
         <v>94</v>
       </c>
       <c r="P13" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -3799,7 +3808,7 @@
         <v>86</v>
       </c>
       <c r="P14" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4211,7 +4220,7 @@
         <v>96</v>
       </c>
       <c r="P16" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q16">
         <v>2.55</v>
@@ -4289,7 +4298,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ16">
         <v>1.78</v>
@@ -4417,7 +4426,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -4623,7 +4632,7 @@
         <v>86</v>
       </c>
       <c r="P18" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q18">
         <v>2.62</v>
@@ -5113,7 +5122,7 @@
         <v>3</v>
       </c>
       <c r="AP20">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AQ20">
         <v>1.29</v>
@@ -5241,7 +5250,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5322,7 +5331,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ21">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AR21">
         <v>1.59</v>
@@ -5653,7 +5662,7 @@
         <v>86</v>
       </c>
       <c r="P23" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q23">
         <v>2.62</v>
@@ -5731,10 +5740,10 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ23">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR23">
         <v>1.22</v>
@@ -5937,7 +5946,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ24">
         <v>0.63</v>
@@ -6271,7 +6280,7 @@
         <v>102</v>
       </c>
       <c r="P26" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q26">
         <v>3.2</v>
@@ -6349,7 +6358,7 @@
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ26">
         <v>1.57</v>
@@ -6477,7 +6486,7 @@
         <v>103</v>
       </c>
       <c r="P27" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q27">
         <v>1.72</v>
@@ -7176,7 +7185,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ30">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR30">
         <v>1.48</v>
@@ -7301,7 +7310,7 @@
         <v>105</v>
       </c>
       <c r="P31" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7507,7 +7516,7 @@
         <v>106</v>
       </c>
       <c r="P32" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q32">
         <v>2.88</v>
@@ -7588,7 +7597,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ32">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR32">
         <v>1.43</v>
@@ -7997,7 +8006,7 @@
         <v>2</v>
       </c>
       <c r="AP34">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AQ34">
         <v>1.44</v>
@@ -8125,7 +8134,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8331,7 +8340,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q36">
         <v>4.75</v>
@@ -8409,7 +8418,7 @@
         <v>2</v>
       </c>
       <c r="AP36">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ36">
         <v>2.22</v>
@@ -8537,7 +8546,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q37">
         <v>2</v>
@@ -8743,7 +8752,7 @@
         <v>111</v>
       </c>
       <c r="P38" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q38">
         <v>4</v>
@@ -8824,7 +8833,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ38">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR38">
         <v>1.5</v>
@@ -8949,7 +8958,7 @@
         <v>112</v>
       </c>
       <c r="P39" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9030,7 +9039,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ39">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AR39">
         <v>1.72</v>
@@ -9236,7 +9245,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ40">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR40">
         <v>1.88</v>
@@ -9567,7 +9576,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q42">
         <v>2.95</v>
@@ -9773,7 +9782,7 @@
         <v>115</v>
       </c>
       <c r="P43" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q43">
         <v>2</v>
@@ -9851,7 +9860,7 @@
         <v>2</v>
       </c>
       <c r="AP43">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ43">
         <v>1.13</v>
@@ -10185,7 +10194,7 @@
         <v>117</v>
       </c>
       <c r="P45" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10469,7 +10478,7 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ46">
         <v>0.57</v>
@@ -11009,7 +11018,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q49">
         <v>3</v>
@@ -11215,7 +11224,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q50">
         <v>3.75</v>
@@ -11293,7 +11302,7 @@
         <v>0</v>
       </c>
       <c r="AP50">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ50">
         <v>0.14</v>
@@ -11502,7 +11511,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ51">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR51">
         <v>1.87</v>
@@ -11627,7 +11636,7 @@
         <v>86</v>
       </c>
       <c r="P52" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -11708,7 +11717,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ52">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR52">
         <v>1.74</v>
@@ -11833,7 +11842,7 @@
         <v>86</v>
       </c>
       <c r="P53" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q53">
         <v>5.5</v>
@@ -12117,10 +12126,10 @@
         <v>2</v>
       </c>
       <c r="AP54">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ54">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AR54">
         <v>1.34</v>
@@ -12245,7 +12254,7 @@
         <v>125</v>
       </c>
       <c r="P55" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q55">
         <v>1.83</v>
@@ -12326,7 +12335,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ55">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR55">
         <v>2.33</v>
@@ -12863,7 +12872,7 @@
         <v>127</v>
       </c>
       <c r="P58" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q58">
         <v>2.38</v>
@@ -13147,10 +13156,10 @@
         <v>2</v>
       </c>
       <c r="AP59">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ59">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR59">
         <v>1.46</v>
@@ -13275,7 +13284,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q60">
         <v>3.1</v>
@@ -13559,7 +13568,7 @@
         <v>1</v>
       </c>
       <c r="AP61">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AQ61">
         <v>1.14</v>
@@ -13893,7 +13902,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q63">
         <v>6</v>
@@ -14099,7 +14108,7 @@
         <v>132</v>
       </c>
       <c r="P64" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14305,7 +14314,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14383,7 +14392,7 @@
         <v>0.75</v>
       </c>
       <c r="AP65">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ65">
         <v>1.78</v>
@@ -14511,7 +14520,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q66">
         <v>1.83</v>
@@ -14589,7 +14598,7 @@
         <v>1.25</v>
       </c>
       <c r="AP66">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AQ66">
         <v>0.75</v>
@@ -14717,7 +14726,7 @@
         <v>135</v>
       </c>
       <c r="P67" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q67">
         <v>3.1</v>
@@ -14798,7 +14807,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ67">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR67">
         <v>1.87</v>
@@ -14923,7 +14932,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q68">
         <v>5.25</v>
@@ -15129,7 +15138,7 @@
         <v>103</v>
       </c>
       <c r="P69" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q69">
         <v>2.38</v>
@@ -15335,7 +15344,7 @@
         <v>137</v>
       </c>
       <c r="P70" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q70">
         <v>2.2</v>
@@ -15416,7 +15425,7 @@
         <v>2</v>
       </c>
       <c r="AQ70">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR70">
         <v>1.63</v>
@@ -15541,7 +15550,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q71">
         <v>2.95</v>
@@ -16365,7 +16374,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q75">
         <v>3.95</v>
@@ -16855,10 +16864,10 @@
         <v>1.4</v>
       </c>
       <c r="AP77">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ77">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR77">
         <v>1.37</v>
@@ -16983,7 +16992,7 @@
         <v>143</v>
       </c>
       <c r="P78" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q78">
         <v>2.75</v>
@@ -17061,7 +17070,7 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ78">
         <v>1.14</v>
@@ -17189,7 +17198,7 @@
         <v>144</v>
       </c>
       <c r="P79" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -17270,7 +17279,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ79">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AR79">
         <v>1.62</v>
@@ -17601,7 +17610,7 @@
         <v>146</v>
       </c>
       <c r="P81" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q81">
         <v>2.45</v>
@@ -17679,7 +17688,7 @@
         <v>2</v>
       </c>
       <c r="AP81">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AQ81">
         <v>2.22</v>
@@ -17888,7 +17897,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ82">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR82">
         <v>2.4</v>
@@ -18013,7 +18022,7 @@
         <v>127</v>
       </c>
       <c r="P83" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q83">
         <v>2.45</v>
@@ -18219,7 +18228,7 @@
         <v>147</v>
       </c>
       <c r="P84" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q84">
         <v>2.5</v>
@@ -18631,7 +18640,7 @@
         <v>118</v>
       </c>
       <c r="P86" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q86">
         <v>4.75</v>
@@ -18709,7 +18718,7 @@
         <v>1.5</v>
       </c>
       <c r="AP86">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ86">
         <v>1.63</v>
@@ -18837,7 +18846,7 @@
         <v>86</v>
       </c>
       <c r="P87" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q87">
         <v>3.5</v>
@@ -18918,7 +18927,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ87">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR87">
         <v>1.8</v>
@@ -19124,7 +19133,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ88">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR88">
         <v>1.53</v>
@@ -19533,7 +19542,7 @@
         <v>1.8</v>
       </c>
       <c r="AP90">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AQ90">
         <v>1.13</v>
@@ -19661,7 +19670,7 @@
         <v>86</v>
       </c>
       <c r="P91" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q91">
         <v>3.4</v>
@@ -19867,7 +19876,7 @@
         <v>86</v>
       </c>
       <c r="P92" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q92">
         <v>2.9</v>
@@ -20279,7 +20288,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -20563,7 +20572,7 @@
         <v>1.8</v>
       </c>
       <c r="AP95">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ95">
         <v>1.29</v>
@@ -20772,7 +20781,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ96">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR96">
         <v>2.35</v>
@@ -20897,7 +20906,7 @@
         <v>148</v>
       </c>
       <c r="P97" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -20978,7 +20987,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ97">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AR97">
         <v>1.72</v>
@@ -21181,7 +21190,7 @@
         <v>0.2</v>
       </c>
       <c r="AP98">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ98">
         <v>0.14</v>
@@ -21309,7 +21318,7 @@
         <v>154</v>
       </c>
       <c r="P99" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q99">
         <v>3.45</v>
@@ -21387,10 +21396,10 @@
         <v>2.14</v>
       </c>
       <c r="AP99">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ99">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR99">
         <v>1.73</v>
@@ -21593,7 +21602,7 @@
         <v>0.8</v>
       </c>
       <c r="AP100">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AQ100">
         <v>0.57</v>
@@ -21721,7 +21730,7 @@
         <v>156</v>
       </c>
       <c r="P101" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q101">
         <v>3.4</v>
@@ -21927,7 +21936,7 @@
         <v>86</v>
       </c>
       <c r="P102" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22008,7 +22017,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ102">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR102">
         <v>1.6</v>
@@ -22214,7 +22223,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ103">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AR103">
         <v>1.74</v>
@@ -22339,7 +22348,7 @@
         <v>158</v>
       </c>
       <c r="P104" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q104">
         <v>3.1</v>
@@ -22829,7 +22838,7 @@
         <v>1.33</v>
       </c>
       <c r="AP106">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ106">
         <v>1.44</v>
@@ -22957,7 +22966,7 @@
         <v>160</v>
       </c>
       <c r="P107" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q107">
         <v>2.25</v>
@@ -23369,7 +23378,7 @@
         <v>86</v>
       </c>
       <c r="P109" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q109">
         <v>4.75</v>
@@ -23653,7 +23662,7 @@
         <v>0.17</v>
       </c>
       <c r="AP110">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AQ110">
         <v>0.14</v>
@@ -23781,7 +23790,7 @@
         <v>162</v>
       </c>
       <c r="P111" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q111">
         <v>2.38</v>
@@ -24065,10 +24074,10 @@
         <v>1.88</v>
       </c>
       <c r="AP112">
+        <v>1.44</v>
+      </c>
+      <c r="AQ112">
         <v>1.5</v>
-      </c>
-      <c r="AQ112">
-        <v>1.67</v>
       </c>
       <c r="AR112">
         <v>1.29</v>
@@ -24274,7 +24283,7 @@
         <v>2</v>
       </c>
       <c r="AQ113">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR113">
         <v>1.6</v>
@@ -24399,7 +24408,7 @@
         <v>164</v>
       </c>
       <c r="P114" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q114">
         <v>2.2</v>
@@ -24605,7 +24614,7 @@
         <v>86</v>
       </c>
       <c r="P115" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -24686,7 +24695,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ115">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR115">
         <v>1.73</v>
@@ -24811,7 +24820,7 @@
         <v>123</v>
       </c>
       <c r="P116" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q116">
         <v>3</v>
@@ -25429,7 +25438,7 @@
         <v>167</v>
       </c>
       <c r="P119" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q119">
         <v>3.4</v>
@@ -26047,7 +26056,7 @@
         <v>169</v>
       </c>
       <c r="P122" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q122">
         <v>2.2</v>
@@ -26253,7 +26262,7 @@
         <v>111</v>
       </c>
       <c r="P123" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q123">
         <v>4</v>
@@ -26331,7 +26340,7 @@
         <v>2.13</v>
       </c>
       <c r="AP123">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ123">
         <v>2.22</v>
@@ -26665,7 +26674,7 @@
         <v>86</v>
       </c>
       <c r="P125" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q125">
         <v>5.75</v>
@@ -26871,7 +26880,7 @@
         <v>86</v>
       </c>
       <c r="P126" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27028,6 +27037,830 @@
       </c>
       <c r="BP126">
         <v>1.91</v>
+      </c>
+    </row>
+    <row r="127" spans="1:68">
+      <c r="A127" s="1">
+        <v>126</v>
+      </c>
+      <c r="B127">
+        <v>7779075</v>
+      </c>
+      <c r="C127" t="s">
+        <v>68</v>
+      </c>
+      <c r="D127" t="s">
+        <v>69</v>
+      </c>
+      <c r="E127" s="2">
+        <v>45858.375</v>
+      </c>
+      <c r="F127">
+        <v>16</v>
+      </c>
+      <c r="G127" t="s">
+        <v>84</v>
+      </c>
+      <c r="H127" t="s">
+        <v>81</v>
+      </c>
+      <c r="I127">
+        <v>0</v>
+      </c>
+      <c r="J127">
+        <v>0</v>
+      </c>
+      <c r="K127">
+        <v>0</v>
+      </c>
+      <c r="L127">
+        <v>2</v>
+      </c>
+      <c r="M127">
+        <v>0</v>
+      </c>
+      <c r="N127">
+        <v>2</v>
+      </c>
+      <c r="O127" t="s">
+        <v>171</v>
+      </c>
+      <c r="P127" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q127">
+        <v>2.75</v>
+      </c>
+      <c r="R127">
+        <v>2.1</v>
+      </c>
+      <c r="S127">
+        <v>4</v>
+      </c>
+      <c r="T127">
+        <v>1.44</v>
+      </c>
+      <c r="U127">
+        <v>2.63</v>
+      </c>
+      <c r="V127">
+        <v>3.25</v>
+      </c>
+      <c r="W127">
+        <v>1.33</v>
+      </c>
+      <c r="X127">
+        <v>9</v>
+      </c>
+      <c r="Y127">
+        <v>1.07</v>
+      </c>
+      <c r="Z127">
+        <v>2.03</v>
+      </c>
+      <c r="AA127">
+        <v>3.34</v>
+      </c>
+      <c r="AB127">
+        <v>3.06</v>
+      </c>
+      <c r="AC127">
+        <v>1.06</v>
+      </c>
+      <c r="AD127">
+        <v>9</v>
+      </c>
+      <c r="AE127">
+        <v>1.38</v>
+      </c>
+      <c r="AF127">
+        <v>3.1</v>
+      </c>
+      <c r="AG127">
+        <v>1.85</v>
+      </c>
+      <c r="AH127">
+        <v>1.85</v>
+      </c>
+      <c r="AI127">
+        <v>1.95</v>
+      </c>
+      <c r="AJ127">
+        <v>1.8</v>
+      </c>
+      <c r="AK127">
+        <v>1.3</v>
+      </c>
+      <c r="AL127">
+        <v>1.25</v>
+      </c>
+      <c r="AM127">
+        <v>1.67</v>
+      </c>
+      <c r="AN127">
+        <v>2.43</v>
+      </c>
+      <c r="AO127">
+        <v>1.67</v>
+      </c>
+      <c r="AP127">
+        <v>2.5</v>
+      </c>
+      <c r="AQ127">
+        <v>1.5</v>
+      </c>
+      <c r="AR127">
+        <v>1.43</v>
+      </c>
+      <c r="AS127">
+        <v>1.31</v>
+      </c>
+      <c r="AT127">
+        <v>2.74</v>
+      </c>
+      <c r="AU127">
+        <v>5</v>
+      </c>
+      <c r="AV127">
+        <v>2</v>
+      </c>
+      <c r="AW127">
+        <v>6</v>
+      </c>
+      <c r="AX127">
+        <v>7</v>
+      </c>
+      <c r="AY127">
+        <v>11</v>
+      </c>
+      <c r="AZ127">
+        <v>9</v>
+      </c>
+      <c r="BA127">
+        <v>5</v>
+      </c>
+      <c r="BB127">
+        <v>5</v>
+      </c>
+      <c r="BC127">
+        <v>10</v>
+      </c>
+      <c r="BD127">
+        <v>1.85</v>
+      </c>
+      <c r="BE127">
+        <v>6.75</v>
+      </c>
+      <c r="BF127">
+        <v>2.12</v>
+      </c>
+      <c r="BG127">
+        <v>1.14</v>
+      </c>
+      <c r="BH127">
+        <v>4.8</v>
+      </c>
+      <c r="BI127">
+        <v>1.26</v>
+      </c>
+      <c r="BJ127">
+        <v>3.4</v>
+      </c>
+      <c r="BK127">
+        <v>1.45</v>
+      </c>
+      <c r="BL127">
+        <v>2.55</v>
+      </c>
+      <c r="BM127">
+        <v>1.72</v>
+      </c>
+      <c r="BN127">
+        <v>1.98</v>
+      </c>
+      <c r="BO127">
+        <v>2.1</v>
+      </c>
+      <c r="BP127">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="128" spans="1:68">
+      <c r="A128" s="1">
+        <v>127</v>
+      </c>
+      <c r="B128">
+        <v>7779077</v>
+      </c>
+      <c r="C128" t="s">
+        <v>68</v>
+      </c>
+      <c r="D128" t="s">
+        <v>69</v>
+      </c>
+      <c r="E128" s="2">
+        <v>45858.375</v>
+      </c>
+      <c r="F128">
+        <v>16</v>
+      </c>
+      <c r="G128" t="s">
+        <v>79</v>
+      </c>
+      <c r="H128" t="s">
+        <v>78</v>
+      </c>
+      <c r="I128">
+        <v>0</v>
+      </c>
+      <c r="J128">
+        <v>0</v>
+      </c>
+      <c r="K128">
+        <v>0</v>
+      </c>
+      <c r="L128">
+        <v>0</v>
+      </c>
+      <c r="M128">
+        <v>1</v>
+      </c>
+      <c r="N128">
+        <v>1</v>
+      </c>
+      <c r="O128" t="s">
+        <v>86</v>
+      </c>
+      <c r="P128" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q128">
+        <v>2.88</v>
+      </c>
+      <c r="R128">
+        <v>2.3</v>
+      </c>
+      <c r="S128">
+        <v>3.25</v>
+      </c>
+      <c r="T128">
+        <v>1.33</v>
+      </c>
+      <c r="U128">
+        <v>3.25</v>
+      </c>
+      <c r="V128">
+        <v>2.5</v>
+      </c>
+      <c r="W128">
+        <v>1.5</v>
+      </c>
+      <c r="X128">
+        <v>6</v>
+      </c>
+      <c r="Y128">
+        <v>1.13</v>
+      </c>
+      <c r="Z128">
+        <v>2.49</v>
+      </c>
+      <c r="AA128">
+        <v>3.33</v>
+      </c>
+      <c r="AB128">
+        <v>2.4</v>
+      </c>
+      <c r="AC128">
+        <v>1.05</v>
+      </c>
+      <c r="AD128">
+        <v>10</v>
+      </c>
+      <c r="AE128">
+        <v>1.25</v>
+      </c>
+      <c r="AF128">
+        <v>4</v>
+      </c>
+      <c r="AG128">
+        <v>1.67</v>
+      </c>
+      <c r="AH128">
+        <v>2.07</v>
+      </c>
+      <c r="AI128">
+        <v>1.57</v>
+      </c>
+      <c r="AJ128">
+        <v>2.25</v>
+      </c>
+      <c r="AK128">
+        <v>1.45</v>
+      </c>
+      <c r="AL128">
+        <v>1.25</v>
+      </c>
+      <c r="AM128">
+        <v>1.53</v>
+      </c>
+      <c r="AN128">
+        <v>1</v>
+      </c>
+      <c r="AO128">
+        <v>1.71</v>
+      </c>
+      <c r="AP128">
+        <v>0.88</v>
+      </c>
+      <c r="AQ128">
+        <v>1.88</v>
+      </c>
+      <c r="AR128">
+        <v>1.78</v>
+      </c>
+      <c r="AS128">
+        <v>1.18</v>
+      </c>
+      <c r="AT128">
+        <v>2.96</v>
+      </c>
+      <c r="AU128">
+        <v>4</v>
+      </c>
+      <c r="AV128">
+        <v>4</v>
+      </c>
+      <c r="AW128">
+        <v>13</v>
+      </c>
+      <c r="AX128">
+        <v>10</v>
+      </c>
+      <c r="AY128">
+        <v>17</v>
+      </c>
+      <c r="AZ128">
+        <v>14</v>
+      </c>
+      <c r="BA128">
+        <v>3</v>
+      </c>
+      <c r="BB128">
+        <v>6</v>
+      </c>
+      <c r="BC128">
+        <v>9</v>
+      </c>
+      <c r="BD128">
+        <v>2.15</v>
+      </c>
+      <c r="BE128">
+        <v>6.5</v>
+      </c>
+      <c r="BF128">
+        <v>1.86</v>
+      </c>
+      <c r="BG128">
+        <v>1.16</v>
+      </c>
+      <c r="BH128">
+        <v>4.6</v>
+      </c>
+      <c r="BI128">
+        <v>1.29</v>
+      </c>
+      <c r="BJ128">
+        <v>3.2</v>
+      </c>
+      <c r="BK128">
+        <v>1.49</v>
+      </c>
+      <c r="BL128">
+        <v>2.4</v>
+      </c>
+      <c r="BM128">
+        <v>1.78</v>
+      </c>
+      <c r="BN128">
+        <v>1.91</v>
+      </c>
+      <c r="BO128">
+        <v>2.2</v>
+      </c>
+      <c r="BP128">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="129" spans="1:68">
+      <c r="A129" s="1">
+        <v>128</v>
+      </c>
+      <c r="B129">
+        <v>7779073</v>
+      </c>
+      <c r="C129" t="s">
+        <v>68</v>
+      </c>
+      <c r="D129" t="s">
+        <v>69</v>
+      </c>
+      <c r="E129" s="2">
+        <v>45858.47916666666</v>
+      </c>
+      <c r="F129">
+        <v>16</v>
+      </c>
+      <c r="G129" t="s">
+        <v>72</v>
+      </c>
+      <c r="H129" t="s">
+        <v>82</v>
+      </c>
+      <c r="I129">
+        <v>0</v>
+      </c>
+      <c r="J129">
+        <v>2</v>
+      </c>
+      <c r="K129">
+        <v>2</v>
+      </c>
+      <c r="L129">
+        <v>3</v>
+      </c>
+      <c r="M129">
+        <v>2</v>
+      </c>
+      <c r="N129">
+        <v>5</v>
+      </c>
+      <c r="O129" t="s">
+        <v>172</v>
+      </c>
+      <c r="P129" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q129">
+        <v>2.05</v>
+      </c>
+      <c r="R129">
+        <v>2.5</v>
+      </c>
+      <c r="S129">
+        <v>5</v>
+      </c>
+      <c r="T129">
+        <v>1.25</v>
+      </c>
+      <c r="U129">
+        <v>3.75</v>
+      </c>
+      <c r="V129">
+        <v>2.2</v>
+      </c>
+      <c r="W129">
+        <v>1.62</v>
+      </c>
+      <c r="X129">
+        <v>5</v>
+      </c>
+      <c r="Y129">
+        <v>1.17</v>
+      </c>
+      <c r="Z129">
+        <v>1.52</v>
+      </c>
+      <c r="AA129">
+        <v>4.1</v>
+      </c>
+      <c r="AB129">
+        <v>4.7</v>
+      </c>
+      <c r="AC129">
+        <v>1.01</v>
+      </c>
+      <c r="AD129">
+        <v>17</v>
+      </c>
+      <c r="AE129">
+        <v>1.18</v>
+      </c>
+      <c r="AF129">
+        <v>5</v>
+      </c>
+      <c r="AG129">
+        <v>1.6</v>
+      </c>
+      <c r="AH129">
+        <v>2.34</v>
+      </c>
+      <c r="AI129">
+        <v>1.62</v>
+      </c>
+      <c r="AJ129">
+        <v>2.2</v>
+      </c>
+      <c r="AK129">
+        <v>1.15</v>
+      </c>
+      <c r="AL129">
+        <v>1.17</v>
+      </c>
+      <c r="AM129">
+        <v>2.3</v>
+      </c>
+      <c r="AN129">
+        <v>2.44</v>
+      </c>
+      <c r="AO129">
+        <v>1.63</v>
+      </c>
+      <c r="AP129">
+        <v>2.5</v>
+      </c>
+      <c r="AQ129">
+        <v>1.44</v>
+      </c>
+      <c r="AR129">
+        <v>2.2</v>
+      </c>
+      <c r="AS129">
+        <v>1.62</v>
+      </c>
+      <c r="AT129">
+        <v>3.82</v>
+      </c>
+      <c r="AU129">
+        <v>10</v>
+      </c>
+      <c r="AV129">
+        <v>5</v>
+      </c>
+      <c r="AW129">
+        <v>12</v>
+      </c>
+      <c r="AX129">
+        <v>9</v>
+      </c>
+      <c r="AY129">
+        <v>22</v>
+      </c>
+      <c r="AZ129">
+        <v>14</v>
+      </c>
+      <c r="BA129">
+        <v>8</v>
+      </c>
+      <c r="BB129">
+        <v>6</v>
+      </c>
+      <c r="BC129">
+        <v>14</v>
+      </c>
+      <c r="BD129">
+        <v>1.34</v>
+      </c>
+      <c r="BE129">
+        <v>7.5</v>
+      </c>
+      <c r="BF129">
+        <v>3.55</v>
+      </c>
+      <c r="BG129">
+        <v>1.13</v>
+      </c>
+      <c r="BH129">
+        <v>5.1</v>
+      </c>
+      <c r="BI129">
+        <v>1.23</v>
+      </c>
+      <c r="BJ129">
+        <v>3.65</v>
+      </c>
+      <c r="BK129">
+        <v>1.4</v>
+      </c>
+      <c r="BL129">
+        <v>2.7</v>
+      </c>
+      <c r="BM129">
+        <v>1.64</v>
+      </c>
+      <c r="BN129">
+        <v>2.1</v>
+      </c>
+      <c r="BO129">
+        <v>1.98</v>
+      </c>
+      <c r="BP129">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="130" spans="1:68">
+      <c r="A130" s="1">
+        <v>129</v>
+      </c>
+      <c r="B130">
+        <v>7779078</v>
+      </c>
+      <c r="C130" t="s">
+        <v>68</v>
+      </c>
+      <c r="D130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E130" s="2">
+        <v>45858.47916666666</v>
+      </c>
+      <c r="F130">
+        <v>16</v>
+      </c>
+      <c r="G130" t="s">
+        <v>75</v>
+      </c>
+      <c r="H130" t="s">
+        <v>71</v>
+      </c>
+      <c r="I130">
+        <v>0</v>
+      </c>
+      <c r="J130">
+        <v>0</v>
+      </c>
+      <c r="K130">
+        <v>0</v>
+      </c>
+      <c r="L130">
+        <v>0</v>
+      </c>
+      <c r="M130">
+        <v>0</v>
+      </c>
+      <c r="N130">
+        <v>0</v>
+      </c>
+      <c r="O130" t="s">
+        <v>86</v>
+      </c>
+      <c r="P130" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q130">
+        <v>4</v>
+      </c>
+      <c r="R130">
+        <v>2.25</v>
+      </c>
+      <c r="S130">
+        <v>2.63</v>
+      </c>
+      <c r="T130">
+        <v>1.33</v>
+      </c>
+      <c r="U130">
+        <v>3.25</v>
+      </c>
+      <c r="V130">
+        <v>2.63</v>
+      </c>
+      <c r="W130">
+        <v>1.44</v>
+      </c>
+      <c r="X130">
+        <v>7</v>
+      </c>
+      <c r="Y130">
+        <v>1.1</v>
+      </c>
+      <c r="Z130">
+        <v>3.17</v>
+      </c>
+      <c r="AA130">
+        <v>3.45</v>
+      </c>
+      <c r="AB130">
+        <v>1.94</v>
+      </c>
+      <c r="AC130">
+        <v>1.05</v>
+      </c>
+      <c r="AD130">
+        <v>10</v>
+      </c>
+      <c r="AE130">
+        <v>1.25</v>
+      </c>
+      <c r="AF130">
+        <v>3.85</v>
+      </c>
+      <c r="AG130">
+        <v>1.76</v>
+      </c>
+      <c r="AH130">
+        <v>1.94</v>
+      </c>
+      <c r="AI130">
+        <v>1.67</v>
+      </c>
+      <c r="AJ130">
+        <v>2.1</v>
+      </c>
+      <c r="AK130">
+        <v>1.75</v>
+      </c>
+      <c r="AL130">
+        <v>1.25</v>
+      </c>
+      <c r="AM130">
+        <v>1.3</v>
+      </c>
+      <c r="AN130">
+        <v>1.5</v>
+      </c>
+      <c r="AO130">
+        <v>1.43</v>
+      </c>
+      <c r="AP130">
+        <v>1.44</v>
+      </c>
+      <c r="AQ130">
+        <v>1.38</v>
+      </c>
+      <c r="AR130">
+        <v>1.22</v>
+      </c>
+      <c r="AS130">
+        <v>1.67</v>
+      </c>
+      <c r="AT130">
+        <v>2.89</v>
+      </c>
+      <c r="AU130">
+        <v>6</v>
+      </c>
+      <c r="AV130">
+        <v>7</v>
+      </c>
+      <c r="AW130">
+        <v>7</v>
+      </c>
+      <c r="AX130">
+        <v>14</v>
+      </c>
+      <c r="AY130">
+        <v>13</v>
+      </c>
+      <c r="AZ130">
+        <v>21</v>
+      </c>
+      <c r="BA130">
+        <v>2</v>
+      </c>
+      <c r="BB130">
+        <v>11</v>
+      </c>
+      <c r="BC130">
+        <v>13</v>
+      </c>
+      <c r="BD130">
+        <v>3.05</v>
+      </c>
+      <c r="BE130">
+        <v>7</v>
+      </c>
+      <c r="BF130">
+        <v>1.45</v>
+      </c>
+      <c r="BG130">
+        <v>1.18</v>
+      </c>
+      <c r="BH130">
+        <v>4.3</v>
+      </c>
+      <c r="BI130">
+        <v>1.3</v>
+      </c>
+      <c r="BJ130">
+        <v>3.05</v>
+      </c>
+      <c r="BK130">
+        <v>1.52</v>
+      </c>
+      <c r="BL130">
+        <v>2.32</v>
+      </c>
+      <c r="BM130">
+        <v>1.84</v>
+      </c>
+      <c r="BN130">
+        <v>1.84</v>
+      </c>
+      <c r="BO130">
+        <v>2.32</v>
+      </c>
+      <c r="BP130">
+        <v>1.53</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Sweden Allsvenskan_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="237">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -535,6 +535,9 @@
     <t>['54', '72', '76']</t>
   </si>
   <si>
+    <t>['3', '52', '55']</t>
+  </si>
+  <si>
     <t>['45+8']</t>
   </si>
   <si>
@@ -719,6 +722,9 @@
   </si>
   <si>
     <t>['43', '45+7']</t>
+  </si>
+  <si>
+    <t>['48']</t>
   </si>
 </sst>
 </file>
@@ -1080,7 +1086,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP130"/>
+  <dimension ref="A1:BP131"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1336,7 +1342,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q2">
         <v>3.5</v>
@@ -2160,7 +2166,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q6">
         <v>2.6</v>
@@ -2238,7 +2244,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ6">
         <v>0.63</v>
@@ -2366,7 +2372,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -2572,7 +2578,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -2778,7 +2784,7 @@
         <v>86</v>
       </c>
       <c r="P9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3190,7 +3196,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q11">
         <v>4</v>
@@ -3602,7 +3608,7 @@
         <v>94</v>
       </c>
       <c r="P13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -3808,7 +3814,7 @@
         <v>86</v>
       </c>
       <c r="P14" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4095,7 +4101,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ15">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4220,7 +4226,7 @@
         <v>96</v>
       </c>
       <c r="P16" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q16">
         <v>2.55</v>
@@ -4426,7 +4432,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -4632,7 +4638,7 @@
         <v>86</v>
       </c>
       <c r="P18" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q18">
         <v>2.62</v>
@@ -5250,7 +5256,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5662,7 +5668,7 @@
         <v>86</v>
       </c>
       <c r="P23" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q23">
         <v>2.62</v>
@@ -6280,7 +6286,7 @@
         <v>102</v>
       </c>
       <c r="P26" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q26">
         <v>3.2</v>
@@ -6486,7 +6492,7 @@
         <v>103</v>
       </c>
       <c r="P27" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q27">
         <v>1.72</v>
@@ -6976,7 +6982,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ29">
         <v>0.57</v>
@@ -7310,7 +7316,7 @@
         <v>105</v>
       </c>
       <c r="P31" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7391,7 +7397,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ31">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AR31">
         <v>1.47</v>
@@ -7516,7 +7522,7 @@
         <v>106</v>
       </c>
       <c r="P32" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q32">
         <v>2.88</v>
@@ -8134,7 +8140,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8340,7 +8346,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q36">
         <v>4.75</v>
@@ -8546,7 +8552,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q37">
         <v>2</v>
@@ -8752,7 +8758,7 @@
         <v>111</v>
       </c>
       <c r="P38" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q38">
         <v>4</v>
@@ -8958,7 +8964,7 @@
         <v>112</v>
       </c>
       <c r="P39" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9036,7 +9042,7 @@
         <v>1.5</v>
       </c>
       <c r="AP39">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ39">
         <v>1.88</v>
@@ -9576,7 +9582,7 @@
         <v>114</v>
       </c>
       <c r="P42" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q42">
         <v>2.95</v>
@@ -9782,7 +9788,7 @@
         <v>115</v>
       </c>
       <c r="P43" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q43">
         <v>2</v>
@@ -10194,7 +10200,7 @@
         <v>117</v>
       </c>
       <c r="P45" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -11018,7 +11024,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q49">
         <v>3</v>
@@ -11224,7 +11230,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q50">
         <v>3.75</v>
@@ -11305,7 +11311,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ50">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AR50">
         <v>1.29</v>
@@ -11636,7 +11642,7 @@
         <v>86</v>
       </c>
       <c r="P52" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -11714,7 +11720,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ52">
         <v>1.38</v>
@@ -11842,7 +11848,7 @@
         <v>86</v>
       </c>
       <c r="P53" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q53">
         <v>5.5</v>
@@ -12254,7 +12260,7 @@
         <v>125</v>
       </c>
       <c r="P55" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q55">
         <v>1.83</v>
@@ -12872,7 +12878,7 @@
         <v>127</v>
       </c>
       <c r="P58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q58">
         <v>2.38</v>
@@ -12953,7 +12959,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ58">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AR58">
         <v>1.92</v>
@@ -13284,7 +13290,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q60">
         <v>3.1</v>
@@ -13902,7 +13908,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q63">
         <v>6</v>
@@ -14108,7 +14114,7 @@
         <v>132</v>
       </c>
       <c r="P64" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14314,7 +14320,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q65">
         <v>4.5</v>
@@ -14520,7 +14526,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q66">
         <v>1.83</v>
@@ -14726,7 +14732,7 @@
         <v>135</v>
       </c>
       <c r="P67" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q67">
         <v>3.1</v>
@@ -14932,7 +14938,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q68">
         <v>5.25</v>
@@ -15138,7 +15144,7 @@
         <v>103</v>
       </c>
       <c r="P69" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q69">
         <v>2.38</v>
@@ -15216,7 +15222,7 @@
         <v>1.5</v>
       </c>
       <c r="AP69">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ69">
         <v>1.13</v>
@@ -15344,7 +15350,7 @@
         <v>137</v>
       </c>
       <c r="P70" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q70">
         <v>2.2</v>
@@ -15550,7 +15556,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q71">
         <v>2.95</v>
@@ -16249,7 +16255,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ74">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AR74">
         <v>1.9</v>
@@ -16374,7 +16380,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q75">
         <v>3.95</v>
@@ -16992,7 +16998,7 @@
         <v>143</v>
       </c>
       <c r="P78" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q78">
         <v>2.75</v>
@@ -17198,7 +17204,7 @@
         <v>144</v>
       </c>
       <c r="P79" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -17610,7 +17616,7 @@
         <v>146</v>
       </c>
       <c r="P81" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q81">
         <v>2.45</v>
@@ -18022,7 +18028,7 @@
         <v>127</v>
       </c>
       <c r="P83" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q83">
         <v>2.45</v>
@@ -18228,7 +18234,7 @@
         <v>147</v>
       </c>
       <c r="P84" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q84">
         <v>2.5</v>
@@ -18640,7 +18646,7 @@
         <v>118</v>
       </c>
       <c r="P86" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q86">
         <v>4.75</v>
@@ -18846,7 +18852,7 @@
         <v>86</v>
       </c>
       <c r="P87" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q87">
         <v>3.5</v>
@@ -19336,7 +19342,7 @@
         <v>2.17</v>
       </c>
       <c r="AP89">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ89">
         <v>2.22</v>
@@ -19670,7 +19676,7 @@
         <v>86</v>
       </c>
       <c r="P91" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q91">
         <v>3.4</v>
@@ -19876,7 +19882,7 @@
         <v>86</v>
       </c>
       <c r="P92" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q92">
         <v>2.9</v>
@@ -20288,7 +20294,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -20366,7 +20372,7 @@
         <v>1.17</v>
       </c>
       <c r="AP94">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ94">
         <v>1.78</v>
@@ -20906,7 +20912,7 @@
         <v>148</v>
       </c>
       <c r="P97" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21193,7 +21199,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ98">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AR98">
         <v>1.34</v>
@@ -21318,7 +21324,7 @@
         <v>154</v>
       </c>
       <c r="P99" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q99">
         <v>3.45</v>
@@ -21730,7 +21736,7 @@
         <v>156</v>
       </c>
       <c r="P101" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q101">
         <v>3.4</v>
@@ -21936,7 +21942,7 @@
         <v>86</v>
       </c>
       <c r="P102" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22348,7 +22354,7 @@
         <v>158</v>
       </c>
       <c r="P104" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q104">
         <v>3.1</v>
@@ -22966,7 +22972,7 @@
         <v>160</v>
       </c>
       <c r="P107" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q107">
         <v>2.25</v>
@@ -23378,7 +23384,7 @@
         <v>86</v>
       </c>
       <c r="P109" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q109">
         <v>4.75</v>
@@ -23665,7 +23671,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ110">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AR110">
         <v>2.17</v>
@@ -23790,7 +23796,7 @@
         <v>162</v>
       </c>
       <c r="P111" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q111">
         <v>2.38</v>
@@ -24408,7 +24414,7 @@
         <v>164</v>
       </c>
       <c r="P114" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q114">
         <v>2.2</v>
@@ -24614,7 +24620,7 @@
         <v>86</v>
       </c>
       <c r="P115" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -24692,7 +24698,7 @@
         <v>1.43</v>
       </c>
       <c r="AP115">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ115">
         <v>1.44</v>
@@ -24820,7 +24826,7 @@
         <v>123</v>
       </c>
       <c r="P116" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q116">
         <v>3</v>
@@ -25438,7 +25444,7 @@
         <v>167</v>
       </c>
       <c r="P119" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q119">
         <v>3.4</v>
@@ -26056,7 +26062,7 @@
         <v>169</v>
       </c>
       <c r="P122" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q122">
         <v>2.2</v>
@@ -26262,7 +26268,7 @@
         <v>111</v>
       </c>
       <c r="P123" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q123">
         <v>4</v>
@@ -26674,7 +26680,7 @@
         <v>86</v>
       </c>
       <c r="P125" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q125">
         <v>5.75</v>
@@ -26880,7 +26886,7 @@
         <v>86</v>
       </c>
       <c r="P126" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27292,7 +27298,7 @@
         <v>86</v>
       </c>
       <c r="P128" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q128">
         <v>2.88</v>
@@ -27498,7 +27504,7 @@
         <v>172</v>
       </c>
       <c r="P129" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q129">
         <v>2.05</v>
@@ -27861,6 +27867,212 @@
       </c>
       <c r="BP130">
         <v>1.53</v>
+      </c>
+    </row>
+    <row r="131" spans="1:68">
+      <c r="A131" s="1">
+        <v>130</v>
+      </c>
+      <c r="B131">
+        <v>7779076</v>
+      </c>
+      <c r="C131" t="s">
+        <v>68</v>
+      </c>
+      <c r="D131" t="s">
+        <v>69</v>
+      </c>
+      <c r="E131" s="2">
+        <v>45859.58333333334</v>
+      </c>
+      <c r="F131">
+        <v>16</v>
+      </c>
+      <c r="G131" t="s">
+        <v>74</v>
+      </c>
+      <c r="H131" t="s">
+        <v>76</v>
+      </c>
+      <c r="I131">
+        <v>1</v>
+      </c>
+      <c r="J131">
+        <v>0</v>
+      </c>
+      <c r="K131">
+        <v>1</v>
+      </c>
+      <c r="L131">
+        <v>3</v>
+      </c>
+      <c r="M131">
+        <v>1</v>
+      </c>
+      <c r="N131">
+        <v>4</v>
+      </c>
+      <c r="O131" t="s">
+        <v>173</v>
+      </c>
+      <c r="P131" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q131">
+        <v>2.75</v>
+      </c>
+      <c r="R131">
+        <v>2.3</v>
+      </c>
+      <c r="S131">
+        <v>3.5</v>
+      </c>
+      <c r="T131">
+        <v>1.3</v>
+      </c>
+      <c r="U131">
+        <v>3.4</v>
+      </c>
+      <c r="V131">
+        <v>2.5</v>
+      </c>
+      <c r="W131">
+        <v>1.5</v>
+      </c>
+      <c r="X131">
+        <v>6</v>
+      </c>
+      <c r="Y131">
+        <v>1.13</v>
+      </c>
+      <c r="Z131">
+        <v>2.04</v>
+      </c>
+      <c r="AA131">
+        <v>3.56</v>
+      </c>
+      <c r="AB131">
+        <v>2.88</v>
+      </c>
+      <c r="AC131">
+        <v>1.04</v>
+      </c>
+      <c r="AD131">
+        <v>11</v>
+      </c>
+      <c r="AE131">
+        <v>1.22</v>
+      </c>
+      <c r="AF131">
+        <v>4.33</v>
+      </c>
+      <c r="AG131">
+        <v>1.57</v>
+      </c>
+      <c r="AH131">
+        <v>2.25</v>
+      </c>
+      <c r="AI131">
+        <v>1.57</v>
+      </c>
+      <c r="AJ131">
+        <v>2.25</v>
+      </c>
+      <c r="AK131">
+        <v>1.36</v>
+      </c>
+      <c r="AL131">
+        <v>1.25</v>
+      </c>
+      <c r="AM131">
+        <v>1.67</v>
+      </c>
+      <c r="AN131">
+        <v>0.88</v>
+      </c>
+      <c r="AO131">
+        <v>0.14</v>
+      </c>
+      <c r="AP131">
+        <v>1.11</v>
+      </c>
+      <c r="AQ131">
+        <v>0.13</v>
+      </c>
+      <c r="AR131">
+        <v>1.74</v>
+      </c>
+      <c r="AS131">
+        <v>1.46</v>
+      </c>
+      <c r="AT131">
+        <v>3.2</v>
+      </c>
+      <c r="AU131">
+        <v>7</v>
+      </c>
+      <c r="AV131">
+        <v>5</v>
+      </c>
+      <c r="AW131">
+        <v>10</v>
+      </c>
+      <c r="AX131">
+        <v>14</v>
+      </c>
+      <c r="AY131">
+        <v>17</v>
+      </c>
+      <c r="AZ131">
+        <v>19</v>
+      </c>
+      <c r="BA131">
+        <v>4</v>
+      </c>
+      <c r="BB131">
+        <v>7</v>
+      </c>
+      <c r="BC131">
+        <v>11</v>
+      </c>
+      <c r="BD131">
+        <v>1.95</v>
+      </c>
+      <c r="BE131">
+        <v>6.75</v>
+      </c>
+      <c r="BF131">
+        <v>2.02</v>
+      </c>
+      <c r="BG131">
+        <v>1.08</v>
+      </c>
+      <c r="BH131">
+        <v>6.25</v>
+      </c>
+      <c r="BI131">
+        <v>1.16</v>
+      </c>
+      <c r="BJ131">
+        <v>4.4</v>
+      </c>
+      <c r="BK131">
+        <v>1.29</v>
+      </c>
+      <c r="BL131">
+        <v>3.2</v>
+      </c>
+      <c r="BM131">
+        <v>1.49</v>
+      </c>
+      <c r="BN131">
+        <v>2.43</v>
+      </c>
+      <c r="BO131">
+        <v>1.75</v>
+      </c>
+      <c r="BP131">
+        <v>1.95</v>
       </c>
     </row>
   </sheetData>
